--- a/marketing/Calendario_Editorial_FairHealth.xlsx
+++ b/marketing/Calendario_Editorial_FairHealth.xlsx
@@ -12,11 +12,12 @@
     <sheet name="Visão do mês" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Calendário" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Formatos" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Fontes" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Banco de ideias" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Linhas e personas" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Pendências" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Listas" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Ciência" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Fontes" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Banco de ideias" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Linhas e personas" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Pendências" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Listas" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Calendário!$A$4:$Z$80</definedName>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="678">
   <si>
     <t xml:space="preserve">Calendário editorial · Fair Health · Instagram e LinkedIn</t>
   </si>
@@ -82,7 +83,13 @@
     <t xml:space="preserve">2. Não filmamos clientes: nada gravado dentro das empresas-clientes nem com pessoas atendidas. Os vídeos do mês são de tipografia, motion, gravação de tela ou imagem de banco (aba Formatos).</t>
   </si>
   <si>
-    <t xml:space="preserve">3. O artigo do cofundador Fernando Brancaccio na RH Pra Você (25/09/2026) entra como peça de autoridade, sem foto e sem apresentação do time.</t>
+    <t xml:space="preserve">3. Nunca citamos nomes reais de pessoas ou empresas nos posts. Quando a história precisa de alguém, usamos personagem fictícia, sinalizada como "história ilustrativa". O artigo da RH Pra Você (25/09/2026) é citado só pelo título e pelo veículo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Números são bem-vindos, mas o foco é o cuidado: a frase de cuidado vem primeiro e o número entra como contexto, em tom calmo, com a fonte visível (regras na aba Ciência).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Artigos científicos e fontes oficiais viram posts que conectam a evidência ao nosso trabalho (aba Ciência). Medicina do Estilo de Vida: 6 pilares, sem espiritualidade (a confirmar).</t>
   </si>
   <si>
     <t xml:space="preserve">Como trabalhamos nesta planilha</t>
@@ -118,7 +125,7 @@
     <t xml:space="preserve">Coluna "Validação necessária": tudo o que precisa de aval antes de publicar. Afirmações clínicas, benefícios, prazos e resultados passam pela responsável médica.</t>
   </si>
   <si>
-    <t xml:space="preserve">Só usamos números liberados e com fonte (aba Fontes). Números do posicionamento sem fonte (23%, R$ 2.400, burnout) ficam de fora.</t>
+    <t xml:space="preserve">Usamos números liberados (aba Fontes) e números de estudos científicos e fontes oficiais com a referência completa (aba Ciência). Números do posicionamento sem fonte (23%, R$ 2.400, burnout) ficam de fora.</t>
   </si>
   <si>
     <t xml:space="preserve">Fluxo de status</t>
@@ -139,7 +146,10 @@
     <t xml:space="preserve">Formatos: os formatos usados no mês, por que funcionam e o que cada um precisa para ser produzido sem time em cena e sem gravar nas empresas.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fontes: o artigo do cofundador, os números liberados e o que não usar.</t>
+    <t xml:space="preserve">Ciência: estudos e fontes oficiais com referência, o que encontraram, como apresentar o número com suavidade e a ligação com o nosso trabalho.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fontes: o artigo da RH Pra Você, os números internos liberados e o que não usar.</t>
   </si>
   <si>
     <t xml:space="preserve">Banco de ideias: o que ficou para depois (com o motivo) e os temas dos próximos meses.</t>
@@ -172,7 +182,7 @@
     <t xml:space="preserve">Argumento principal</t>
   </si>
   <si>
-    <t xml:space="preserve">Liderança Bem-Estar, com a apresentação da marca. A NR-1 entra como contexto (artigo do cofundador) e abre o próximo mês.</t>
+    <t xml:space="preserve">Liderança Bem-Estar, com a apresentação da marca. A NR-1 entra como contexto (artigo da RH Pra Você) e a ciência sustenta o mês (OMS, Diabetes Prevention Program, RAND).</t>
   </si>
   <si>
     <t xml:space="preserve">Mensagem do mês</t>
@@ -190,13 +200,19 @@
     <t xml:space="preserve">Restrições</t>
   </si>
   <si>
-    <t xml:space="preserve">Sem apresentar o time (questão administrativa) e sem filmar clientes. Vídeos de tipografia, motion, gravação de tela ou imagem de banco.</t>
+    <t xml:space="preserve">Sem apresentar o time (questão administrativa), sem filmar clientes e sem nomes reais (personagens fictícias quando preciso). Vídeos de tipografia, motion, gravação de tela ou imagem de banco.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Números</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sim, com suavidade: cuidado primeiro, número como contexto, fonte visível. Um número principal por peça.</t>
   </si>
   <si>
     <t xml:space="preserve">Datas do calendário</t>
   </si>
   <si>
-    <t xml:space="preserve">02/11 feriado (Finados): a semana 3 começa na terça. 14/11 (sábado) Dia Mundial do Diabetes: avaliar um stories com a responsável médica. Novembro Azul: só se houver conexão real.</t>
+    <t xml:space="preserve">02/11 feriado (Finados): a semana 3 começa na terça. 14/11 (sábado) Dia Mundial do Diabetes: post de ciência na véspera (M1-16) e stories no dia. Novembro Azul: só se houver conexão real.</t>
   </si>
   <si>
     <t xml:space="preserve">A história semana a semana</t>
@@ -259,7 +275,7 @@
     <t xml:space="preserve">Convite</t>
   </si>
   <si>
-    <t xml:space="preserve">"Como começo?" Para o colaborador, o líder e o RH; abre o tema NR-1.</t>
+    <t xml:space="preserve">"Como começo?" Para o colaborador, o líder e o RH, com a ciência por trás do cuidado.</t>
   </si>
   <si>
     <t xml:space="preserve">M1-13 a M1-16</t>
@@ -521,10 +537,10 @@
     <t xml:space="preserve">Todo afastamento tem um antes. A Fair Health cuida nesse antes, dentro da empresa, começando por uma pergunta.</t>
   </si>
   <si>
-    <t xml:space="preserve">Posicionamento Fair Health v3.2 (eixo "antes", dores de entrada do RH).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sem números e sem promessa de evitar doença (CFM): o texto fala de cuidado, não de resultado.</t>
+    <t xml:space="preserve">Posicionamento Fair Health v3.2 (eixo "antes"). Ministério da Previdência Social: 472.328 licenças por transtornos mentais em 2024, maior número da série iniciada em 2014 (dados divulgados em 2025; conferir no painel oficial de dados abertos antes de publicar).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sem promessa de evitar doença (CFM): o texto fala de cuidado, não de resultado. Número suave: cuidado primeiro, número como contexto, fonte visível e discreta (aba Ciência). Conferir o número no painel oficial.</t>
   </si>
   <si>
     <t xml:space="preserve">Pauta proposta</t>
@@ -534,18 +550,20 @@
 Antes do atestado, teve uma semana pesada.
 Antes da semana pesada, teve uma noite sem dormir.
 E antes de tudo isso, ninguém perguntou: o que é importante para você?
+Em 2024, o Brasil registrou mais de 470 mil licenças do trabalho por saúde mental, o maior número em dez anos (Ministério da Previdência Social). Cada uma delas teve um antes.
 A Fair Health existe para cuidar nesse antes. Dentro da empresa, perto de quem trabalha, com médicos e psicólogos e um plano feito para cada pessoa.
 Cuidar antes também é papel da liderança. Na sua empresa, quem faz essa pergunta?
 #fairhealth #saudecorporativa #cuidadocentradonapessoa #medicinadoestilodevida #saudedotrabalhador</t>
   </si>
   <si>
-    <t xml:space="preserve">Reel de 18 a 22 s, só tipografia sobre o fundo Tiffany, frase a frase, com corte seco.
+    <t xml:space="preserve">Reel de 22 a 26 s, só tipografia sobre o fundo Tiffany, frase a frase, com corte seco.
 0–3 s: "Antes do afastamento, teve um atestado."
 3–6 s: "Antes do atestado, teve uma semana pesada."
 6–9 s: "Antes da semana pesada, uma noite sem dormir."
 9–14 s: "E antes de tudo isso, ninguém perguntou:"
 14–18 s: "O que é importante para você?" (palavra-chave em destaque)
-18–22 s: "Cuidar antes." + logo.
+18–22 s: em texto menor e calmo: "Em 2024, mais de 470 mil licenças por saúde mental no Brasil. Cada uma teve um antes." Fonte no rodapé.
+22–26 s: "Cuidar antes." + logo.
 Trilha calma, sem locução (ou voz em off opcional).</t>
   </si>
   <si>
@@ -558,7 +576,7 @@
     <t xml:space="preserve">Projetos, eventos e entregas</t>
   </si>
   <si>
-    <t xml:space="preserve">Na imprensa: artigo do cofundador</t>
+    <t xml:space="preserve">Na imprensa: artigo sobre riscos psicossociais</t>
   </si>
   <si>
     <t xml:space="preserve">Saúde mental é de todos (1/2)</t>
@@ -576,24 +594,24 @@
     <t xml:space="preserve">Trazer a NR-1 com uma visão madura e transferir a autoridade da publicação para a marca</t>
   </si>
   <si>
-    <t xml:space="preserve">Carrossel-resumo de artigo publicado: formato muito compartilhado entre profissionais de RH. Leva a autoridade do veículo (RH Pra Você) e do autor sem precisar apresentar o time.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FairJob; Fernando Brancaccio (se quiser); RH Pra Você (marcar)</t>
+    <t xml:space="preserve">Carrossel-resumo de artigo publicado: formato muito compartilhado entre profissionais de RH. Leva a autoridade do veículo para a marca, sem citar pessoas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FairJob; RH Pra Você (marcar o veículo, se fizer sentido)</t>
   </si>
   <si>
     <t xml:space="preserve">A NR-1 formalizou que o trabalho pode adoecer, e a empresa responde pelo ambiente que constrói. Mas saúde mental é multifatorial: é, ao mesmo tempo, de cada um e de todos.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fernando Brancaccio, "Riscos psicossociais no ambiente de trabalho e saúde", RH Pra Você, 25/09/2026. https://rhpravoce.com.br/colab/riscos-psicossociais-no-ambiente-de-trabalho-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirmar como creditar o Fernando (o artigo diz "fundador da FairJob"; aqui ele é cofundador da Fair Health). Peça é sobre a opinião publicada, não apresentação do time: sem foto dele, a menos que se decida o contrário. Conferir as citações literais com o artigo.</t>
+    <t xml:space="preserve">Artigo "Riscos psicossociais no ambiente de trabalho e saúde", RH Pra Você, 25/09/2026. https://rhpravoce.com.br/colab/riscos-psicossociais-no-ambiente-de-trabalho-2 Dado do slide 4: Global Burden of Disease (citado no artigo).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citar só o artigo (título e veículo), sem o nome do autor. Nenhum nome real de pessoa ou empresa no post (decisão de 09/10). Conferir as citações literais com o artigo. Número suave: cuidado primeiro, número como contexto, fonte visível e discreta (aba Ciência).</t>
   </si>
   <si>
     <t xml:space="preserve">O trabalho pode adoecer. Mas não é o único vilão.
 Desde maio de 2026, a NR-1 exige que as empresas identifiquem, avaliem e gerenciem os riscos psicossociais. É um avanço necessário: assédio, excesso de pressão, jornadas inadequadas e lideranças despreparadas têm impacto real na saúde mental.
-No artigo que publicou na RH Pra Você, nosso cofundador Fernando Brancaccio propõe ampliar o debate: ninguém começa a vida quando é contratado. Família, escola, comunidade e condições de vida chegam ao trabalho junto com a pessoa.
+Um artigo publicado na RH Pra Você propõe ampliar o debate: ninguém começa a vida quando é contratado. Família, escola, comunidade e condições de vida chegam ao trabalho junto com a pessoa.
 Isso não diminui a responsabilidade da empresa. Ela responde pelo ambiente que constrói. Mas não controla todas as variáveis.
 "Saúde mental é, ao mesmo tempo, de cada um e de todos."
 O artigo completo está no link dos stories. Concorda? Conta pra gente nos comentários.
@@ -601,13 +619,13 @@
   </si>
   <si>
     <t xml:space="preserve">8 slides.
-1 Capa: "O trabalho pode adoecer. Mas não é o único vilão." + selo "RH Pra Você".
+1 Capa: "O trabalho pode adoecer. Mas não é o único vilão." + "Da RH Pra Você".
 2 Desde maio de 2026, a NR-1 exige identificar, avaliar e gerenciar os riscos psicossociais.
 3 É um avanço necessário: ambientes tóxicos, assédio, excesso de pressão, jornadas inadequadas, insegurança e lideranças despreparadas adoecem.
-4 "Nenhuma pessoa começa sua vida quando é contratada por uma empresa."
+4 "Nenhuma pessoa começa sua vida quando é contratada por uma empresa." Abaixo, em texto menor: no mundo, quase 1 bilhão de pessoas convivem com algum transtorno mental (Global Burden of Disease, 2019).
 5 A empresa responde pelo ambiente que constrói. Não controla todas as variáveis.
 6 Responsabilidade compartilhada: poder público, sociedade, empresas e cada pessoa (sem culpar quem adoece).
-7 "Saúde mental é, ao mesmo tempo, de cada um e de todos." Fernando Brancaccio.
+7 "Saúde mental é, ao mesmo tempo, de cada um e de todos." (do artigo, sem nome)
 8 A parte da empresa começa antes: um cuidado dentro do trabalho, que começa com uma pergunta. Link nos stories.</t>
   </si>
   <si>
@@ -635,19 +653,19 @@
     <t xml:space="preserve">Explicador animado com ícones (motion): conceito novo explicado em 1 minuto, sem rosto. Responde ao mito "é só dieta e academia".</t>
   </si>
   <si>
-    <t xml:space="preserve">Os pilares não funcionam isoladamente: o plano olha para a pessoa inteira, a partir da rotina real.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACLM (American College of Lifestyle Medicine) e CBMEV (Colégio Brasileiro de Medicina do Estilo de Vida); cartilha do Escritório do Cuidado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Responsável médica valida a definição de MEV e os nomes dos pilares (6 ou 7: decidir antes de produzir).</t>
+    <t xml:space="preserve">Seis pilares, uma pessoa inteira: alimentação, atividade física, sono, manejo do estresse, relacionamentos e evitar substâncias de risco. O plano olha para todos, a partir da rotina real.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACLM (American College of Lifestyle Medicine), 6 pilares; CBMEV (Colégio Brasileiro de Medicina do Estilo de Vida); cartilha do Escritório do Cuidado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 pilares, sem espiritualidade (decisão de 09/10, ainda a confirmar). Responsável médica valida a definição de MEV e os nomes dos pilares.</t>
   </si>
   <si>
     <t xml:space="preserve">Reel de 45 a 60 s, motion com ícones, voz em off.
 0–3 s: "Medicina do Estilo de Vida é dieta e academia? Não só."
 3–10 s: definição curta, com fonte na tela.
-10–40 s: um ícone por pilar, uma frase por pilar.
+10–40 s: os 6 pilares, um ícone e uma frase por pilar: alimentação · atividade física · sono · manejo do estresse · relacionamentos · evitar substâncias de risco.
 40–50 s: "Os pilares conversam entre si: o plano olha para a pessoa inteira."
 50–60 s: "No Escritório do Cuidado, começa com uma pergunta." + logo.</t>
   </si>
@@ -758,19 +776,29 @@
     <t xml:space="preserve">Explicar como o plano é montado com a pessoa (decisão compartilhada)</t>
   </si>
   <si>
-    <t xml:space="preserve">Carrossel com card de interface (M3), já testado no carrossel de acolhimento: mostra o plano como algo concreto e possível.</t>
+    <t xml:space="preserve">Carrossel com card de interface (M3), já testado no carrossel de acolhimento, contado pela história de uma personagem fictícia: história prende mais que explicação e mostra o plano como algo possível.</t>
   </si>
   <si>
     <t xml:space="preserve">O plano parte do que é importante para você e da sua rotina real, com ações nos pilares da MEV, e muda quando a vida muda.</t>
   </si>
   <si>
-    <t xml:space="preserve">Responsável médica valida etapas e prazos. Nome único do plano: "Plano Individualizado de Cuidado" ou "Plano de Cuidado Personalizado"?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 slides: 1 capa "O plano é seu" · 2 começa pelo que é importante para você · 3 card do plano com 3 ações pequenas · 4 cabe na rotina real · 5 muda quando a vida muda · 6 alguém acompanha · 7 convite para comentar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modelo M3 (card de interface do plano).</t>
+    <t xml:space="preserve">Cartilha do Escritório do Cuidado. Personagem fictícia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsável médica valida etapas e prazos. Nome único do plano: "Plano Individualizado de Cuidado" ou "Plano de Cuidado Personalizado"? Indicar no slide e na legenda que é uma história ilustrativa (personagem fictícia), para não parecer depoimento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 slides, com a Clara (personagem fictícia, 41 anos, supervisora de turno).
+1 Capa: "O plano é seu."
+2 A Clara chegou dizendo: "Quero voltar a ter energia para brincar com meu filho." Isso é o que importa para ela.
+3 Card do plano da Clara: 3 ações pequenas (dormir 30 min mais cedo, caminhada de 10 min no almoço, conversa quinzenal com a psicóloga).
+4 Cabe na rotina real: no turno dela, não numa rotina ideal.
+5 Muda quando a vida muda.
+6 Alguém acompanha, sem julgamento.
+7 "E para você, o que é importante?" Rodapé: "História ilustrativa. Personagem fictícia."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modelo M3 (card de interface do plano). Sem foto de pessoa: a personagem aparece só no texto e no card.</t>
   </si>
   <si>
     <t xml:space="preserve">M1-09</t>
@@ -779,7 +807,7 @@
     <t xml:space="preserve">Adesão (número liberado)</t>
   </si>
   <si>
-    <t xml:space="preserve">Uma indústria, um semestre: 98% de adesão</t>
+    <t xml:space="preserve">Quando o cuidado está perto, as pessoas voltam</t>
   </si>
   <si>
     <t xml:space="preserve">RH; Diretoria financeira</t>
@@ -788,30 +816,30 @@
     <t xml:space="preserve">Programa de saúde que ninguém usa é custo. As pessoas usam isso de verdade?</t>
   </si>
   <si>
-    <t xml:space="preserve">Provar adesão com número liberado, sem argumento financeiro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dado animado com fonte: número grande, uma frase de contexto. É a prova que o RH leva para a diretoria.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No 1º semestre de 2026, numa indústria atendida: 161 atendimentos, 48 colaboradores atendidos (98% de adesão) e 81,3% voltaram para dois ou mais atendimentos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chemitec, 1º semestre de 2026 (número liberado, instagram/voice.md). Sempre agregado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decisão de 01/10 deixava números para depois da estreia: adesão não é retorno financeiro, mas confirmar se pode entrar no Mês 1. Citar a Chemitec pelo nome só com autorização (senão, "uma indústria").</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reel de 15 a 20 s, números animados.
-0–3 s: "As pessoas usam?"
-3–8 s: 98% (de adesão)
-8–13 s: 81,3% voltaram para dois ou mais atendimentos
-13–17 s: 161 atendimentos em um semestre
-17–20 s: fonte na tela + "Cuidado que as pessoas procuram." + logo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modelo M6 (dado com fonte) animado, um número por cena.</t>
+    <t xml:space="preserve">Provar adesão com número liberado, contado como cuidado e não como resultado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Número contado como história: primeiro a cena de cuidado, depois o número, em tom calmo. É a prova que o RH leva para a diretoria, sem cara de anúncio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quando o cuidado está perto e começa por uma conversa, as pessoas voltam: numa indústria atendida, 8 em cada 10 pessoas voltaram para mais de um atendimento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dados internos de um cliente do setor industrial, 1º semestre de 2026 (liberados; ver aba Fontes). Sempre agregado e sem o nome da empresa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nenhum nome real de pessoa ou empresa no post (decisão de 09/10). Usar "uma indústria". Número suave: cuidado primeiro, número como contexto, fonte visível e discreta (aba Ciência).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reel de 18 a 22 s, tipografia e números suaves.
+0–4 s: "Ninguém volta a um lugar onde não se sentiu cuidado."
+4–9 s: "Numa indústria que atendemos, no primeiro semestre de 2026..."
+9–14 s: "8 em cada 10 pessoas voltaram para mais de um atendimento." (número em destaque, sem exagero)
+14–18 s: em texto menor: "A adesão chegou a 98%."
+18–22 s: "Cuidado que as pessoas procuram." + fonte discreta + logo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modelo M6 (dado com fonte) animado, em ritmo lento. Número em verde-escuro, nunca em vermelho; sem setas para cima nem efeito de "conquista".</t>
   </si>
   <si>
     <t xml:space="preserve">M1-10</t>
@@ -868,10 +896,10 @@
     <t xml:space="preserve">O modelo nasceu em 2009, num hospital, para colocar o paciente no centro do cuidado. Hoje, coloca quem trabalha no centro, dentro da empresa.</t>
   </si>
   <si>
-    <t xml:space="preserve">Histórico do Escritório do Paciente (2009); caso Hospital Dia Santo Amaro (liberado).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[PENDENTE] Quem idealizou o Escritório do Paciente. Não usar "validado no SUS" até confirmar a fonte. Conferir datas.</t>
+    <t xml:space="preserve">Histórico do Escritório do Paciente (2009); caso do hospital onde o modelo começou (liberado; ver aba Fontes).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sem nomes de pessoas nem do hospital. Não usar "validado no SUS" até confirmar a fonte. Conferir datas.</t>
   </si>
   <si>
     <t xml:space="preserve">Reel de 25 a 30 s, linha do tempo em tipografia.
@@ -907,16 +935,16 @@
     <t xml:space="preserve">Card de citação: uma frase forte, fácil de compartilhar nos stories e no LinkedIn. Reaproveita o artigo sem repetir o carrossel.</t>
   </si>
   <si>
-    <t xml:space="preserve">FairJob; Fernando Brancaccio (se quiser)</t>
-  </si>
-  <si>
     <t xml:space="preserve">"Antes de perguntar apenas o que o trabalho está fazendo com a saúde mental das pessoas, deveríamos fazer uma pergunta maior: o que a nossa forma de viver em sociedade está fazendo com a saúde mental das pessoas?"</t>
   </si>
   <si>
-    <t xml:space="preserve">Citação literal conferida com o artigo. Crédito do Fernando como no post da semana 1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagem única: a pergunta em destaque, assinatura "Fernando Brancaccio, na RH Pra Você". Legenda curta que liga a pergunta à da marca ("o que é importante para você?") e convida a ler o artigo.</t>
+    <t xml:space="preserve">Artigo "Riscos psicossociais no ambiente de trabalho e saúde", RH Pra Você, 25/09/2026. https://rhpravoce.com.br/colab/riscos-psicossociais-no-ambiente-de-trabalho-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citação literal conferida com o artigo. Crédito só ao artigo e ao veículo, sem nome do autor. Nenhum nome real de pessoa ou empresa no post (decisão de 09/10).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagem única: a pergunta em destaque, assinatura "Do artigo 'Riscos psicossociais no ambiente de trabalho e saúde', RH Pra Você". Legenda curta que liga a pergunta à da marca ("o que é importante para você?") e convida a ler o artigo.</t>
   </si>
   <si>
     <t xml:space="preserve">Modelo M8 (citação), sem foto.</t>
@@ -946,19 +974,21 @@
     <t xml:space="preserve">Instagram</t>
   </si>
   <si>
-    <t xml:space="preserve">Dormir não é tempo perdido. No Escritório do Cuidado, o sono entra no plano a partir da sua rotina real.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guia "Saúde mental: o cuidado no dia a dia" (higiene do sono; OMS, APA, IPq-USP).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Responsável médica valida as orientações. Sem promessa clínica.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reel de 20 a 25 s.
+    <t xml:space="preserve">Dormir não é tempo perdido. A faixa saudável para adultos fica entre 7 e 9 horas por noite. No Escritório do Cuidado, o sono entra no plano a partir da sua rotina real.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guia "Saúde mental: o cuidado no dia a dia" (higiene do sono; OMS, APA, IPq-USP). Hafner M. et al. Why sleep matters: the economic costs of insufficient sleep. RAND Europe, 2016 (RR-1791). https://www.rand.org/news/press/2016/11/30.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsável médica valida as orientações. Sem promessa clínica. Número suave: cuidado primeiro, número como contexto, fonte visível e discreta (aba Ciência).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reel de 22 a 27 s.
 0–3 s: "Acorda cansado mesmo dormindo?"
-3–17 s: 3 hábitos, um por cena (tela antes de dormir, horário regular, cafeína à tarde).
-17–25 s: "Se o cansaço não passa, conversa com a gente no Escritório do Cuidado." + logo.</t>
+3–6 s: em texto calmo: "Para adultos, o sono saudável fica entre 7 e 9 horas." (fonte discreta: RAND Europe, 2016)
+6–19 s: 3 hábitos, um por cena (tela antes de dormir, horário regular, cafeína à tarde).
+19–27 s: "Se o cansaço não passa, conversa com a gente no Escritório do Cuidado." + logo.
+Legenda (opcional, para o RH no LinkedIn): um estudo da RAND Europe estimou que a falta de sono custa mais de 1 milhão de dias de trabalho por ano só nos Estados Unidos.</t>
   </si>
   <si>
     <t xml:space="preserve">Modelo M9 com etiqueta "PILARES · SONO". Imagens de banco (quarto, celular à noite), sem rosto identificável.</t>
@@ -967,37 +997,47 @@
     <t xml:space="preserve">M1-14</t>
   </si>
   <si>
-    <t xml:space="preserve">A pergunta</t>
+    <t xml:space="preserve">A pergunta (com a recomendação da OMS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciência no cuidado</t>
   </si>
   <si>
     <t xml:space="preserve">Uma pergunta que todo líder pode fazer</t>
   </si>
   <si>
-    <t xml:space="preserve">Lideranças; Colaboradores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como a liderança pode cuidar do time no dia a dia?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gerar conversa nos comentários e levar a pergunta da marca para a liderança</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Card de pergunta aberta: gera comentários e respostas nos stories (caixa de perguntas), o que ajuda o alcance das próximas peças.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"O que é importante para você?" é a pergunta que abre o nosso cuidado, e pode abrir uma conversa entre líder e time.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Posicionamento Fair Health v3.2 (a pergunta como modelo de liderança).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sem números.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagem única com a pergunta. Instagram: "Responde aqui: o que é importante para você hoje?". LinkedIn: "Líder, quando foi a última vez que você fez essa pergunta ao seu time?". Stories no mesmo dia com caixa de perguntas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modelo M1 (capa-pergunta) em versão de imagem única.</t>
+    <t xml:space="preserve">Lideranças; RH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como a liderança pode cuidar do time no dia a dia, sem ser médica nem psicóloga?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levar a pergunta da marca para a liderança, com o respaldo da recomendação da OMS, e gerar conversa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrossel de ciência aplicada: a recomendação de uma fonte respeitada (OMS) vira um gesto simples que o líder pode repetir. Fecha com pergunta aberta, que gera comentários.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A OMS recomenda preparar as lideranças para prevenir ambientes de estresse e acolher quem está em sofrimento. Um bom começo cabe numa pergunta: o que é importante para você?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OMS. Guidelines on mental health at work, 28/09/2022 (com a OIT: policy brief "Mental health at work"). https://www.who.int/news/item/28-09-2022-who-and-ilo-call-for-new-measures-to-tackle-mental-health-issues-at-work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conferir a redação da recomendação nas diretrizes da OMS. O líder não substitui o cuidado clínico: deixar claro onde pedir ajuda.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 slides.
+1 Capa: "Uma pergunta que todo líder pode fazer."
+2 Em 2022, a OMS publicou suas primeiras diretrizes sobre saúde mental no trabalho. Uma das recomendações: preparar as lideranças.
+3 Para quê? Para prevenir ambientes de estresse e acolher quem está em sofrimento.
+4 Não é virar terapeuta. É perguntar, ouvir e saber para onde encaminhar.
+5 Um bom começo: "O que é importante para você?"
+6 Líder, quando foi a última vez que você fez essa pergunta? Conta nos comentários. Fonte: OMS, 2022.
+Stories no mesmo dia com caixa de perguntas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modelo M1 na capa e M2 nos demais; fonte no rodapé (M6).</t>
   </si>
   <si>
     <t xml:space="preserve">M1-15</t>
@@ -1044,50 +1084,47 @@
     <t xml:space="preserve">M1-16</t>
   </si>
   <si>
-    <t xml:space="preserve">NR-1 e riscos psicossociais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ponte para o próximo mês (NR-1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antes de preencher a planilha: 5 perguntas sobre riscos psicossociais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RH; Medicina do Trabalho; Risco e Compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A NR-1 pede o mapeamento dos riscos psicossociais. Por onde eu começo de verdade?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ajudar o RH a olhar além do documento e abrir o tema do próximo mês</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checklist salvável: conteúdo útil que o RH guarda e repassa para a liderança. Fecha o mês e abre o capítulo NR-1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adequar-se à NR-1 não é só preencher a planilha de riscos. Se nada muda no dia a dia de quem trabalha, a pergunta continua sem resposta.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NR-1 (Ministério do Trabalho e Emprego), em vigor desde maio de 2026 segundo o artigo; Fernando Brancaccio, "Riscos psicossociais no ambiente de trabalho e saúde", RH Pra Você, 25/09/2026. https://rhpravoce.com.br/colab/riscos-psicossociais-no-ambiente-de-trabalho-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Texto da norma com fonte oficial. A mensagem usa a posição [SUGESTÃO] 1 do voice.md, que precisa de aprovação. Não prometer conformidade.</t>
+    <t xml:space="preserve">Ciência: estilo de vida e diabetes (Dia Mundial do Diabetes, 14/11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estilo de vida também é tratamento sério</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colaboradores; RH; Medicina do Trabalho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mudar hábitos faz diferença de verdade ou é só conselho?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mostrar a base científica da MEV com um estudo clássico, na véspera do Dia Mundial do Diabetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrossel "o que a ciência diz": um estudo, uma ideia, a fonte completa. Conecta uma data do calendário ao nosso trabalho com evidência, sem oportunismo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Num estudo clássico, publicado no New England Journal of Medicine, mudanças de estilo de vida reduziram em 58% os novos casos de diabetes tipo 2 em pessoas com risco, em comparação com o placebo. É por isso que o nosso cuidado começa pela rotina.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diabetes Prevention Program Research Group. Reduction in the incidence of type 2 diabetes with lifestyle intervention or metformin. N Engl J Med. 2002;346(6):393-403. doi:10.1056/NEJMoa012512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsável médica valida a leitura do estudo. Deixar claro que o estudo foi com adultos com pré-diabetes (risco aumentado) e que não é promessa individual. Número suave: cuidado primeiro, número como contexto, fonte visível e discreta (aba Ciência).</t>
   </si>
   <si>
     <t xml:space="preserve">7 slides.
-1 Capa: "Antes de preencher a planilha, responda 5 perguntas."
-2 Você sabe o que mais pesa no dia a dia do seu time?
-3 Suas lideranças sabem reconhecer os sinais?
-4 Quem está sendo cuidado hoje, e quem só aparece no atestado?
-5 Depois do diagnóstico, o que você vai acompanhar?
-6 Dentro da empresa, onde a pessoa pode pedir ajuda?
-7 "Salve e compartilhe com a sua liderança." Fonte da NR-1 no rodapé.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modelo M2 (uma pergunta por slide, etiqueta 1/5) com fonte no rodapé (M6).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formatos do mês: sem time em cena e sem gravar nas empresas-clientes</t>
+1 Capa: "Estilo de vida também é tratamento sério."
+2 Amanhã é o Dia Mundial do Diabetes. Vale lembrar de um estudo que mudou a forma de cuidar.
+3 Mais de 3 mil adultos com risco aumentado de diabetes tipo 2 foram acompanhados por quase 3 anos.
+4 Quem mudou a rotina (alimentação e 150 minutos de atividade física por semana) teve 58% menos casos novos do que o grupo placebo.
+5 Em texto menor: mais do que o grupo que recebeu medicamento (31%).
+6 Não é promessa: é a ciência dizendo que a rotina importa. Por isso o nosso cuidado começa nela, com um plano feito para cada pessoa.
+7 "O que é importante para você?" Fonte completa: Diabetes Prevention Program, N Engl J Med, 2002.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modelo M6 (dado com fonte) suave nos slides 4 e 5, M2 nos demais. Números em verde-escuro, sem destaque alarmista.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formatos do mês: sem time em cena, sem gravar nas empresas-clientes e sem nomes reais</t>
   </si>
   <si>
     <t xml:space="preserve">Como é</t>
@@ -1117,7 +1154,7 @@
     <t xml:space="preserve">Texto aprovado, Canva (animação de texto) ou CapCut. 1 a 2 horas.</t>
   </si>
   <si>
-    <t xml:space="preserve">Frases curtas; no máximo 6 cenas; logo só no fim.</t>
+    <t xml:space="preserve">Frases curtas; no máximo 7 cenas; logo só no fim.</t>
   </si>
   <si>
     <t xml:space="preserve">M1-03, M1-11</t>
@@ -1156,19 +1193,37 @@
     <t xml:space="preserve">Nunca dado real nem individual.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dado animado com fonte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Um número grande por cena, uma frase de contexto e a fonte visível.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número com fonte é a prova que o RH leva para a diretoria. Animado, segura a atenção.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Só números liberados (aba Fontes).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sempre agregado; nunca por pessoa; fonte na tela.</t>
+    <t xml:space="preserve">Número contado como história</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primeiro a cena de cuidado, depois o número, em ritmo lento e com a fonte discreta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O número prova sem tirar o foco do cuidado; o RH leva a prova para a diretoria sem cara de anúncio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Números liberados (aba Fontes) ou de estudos (aba Ciência).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sempre agregado; sem nome da empresa; regras de número suave (abaixo).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrossel "o que a ciência diz"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Um estudo por post: o que foi feito, o que encontrou, o que isso tem a ver com o nosso cuidado, e a referência completa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transfere a autoridade da ciência para a marca e educa sem prometer. Conecta datas do calendário ao trabalho sem oportunismo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estudo da aba Ciência, lido pela responsável médica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explicar para quem o estudo vale; nunca transformar em promessa individual.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1-14, M1-16</t>
   </si>
   <si>
     <t xml:space="preserve">Reel de dicas com imagem de banco</t>
@@ -1201,586 +1256,838 @@
     <t xml:space="preserve">Até 10 slides; uma ideia por slide.</t>
   </si>
   <si>
+    <t xml:space="preserve">M1-02, M1-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">História com personagem fictícia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uma personagem inventada (nome, idade, rotina) mostra como o cuidado funciona na prática.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">História prende mais que explicação e permite mostrar o plano sem expor ninguém.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personagem escrita com a responsável médica para ser plausível.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sinalizar "história ilustrativa, personagem fictícia" no post; nunca apresentar como depoimento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrossel-resumo de artigo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As ideias principais de um artigo publicado, com citações literais e link nos stories.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leva a autoridade do veículo para a marca; muito compartilhado entre profissionais de RH.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artigo publicado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citar só o artigo e o veículo, sem nome do autor; citações literais conferidas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrossel comparativo (isto × aquilo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duas colunas que contrastam duas ideias.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A diferença fica clara em segundos; ajuda o RH a defender a decisão internamente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modelo M1 e comparativo em duas colunas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não citar marcas de terceiros.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Card de citação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uma frase em destaque com assinatura.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fácil de compartilhar nos stories e no LinkedIn; reaproveita conteúdo sem repetir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modelo M8.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citação literal; crédito ao artigo, sem nome de pessoa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checklist salvável</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perguntas ou itens numerados, um por slide, com convite para salvar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conteúdo útil é salvo e repassado à liderança.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modelo M2 com etiqueta 1/5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonte oficial quando cita norma.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banco de ideias (NR-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Números com suavidade (decisão de 09/10: números sim, foco no cuidado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como fazer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exemplo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evitar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuidado primeiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A frase de cuidado abre; o número entra depois, como contexto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Ninguém volta a um lugar onde não se sentiu cuidado." → "8 em cada 10 voltaram."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abrir com o número como manchete.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Um número principal por peça</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Os outros números, se houver, vão em texto menor ou na legenda.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1-09: 8 em cada 10 em destaque; 98% em texto menor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Painel de números em sequência.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traduzir em gente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preferir "8 em cada 10 pessoas" a "81,3%"; arredondar com honestidade.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Mais de 470 mil licenças" em vez de "472.328".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casas decimais e jargão estatístico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom calmo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verde-escuro, ritmo lento, sem efeito de conquista.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Número em Raleway, peso médio, sem seta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vermelho, alarme, "explodiu", "recorde assustador".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonte sempre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fonte visível no rodapé e referência completa na aba Ciência ou Fontes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Fonte: OMS, 2022."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Número sem fonte ou "estudos mostram".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sem promessa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O número fala do estudo ou do grupo, nunca do resultado de quem vai ser atendido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"No estudo, 58% menos casos novos."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Você vai reduzir 58% do seu risco."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciência: estudos e fontes oficiais para posts (sempre com a referência completa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estudo ou fonte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referência completa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O que encontrou</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como apresentar com suavidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ligação com o nosso trabalho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diabetes Prevention Program (2002)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.234 adultos com pré-diabetes, acompanhados por 2,8 anos em média: mudança de estilo de vida (alimentação, 7% de perda de peso, 150 min de atividade física por semana) reduziu em 58% os casos novos de diabetes tipo 2 em relação ao placebo; a metformina reduziu 31%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Quem mudou a rotina teve 58% menos casos novos." O 31% do medicamento em texto menor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A base da Medicina do Estilo de Vida: o cuidado começa pela rotina.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vale para adultos com risco aumentado; não é promessa individual. Validação médica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OMS: diretrizes sobre saúde mental no trabalho (2022)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primeiras diretrizes da OMS sobre o tema. Recomenda, entre outras ações, preparar gestores para prevenir ambientes de estresse e acolher quem está em sofrimento. Com a OIT, estima que depressão e ansiedade custam cerca de 12 bilhões de dias de trabalho por ano no mundo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recomendação como gesto simples para o líder; os 12 bilhões de dias, se usados, em texto menor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liderança Bem-Estar e NR-1: preparar líderes e cuidar dentro da empresa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conferir a redação exata nas diretrizes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licenças por transtornos mentais no Brasil (2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ministério da Previdência Social: 472.328 licenças por transtornos mentais em 2024, maior número da série iniciada em 2014 (dados divulgados em 2025; conferir no painel oficial de dados abertos antes de publicar).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">472.328 licenças por transtornos mentais em 2024, o maior número da série iniciada em 2014. Ansiedade e depressão lideram.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Mais de 470 mil licenças. Cada uma teve um antes." Em texto calmo, depois da frase de cuidado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O eixo "cuidar antes".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Os números divulgados variam entre veículos (440 mil e 472 mil): conferir no painel oficial e citar a fonte primária.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why sleep matters (RAND Europe, 2016)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hafner M. et al. Why sleep matters: the economic costs of insufficient sleep. RAND Europe, 2016 (RR-1791). https://www.rand.org/news/press/2016/11/30.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sono insuficiente custa até 2,28% do PIB dos EUA e cerca de 1,2 milhão de dias de trabalho por ano; dormir menos de 6 horas está associado a risco de mortalidade 13% maior do que dormir de 7 a 9 horas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usar a faixa saudável (7 a 9 horas) para o colaborador; o custo em dias de trabalho só para o RH, na legenda do LinkedIn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilar sono.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimativas modeladas ("até"); evitar o dado de mortalidade em post para colaborador.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Burden of Disease 2019 (citado no artigo da RH Pra Você)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBD 2019 Mental Disorders Collaborators; artigo na Revista Brasileira de Epidemiologia (SciELO): https://www.scielo.br/j/rbepid/a/cwDkPDjSkDcC3hB73kp7yfC/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pessoas vivendo com 12 transtornos mentais em 204 países: de 654,8 milhões (1990) para 970,1 milhões (2019), +48,1%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Quase 1 bilhão de pessoas", em texto menor, como contexto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saúde mental é multifatorial; a empresa cuida da parte dela.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citar a fonte primária.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atividade física e saúde mental (Singh et al., 2023)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Singh B. et al. Effectiveness of physical activity interventions for improving depression, anxiety and distress: an overview of systematic reviews. Br J Sports Med. 2023. doi:10.1136/bjsports-2022-106195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisão de 97 revisões (1.039 estudos, mais de 128 mil participantes): atividade física teve efeito moderado na redução de sintomas de depressão, ansiedade e sofrimento psicológico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Mexer o corpo também cuida da mente", com o efeito descrito em palavras, sem número.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilar atividade física e manejo do estresse.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não usar o "1,5 vez melhor que remédio" da imprensa: não está no resumo do artigo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banco de ideias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relações sociais e mortalidade (Holt-Lunstad et al., 2010)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holt-Lunstad J., Smith T.B., Layton J.B. Social relationships and mortality risk: a meta-analytic review. PLoS Med. 2010;7(7):e1000316. doi:10.1371/journal.pmed.1000316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148 estudos, 308.849 participantes: relações sociais mais fortes associadas a maior chance de sobrevivência (razão de chances 1,50), efeito comparável a fatores de risco conhecidos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Vínculos também são saúde", sem o número na peça para colaborador.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilar relacionamentos; ambiente de trabalho.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evitar o "equivale a 15 cigarros por dia" da imprensa: não está no artigo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estressores no trabalho, mortalidade e custos (Goh, Pfeffer e Zenios, 2016)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goh J., Pfeffer J., Zenios S.A. The relationship between workplace stressors and mortality and health costs in the United States. Management Science. 2016;62(2):608-628. doi:10.1287/mnsc.2014.2115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modelo com 10 estressores do trabalho (jornadas longas, insegurança, baixa autonomia, conflito trabalho-família, entre outros) estima mais de 120 mil mortes por ano e de 5% a 8% dos gastos com saúde nos EUA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para o RH: "o jeito de trabalhar também entra na conta da saúde", número em texto menor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NR-1 e riscos psicossociais; Stop Loss.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conferir os números no artigo original antes de usar (vieram de resumos).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fontes internas, o artigo e o que não usar (nomes de clientes só para uso interno, nunca no post)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O que diz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como usar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Situação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artigo "Riscos psicossociais no ambiente de trabalho e saúde" (RH Pra Você, 25/09/2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desde maio de 2026 a NR-1 exige que as empresas identifiquem, avaliem e gerenciem os riscos psicossociais; o trabalho pode adoecer, mas não é o único vilão; a empresa responde pelo ambiente que constrói, mas não controla todas as variáveis; responsabilidade compartilhada (poder público, sociedade, empresas e indivíduo); "Saúde mental é, ao mesmo tempo, de cada um e de todos." URL: https://rhpravoce.com.br/colab/riscos-psicossociais-no-ambiente-de-trabalho-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resumo em carrossel, card de citação, link nos stories. Citar só o artigo e o veículo, sem nome do autor. Citações sempre literais.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publicado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1-04, M1-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cliente do setor industrial, 1º semestre de 2026 (uso interno: Chemitec)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161 atendimentos, 48 colaboradores atendidos (98% de adesão), 81,3% voltaram para 2 ou mais atendimentos, 46 smartbands em uso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sempre agregado e como "uma indústria". Nunca o nome da empresa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liberado (instagram/voice.md).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospital onde o modelo começou, 2025 (uso interno: Hospital Dia Santo Amaro)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reclamações mensais de 34 para cerca de 20 (cerca de 40% a menos); conformidade média de 98,2%; apresentado em congresso internacional.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">História de origem e prova do modelo, sem o nome do hospital.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harvard Business Review (2022) e SHRM (2023)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−28% de absenteísmo (HBR 2022); −22% de custos com saúde (SHRM 2023).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argumento de retorno, sempre com a fonte. Fica para o mês de Stop Loss.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACLM e CBMEV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Definição de Medicina do Estilo de Vida e seus 6 pilares: alimentação, atividade física, sono, manejo do estresse, relacionamentos e evitar substâncias de risco.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base do explicador de MEV.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsável médica confere. Espiritualidade fora (a confirmar).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não usar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"23% mais caro", "R$ 2.400 por colaborador", "maior índice de burnout" (sem fonte no posicionamento); −27%, "R$ 2,70 por R$ 1" e "70% dos custos do plano"; "validado no SUS" até confirmar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloqueado até ter fonte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banco de ideias: o que ficou para depois e os próximos meses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ideia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motivo / o que destrava</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Próximo uso sugerido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Série Quem cuida (apresentação de cada integrante do time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calendário de 90 dias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adiada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não vamos apresentar o time por agora (questão administrativa). As capas já feitas ficam guardadas em instagram/posts/time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quando a questão for resolvida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Um dia no Escritório do Cuidado (vídeo no espaço)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calendário de 90 dias (M1-03)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não podemos filmar clientes: o espaço fica dentro das empresas-clientes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recriar em local próprio ou em motion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bastidores de uma implantação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calendário de 90 dias (M2-01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesmo motivo: gravação dentro da empresa-cliente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Versão em motion, com empresa fictícia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depoimentos em vídeo e por escrito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calendário de 90 dias (M2-10, M3-03)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não podemos filmar clientes; nunca nomes; limites do CFM para depoimentos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trocar por histórias com personagem fictícia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Workshops nos pilares (fotos reais)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calendário de 90 dias (M1-06, M2-13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aguardando material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fotos de encontros expõem clientes. Possível versão só com materiais e slides do workshop.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mês de Ambiente positivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registro do mês</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aguardando pauta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depende da agenda de eventos e entregas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quando houver evento próprio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checklist "Antes de preencher a planilha: 5 perguntas sobre riscos psicossociais"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mês 1 (versão de 09/10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saiu do Mês 1 para dar lugar ao post de ciência do Dia Mundial do Diabetes. Abre bem o mês da NR-1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mês 2, semana 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Série NR-1 (contexto, diagnóstico, cuidado individualizado, acompanhamento, versão para colaboradores)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano mensal (Mês 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Próximo capítulo. O artigo da RH Pra Você já abre o tema. Estudo de Goh, Pfeffer e Zenios (aba Ciência) para o RH.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mês 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Série "Ciência no cuidado": um estudo por mês ligado ao pilar ou ao argumento do mês</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decisão de 09/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estudos na aba Ciência: atividade física e saúde mental (Singh, 2023), relações sociais (Holt-Lunstad, 2010), estressores do trabalho (Goh, 2016), OMS (12 bilhões de dias).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todo mês</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"O que nos diferencia": plano de saúde, plataformas de bem-estar e QVT (3 posts)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Posicionamento v3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falar da categoria, sem citar marcas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mês 2 ou 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Quem cuida também precisa de cuidado" (edição especial para a saúde)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Posicionamento v3.2 (arenas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liga a origem hospitalar ao cuidado de quem cuida.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mês 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilares da MEV, um por vez (alimentação, atividade física, manejo do estresse, relacionamentos, evitar substâncias de risco)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 pilares, sem espiritualidade (a confirmar). Sono já entra no Mês 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Um pilar por mês</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Histórias com personagens fictícias (um dia na rotina de quem é cuidado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sempre sinalizadas como ilustrativas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todo mês, 1 peça</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Case do hospital onde o modelo começou (sem o nome)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">voice.md (liberado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prova da origem do modelo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mês de Stop Loss ou de prova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicadores para o RH (HBR 2022, SHRM 2023)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argumento de retorno, um indicador por vez.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mês de Stop Loss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linhas editoriais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O que entra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Objetivos típicos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formatos que funcionam agora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peso no mês</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O que é a Fair Health, por que existe, de onde veio (Escritório do Paciente → Escritório do Cuidado, ecossistema FairJob) e em que acredita ("cuidar antes", "não é benefício, é infraestrutura de cuidado").</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apresentar, gerar confiança, fixar a tese.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipografia animada, linha do tempo, comparativo, card de pergunta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerca de 1/3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escritório do Cuidado (percurso, sigilo), Medicina do Estilo de Vida e os pilares, plano individualizado, tecnologia e temas do entorno (NR-1, saúde mental) quando a ligação com a oferta é clara.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explicar, educar com rigor, tirar dúvidas, levar à conversa comercial.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrossel passo a passo, explicador animado, checklist, dicas com imagem de banco.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerca de 1/3 a 2/5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O que a Fair Health está fazendo e entregando: números liberados, entregas para o RH, participações na imprensa e em eventos, como chega a uma empresa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provar, mostrar movimento, gerar autoridade.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dado animado, gravação de tela, resumo de artigo, card de citação.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerca de 1/4 a 1/3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personas (posicionamento v3.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quem é</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dor de entrada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como falar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHROs, gerentes de pessoas e business partners de empresas de médio e grande porte, principalmente indústria. Público principal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como atender à NR-1 de um jeito que mude algo? Meu programa tem adesão? O que eu recebo? Como começar?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assertivo e pragmático, com processo e evidência.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Números só liberados e com fonte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lideranças</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gestores e líderes de equipe.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como cuidar do time no dia a dia sem ser médico nem psicólogo?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direto, com perguntas práticas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não transferir ao líder a responsabilidade clínica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quem é ou pode ser atendido pelo Escritório do Cuidado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vou ser julgado? O que eu contar fica entre nós? Cabe na minha rotina?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acolhedor, em segunda pessoa, sem números de negócio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nunca expor quem é atendido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medicina do Trabalho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Médicos do trabalho e equipes de SST.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isso substitui ou complementa o que já fazemos?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Técnico, com fontes e precisão.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validação da responsável médica.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risco e Compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Áreas de risco, compliance e jurídico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como documentar e acompanhar os riscos psicossociais?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Objetivo, com a norma e a fonte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não prometer conformidade.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diretoria financeira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diretoria financeira.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qual o retorno? O que muda na sinistralidade?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicadores com fonte, sem promessa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argumento de retorno no mês de Stop Loss.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RI e C-Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C-Level e relações com investidores (ESG).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Como o cuidado aparece nos indicadores da empresa?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estratégico, curto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sem números sem fonte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pendências e validações</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pendência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quem confirma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pautas afetadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Questão administrativa que adia a apresentação do time: previsão para retomar a série Quem cuida.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sócios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aberta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onde gravar o vídeo de abertura sem time e sem empresa-cliente (local próprio ou neutro) ou montar com fotos e tipografia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comunicação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assistentes sociais fazem parte do atendimento? (o posicionamento cita médico e psicológico)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time Fair Health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nome da responsável médica que valida o conteúdo clínico e lê os estudos da aba Ciência.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todas as pautas com "responsável médica"; M1-13, M1-14, M1-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilares da MEV: 6 (ACLM), sem espiritualidade. Decisão de 09/10, ainda sem certeza.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsável médica + sócios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1-05 e série Pilares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conferir no painel oficial do Ministério da Previdência o número de licenças por transtornos mentais em 2024 (veículos divulgam 440 mil e 472 mil).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nome único do plano: Plano Individualizado de Cuidado ou Plano de Cuidado Personalizado (PPC).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Etapas e prazos clínicos: bioimpedância, smartband por 48 h, retorno.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsável médica</t>
+  </si>
+  <si>
     <t xml:space="preserve">M1-02, M1-08, M1-10</t>
   </si>
   <si>
-    <t xml:space="preserve">Carrossel-resumo de artigo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">As ideias principais de um artigo publicado, com citações literais e link nos stories.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leva a autoridade do veículo e do autor para a marca; muito compartilhado entre profissionais de RH.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Artigo publicado e crédito do autor aprovado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Citações literais conferidas; crédito do veículo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carrossel comparativo (isto × aquilo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duas colunas que contrastam duas ideias.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A diferença fica clara em segundos; ajuda o RH a defender a decisão internamente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modelo M1 e comparativo em duas colunas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não citar marcas de terceiros.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checklist salvável</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perguntas ou itens numerados, um por slide, com convite para salvar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conteúdo útil é salvo e repassado à liderança; abre o tema do mês seguinte.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modelo M2 com etiqueta 1/5.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fonte oficial quando cita norma.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Card de citação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uma frase em destaque com assinatura.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fácil de compartilhar nos stories e no LinkedIn; reaproveita conteúdo sem repetir.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modelo M8.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Citação literal e crédito.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Card de pergunta aberta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uma pergunta em destaque e convite para responder.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gera comentários e respostas nos stories; ajuda o alcance das próximas peças.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modelo M1 em imagem única + caixa de perguntas nos stories.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alguém precisa responder os comentários.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fontes e números</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O que diz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como usar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Situação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Artigo do cofundador na RH Pra Você (25/09/2026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fernando Brancaccio: desde maio de 2026 a NR-1 exige que as empresas identifiquem, avaliem e gerenciem os riscos psicossociais; o trabalho pode adoecer, mas não é o único vilão; a empresa responde pelo ambiente que constrói, mas não controla todas as variáveis; responsabilidade compartilhada (poder público, sociedade, empresas e indivíduo); "Saúde mental é, ao mesmo tempo, de cada um e de todos." URL: https://rhpravoce.com.br/colab/riscos-psicossociais-no-ambiente-de-trabalho-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resumo em carrossel, card de citação, link nos stories. Citações sempre literais.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Publicado. Confirmar o crédito do autor.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1-04, M1-12, M1-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Burden of Disease (citado no artigo, via SciELO / Revista Brasileira de Epidemiologia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pessoas vivendo com 12 transtornos mentais em 204 países: de 654,8 milhões (1990) para 970,1 milhões (2019), crescimento de 48,1%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[SUGESTÃO] Dado de contexto para o mês da NR-1, sempre com a fonte original.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não liberado: aprovar antes de usar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banco de ideias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chemitec (1º semestre de 2026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161 atendimentos, 48 colaboradores atendidos (98% de adesão), 81,3% voltaram para 2 ou mais atendimentos, 46 smartbands em uso.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sempre agregado. Nome da empresa só com autorização.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liberado (instagram/voice.md).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hospital Dia Santo Amaro (2025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reclamações mensais de 34 para cerca de 20 (cerca de 40% a menos); conformidade média de 98,2%; apresentado em congresso internacional.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">História de origem e prova do modelo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harvard Business Review (2022) e SHRM (2023)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">−28% de absenteísmo (HBR 2022); −22% de custos com saúde (SHRM 2023).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argumento de retorno, sempre com a fonte. Fica para o mês de Stop Loss.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACLM e CBMEV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Definição de Medicina do Estilo de Vida e seus pilares.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base do explicador de MEV.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Responsável médica confere.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não usar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"23% mais caro", "R$ 2.400 por colaborador", "maior índice de burnout" (sem fonte no posicionamento); −27%, "R$ 2,70 por R$ 1" e "70% dos custos do plano"; "validado no SUS" até confirmar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bloqueado até ter fonte.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banco de ideias: o que ficou para depois e os próximos meses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ideia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motivo / o que destrava</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Próximo uso sugerido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Série Quem cuida (Marília, Nina, Ronald, Floriana, Renata, Liliane, Fernando, Charles e o time junto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calendário de 90 dias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adiada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não vamos apresentar o time por agora (questão administrativa). As capas já feitas ficam guardadas em instagram/posts/time.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quando a questão for resolvida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Um dia no Escritório do Cuidado (vídeo no espaço)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calendário de 90 dias (M1-03)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não podemos filmar clientes: o espaço fica dentro das empresas-clientes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se houver autorização formal, ou recriar em local próprio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bastidores de uma implantação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calendário de 90 dias (M2-01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mesmo motivo: gravação dentro da empresa-cliente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Versão em motion, sem imagens da empresa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depoimentos em vídeo e por escrito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calendário de 90 dias (M2-10, M3-03)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não podemos filmar clientes; limites do CFM para depoimentos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depoimento escrito e anônimo, se aprovado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Workshops nos pilares (fotos reais)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calendário de 90 dias (M1-06, M2-13)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aguardando material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fotos de encontros expõem clientes. Possível versão só com materiais e slides do workshop.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mês de Ambiente positivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registro do mês</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aguardando pauta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depende da agenda de eventos e entregas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quando houver evento próprio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Série NR-1 (contexto, diagnóstico, cuidado individualizado, acompanhamento, versão para colaboradores)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano mensal (Mês 2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Próximo capítulo. O artigo do cofundador e o checklist M1-16 já abrem o tema.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mês 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"O que nos diferencia": plano de saúde, plataformas de bem-estar e QVT (3 posts)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Posicionamento v3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Falar da categoria, sem citar marcas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mês 2 ou 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Quem cuida também precisa de cuidado" (edição especial para a saúde)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Posicionamento v3.2 (arenas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liga a origem hospitalar ao cuidado de quem cuida.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mês 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pilares da MEV, um por vez (saúde mental e estresse, relações sociais, alimentação, propósito, atividade física, substâncias)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depende da decisão 6 ou 7 pilares.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Um pilar por mês</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Case Hospital Dia Santo Amaro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">voice.md (liberado)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prova da origem do modelo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mês de Stop Loss ou de prova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indicadores para o RH (HBR 2022, SHRM 2023)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argumento de retorno, um indicador por vez.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mês de Stop Loss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dia Mundial do Diabetes (14/11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stories sobre alimentação e atividade física, com a responsável médica.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stories de 14/11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linhas editoriais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O que entra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Objetivos típicos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formatos que funcionam agora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peso no mês</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O que é a Fair Health, por que existe, de onde veio (Escritório do Paciente → Escritório do Cuidado, ecossistema FairJob) e em que acredita ("cuidar antes", "não é benefício, é infraestrutura de cuidado").</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apresentar, gerar confiança, fixar a tese.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipografia animada, linha do tempo, comparativo, card de pergunta.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerca de 1/3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Escritório do Cuidado (percurso, sigilo), Medicina do Estilo de Vida e os pilares, plano individualizado, tecnologia e temas do entorno (NR-1, saúde mental) quando a ligação com a oferta é clara.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Explicar, educar com rigor, tirar dúvidas, levar à conversa comercial.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carrossel passo a passo, explicador animado, checklist, dicas com imagem de banco.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerca de 1/3 a 2/5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O que a Fair Health está fazendo e entregando: números liberados, entregas para o RH, participações na imprensa e em eventos, como chega a uma empresa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Provar, mostrar movimento, gerar autoridade.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dado animado, gravação de tela, resumo de artigo, card de citação.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerca de 1/4 a 1/3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personas (posicionamento v3.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quem é</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dor de entrada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como falar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHROs, gerentes de pessoas e business partners de empresas de médio e grande porte, principalmente indústria. Público principal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como atender à NR-1 de um jeito que mude algo? Meu programa tem adesão? O que eu recebo? Como começar?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assertivo e pragmático, com processo e evidência.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Números só liberados e com fonte.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lideranças</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gestores e líderes de equipe.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como cuidar do time no dia a dia sem ser médico nem psicólogo?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direto, com perguntas práticas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não transferir ao líder a responsabilidade clínica.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quem é ou pode ser atendido pelo Escritório do Cuidado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vou ser julgado? O que eu contar fica entre nós? Cabe na minha rotina?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acolhedor, em segunda pessoa, sem números de negócio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nunca expor quem é atendido.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medicina do Trabalho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Médicos do trabalho e equipes de SST.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isso substitui ou complementa o que já fazemos?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Técnico, com fontes e precisão.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validação da responsável médica.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Risco e Compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Áreas de risco, compliance e jurídico.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como documentar e acompanhar os riscos psicossociais?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Objetivo, com a norma e a fonte.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não prometer conformidade.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretoria financeira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diretoria financeira.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qual o retorno? O que muda na sinistralidade?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indicadores com fonte, sem promessa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argumento de retorno no mês de Stop Loss.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RI e C-Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C-Level e relações com investidores (ESG).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Como o cuidado aparece nos indicadores da empresa?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estratégico, curto.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sem números sem fonte.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pendências e validações</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pendência</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quem confirma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pautas afetadas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Questão administrativa que adia a apresentação do time: previsão para retomar a série Quem cuida.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sócios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aberta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crédito do Fernando Brancaccio nos posts (cofundador da Fair Health? fundador da FairJob?) e se ele quer ser marcado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fernando + Comunicação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1-04, M1-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Onde gravar o vídeo de abertura sem time e sem empresa-cliente (local próprio ou neutro) ou montar com fotos e tipografia.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comunicação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assistentes sociais fazem parte do atendimento? (o posicionamento cita médico e psicológico)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time Fair Health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nome da responsável médica que valida o conteúdo clínico.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Todas as pautas com "responsável médica"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 ou 7 pilares da MEV.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Responsável médica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1-05 e série Pilares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nome único do plano: Plano Individualizado de Cuidado ou Plano de Cuidado Personalizado (PPC).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Etapas e prazos clínicos: bioimpedância, smartband por 48 h, retorno.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Número da Chemitec já no Mês 1 (decisão de 01/10 deixava números para depois da estreia) e autorização para citar o nome.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sócios + Chemitec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quem idealizou o Escritório do Paciente; fonte de "validado no SUS".</t>
+    <t xml:space="preserve">Fonte de "validado no SUS" e datas da história de origem.</t>
   </si>
   <si>
     <t xml:space="preserve">Indicadores que entram no relatório do RH (fairdata).</t>
@@ -1789,31 +2096,43 @@
     <t xml:space="preserve">Time Fair Health + fairdata</t>
   </si>
   <si>
+    <t xml:space="preserve">Collab no Instagram e LinkedIn pela FairJob: quem publica, quem aceita o convite.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comunicação + FairJob</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todas as pautas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destino do link e da chamada CUIDADO (www.fairhealth.com.br) e quem responde comentários e DMs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1-06, M1-15</t>
+  </si>
+  <si>
     <t xml:space="preserve">Texto, prazos e obrigações da NR-1 com fonte oficial; aprovação da posição [SUGESTÃO] 1 do voice.md.</t>
   </si>
   <si>
-    <t xml:space="preserve">Responsável médica + sócios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collab no Instagram e LinkedIn pela FairJob: quem publica, quem aceita o convite.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comunicação + FairJob</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Todas as pautas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Destino do link e da chamada CUIDADO (www.fairhealth.com.br) e quem responde comentários e DMs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M1-06, M1-15</t>
+    <t xml:space="preserve">Banco de ideias (checklist NR-1)</t>
   </si>
   <si>
     <t xml:space="preserve">Fontes dos números do posicionamento (23%, R$ 2.400, burnout).</t>
   </si>
   <si>
     <t xml:space="preserve">Fontes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crédito do autor do artigo da RH Pra Você.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolvida em 09/10: citar só o artigo e o veículo, sem nome.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Números no Mês 1 e nome do cliente industrial.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolvida em 09/10: números sim, com suavidade; nunca o nome do cliente.</t>
   </si>
   <si>
     <t xml:space="preserve">Instagram Stories</t>
@@ -2516,7 +2835,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:A41"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="140"/>
@@ -2573,30 +2892,30 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
     </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2"/>
+    </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
@@ -2607,38 +2926,38 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2"/>
+      <c r="A19" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>15</v>
+      <c r="A20" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="A21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2"/>
+      <c r="A23" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
-        <v>18</v>
+      <c r="A24" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="A25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2648,33 +2967,33 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2"/>
+      <c r="A28" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+      <c r="A29" s="2" t="s">
         <v>23</v>
       </c>
     </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2"/>
+    </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
+      <c r="A31" s="3" t="s">
         <v>24</v>
       </c>
     </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="A33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2696,6 +3015,262 @@
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="0" width="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>503</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>539</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>660</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>551</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="13" t="s">
+        <v>661</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>662</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>525</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>663</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D6" s="13" t="s">
+        <v>529</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>664</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D7" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>665</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D8" s="13" t="s">
+        <v>666</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>667</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D9" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D10" s="13" t="s">
+        <v>669</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D11" s="13" t="s">
+        <v>671</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D12" s="13" t="s">
+        <v>673</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D13" s="13" t="s">
+        <v>675</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D14" s="13" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D15" s="13" t="s">
+        <v>508</v>
       </c>
     </row>
   </sheetData>
@@ -2714,7 +3289,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -2728,20 +3303,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -2752,7 +3327,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B5" s="7" t="str">
         <f aca="false">TEXT(Calendário!$D$2,"DD/MM")&amp;" a "&amp;TEXT(Calendário!$D$2+27,"DD/MM")</f>
@@ -2767,10 +3342,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -2781,10 +3356,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -2795,10 +3370,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -2809,10 +3384,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2821,12 +3396,12 @@
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -2835,12 +3410,12 @@
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2849,86 +3424,66 @@
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
-        <v>48</v>
-      </c>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="9" t="s">
+      <c r="A14" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F14" s="9" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="B15" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="C15" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="D15" s="9" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="n">
+      <c r="E15" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <f aca="false">COUNTIFS(Calendário!$C$5:$C$400,$A15)</f>
-        <v>4</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <f aca="false">COUNTIFS(Calendário!$C$5:$C$400,$A15,Calendário!$N$5:$N$400,"Vídeo")</f>
-        <v>2</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <f aca="false">COUNTIFS(Calendário!$C$5:$C$400,$A15,Calendário!$E$5:$E$400,"Institucional")</f>
-        <v>2</v>
-      </c>
-      <c r="H15" s="7" t="n">
-        <f aca="false">COUNTIFS(Calendário!$C$5:$C$400,$A15,Calendário!$E$5:$E$400,"Produto")</f>
-        <v>1</v>
-      </c>
-      <c r="I15" s="7" t="n">
-        <f aca="false">COUNTIFS(Calendário!$C$5:$C$400,$A15,Calendário!$E$5:$E$400,"Projetos, eventos e entregas")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="n">
-        <v>2</v>
-      </c>
       <c r="B16" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E16" s="7" t="n">
         <f aca="false">COUNTIFS(Calendário!$C$5:$C$400,$A16)</f>
@@ -2940,29 +3495,29 @@
       </c>
       <c r="G16" s="7" t="n">
         <f aca="false">COUNTIFS(Calendário!$C$5:$C$400,$A16,Calendário!$E$5:$E$400,"Institucional")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="7" t="n">
         <f aca="false">COUNTIFS(Calendário!$C$5:$C$400,$A16,Calendário!$E$5:$E$400,"Produto")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" s="7" t="n">
         <f aca="false">COUNTIFS(Calendário!$C$5:$C$400,$A16,Calendário!$E$5:$E$400,"Projetos, eventos e entregas")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E17" s="7" t="n">
         <f aca="false">COUNTIFS(Calendário!$C$5:$C$400,$A17)</f>
@@ -2978,25 +3533,25 @@
       </c>
       <c r="H17" s="7" t="n">
         <f aca="false">COUNTIFS(Calendário!$C$5:$C$400,$A17,Calendário!$E$5:$E$400,"Produto")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" s="7" t="n">
         <f aca="false">COUNTIFS(Calendário!$C$5:$C$400,$A17,Calendário!$E$5:$E$400,"Projetos, eventos e entregas")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E18" s="7" t="n">
         <f aca="false">COUNTIFS(Calendário!$C$5:$C$400,$A18)</f>
@@ -3012,122 +3567,140 @@
       </c>
       <c r="H18" s="7" t="n">
         <f aca="false">COUNTIFS(Calendário!$C$5:$C$400,$A18,Calendário!$E$5:$E$400,"Produto")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" s="7" t="n">
         <f aca="false">COUNTIFS(Calendário!$C$5:$C$400,$A18,Calendário!$E$5:$E$400,"Projetos, eventos e entregas")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <f aca="false">COUNTIFS(Calendário!$C$5:$C$400,$A19)</f>
+        <v>4</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <f aca="false">COUNTIFS(Calendário!$C$5:$C$400,$A19,Calendário!$N$5:$N$400,"Vídeo")</f>
+        <v>2</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <f aca="false">COUNTIFS(Calendário!$C$5:$C$400,$A19,Calendário!$E$5:$E$400,"Institucional")</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="11" t="n">
-        <f aca="false">SUM(E15:E18)</f>
+      <c r="H19" s="7" t="n">
+        <f aca="false">COUNTIFS(Calendário!$C$5:$C$400,$A19,Calendário!$E$5:$E$400,"Produto")</f>
+        <v>2</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <f aca="false">COUNTIFS(Calendário!$C$5:$C$400,$A19,Calendário!$E$5:$E$400,"Projetos, eventos e entregas")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <f aca="false">SUM(E16:E19)</f>
         <v>16</v>
       </c>
-      <c r="F19" s="11" t="n">
-        <f aca="false">SUM(F15:F18)</f>
+      <c r="F20" s="11" t="n">
+        <f aca="false">SUM(F16:F19)</f>
         <v>8</v>
       </c>
-      <c r="G19" s="11" t="n">
-        <f aca="false">SUM(G15:G18)</f>
+      <c r="G20" s="11" t="n">
+        <f aca="false">SUM(G16:G19)</f>
         <v>5</v>
       </c>
-      <c r="H19" s="11" t="n">
-        <f aca="false">SUM(H15:H18)</f>
+      <c r="H20" s="11" t="n">
+        <f aca="false">SUM(H16:H19)</f>
         <v>6</v>
       </c>
-      <c r="I19" s="11" t="n">
-        <f aca="false">SUM(I15:I18)</f>
+      <c r="I20" s="11" t="n">
+        <f aca="false">SUM(I16:I19)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
-        <v>70</v>
-      </c>
-    </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>73</v>
+      <c r="A22" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B23" s="13" t="n">
-        <f aca="false">COUNTIFS(Calendário!$F$5:$F$400,$A23)</f>
-        <v>6</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E23" s="13" t="n">
-        <f aca="false">COUNTIFS(Calendário!$G$5:$G$400,$D23)</f>
-        <v>2</v>
-      </c>
-      <c r="G23" s="13" t="n">
-        <f aca="false">SUMPRODUCT((Calendário!$B$5:$B$400&lt;&gt;"")*ISNUMBER(SEARCH("responsável médica",Calendário!$T$5:$T$400)))</f>
-        <v>4</v>
+      <c r="A23" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B24" s="13" t="n">
         <f aca="false">COUNTIFS(Calendário!$F$5:$F$400,$A24)</f>
         <v>6</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E24" s="13" t="n">
         <f aca="false">COUNTIFS(Calendário!$G$5:$G$400,$D24)</f>
         <v>2</v>
       </c>
+      <c r="G24" s="13" t="n">
+        <f aca="false">SUMPRODUCT((Calendário!$B$5:$B$400&lt;&gt;"")*ISNUMBER(SEARCH("responsável médica",Calendário!$T$5:$T$400)))</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B25" s="13" t="n">
         <f aca="false">COUNTIFS(Calendário!$F$5:$F$400,$A25)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="E25" s="13" t="n">
         <f aca="false">COUNTIFS(Calendário!$G$5:$G$400,$D25)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B26" s="13" t="n">
         <f aca="false">COUNTIFS(Calendário!$F$5:$F$400,$A26)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E26" s="13" t="n">
         <f aca="false">COUNTIFS(Calendário!$G$5:$G$400,$D26)</f>
@@ -3136,14 +3709,14 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B27" s="13" t="n">
         <f aca="false">COUNTIFS(Calendário!$F$5:$F$400,$A27)</f>
         <v>0</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E27" s="13" t="n">
         <f aca="false">COUNTIFS(Calendário!$G$5:$G$400,$D27)</f>
@@ -3152,15 +3725,31 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B28" s="13" t="n">
         <f aca="false">COUNTIFS(Calendário!$F$5:$F$400,$A28)</f>
         <v>0</v>
       </c>
+      <c r="D28" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <f aca="false">COUNTIFS(Calendário!$G$5:$G$400,$D28)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="13" t="n">
+        <f aca="false">COUNTIFS(Calendário!$F$5:$F$400,$A29)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="B6:H6"/>
@@ -3169,6 +3758,7 @@
     <mergeCell ref="B9:H9"/>
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B12:H12"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3214,12 +3804,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -3227,95 +3817,95 @@
         <v>46314</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="P4" s="9" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="Q4" s="9" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="R4" s="9" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="S4" s="9" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="U4" s="9" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="V4" s="9" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="W4" s="9" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="X4" s="9" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="Y4" s="9" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="Z4" s="9" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>1</v>
@@ -3325,74 +3915,74 @@
         <v>46314</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="7" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R5" s="7" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="S5" s="7" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="T5" s="7" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="U5" s="7" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="V5" s="7" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="W5" s="7" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="X5" s="7" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="Y5" s="7"/>
       <c r="Z5" s="7" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="202.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>1</v>
@@ -3402,76 +3992,76 @@
         <v>46315</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R6" s="7" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="S6" s="7" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="T6" s="7" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="V6" s="7" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="W6" s="7" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="X6" s="7" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="Y6" s="7"/>
       <c r="Z6" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="202.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>1</v>
@@ -3481,72 +4071,72 @@
         <v>46317</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R7" s="7" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="S7" s="7" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="T7" s="7" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="U7" s="7" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="V7" s="7" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="W7" s="7" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="X7" s="7" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="Y7" s="7"/>
       <c r="Z7" s="7"/>
     </row>
-    <row r="8" customFormat="false" ht="236.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="225.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>1</v>
@@ -3556,74 +4146,74 @@
         <v>46318</v>
       </c>
       <c r="E8" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="R8" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="S8" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="T8" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="U8" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="P8" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q8" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="R8" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="S8" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="T8" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="U8" s="7" t="s">
-        <v>152</v>
-      </c>
       <c r="V8" s="7" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="W8" s="7" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="X8" s="7" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="Y8" s="7"/>
       <c r="Z8" s="7"/>
     </row>
-    <row r="9" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>2</v>
@@ -3633,72 +4223,72 @@
         <v>46321</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R9" s="7" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="S9" s="7" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="U9" s="7" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="V9" s="7"/>
       <c r="W9" s="7" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="X9" s="7" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="Y9" s="7"/>
       <c r="Z9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>2</v>
@@ -3708,70 +4298,70 @@
         <v>46322</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R10" s="7" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="S10" s="7" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="T10" s="7" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="U10" s="7" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="V10" s="7"/>
       <c r="W10" s="7" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="X10" s="7" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="Y10" s="7"/>
       <c r="Z10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>2</v>
@@ -3781,72 +4371,72 @@
         <v>46324</v>
       </c>
       <c r="E11" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="R11" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="S11" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="T11" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="U11" s="7" t="s">
         <v>157</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="P11" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q11" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="R11" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="S11" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="T11" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="U11" s="7" t="s">
-        <v>152</v>
       </c>
       <c r="V11" s="7"/>
       <c r="W11" s="7" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="Y11" s="7"/>
       <c r="Z11" s="7"/>
     </row>
-    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>2</v>
@@ -3856,72 +4446,72 @@
         <v>46325</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="P12" s="7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R12" s="7" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="S12" s="7" t="s">
-        <v>135</v>
+        <v>222</v>
       </c>
       <c r="T12" s="7" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="U12" s="7" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="V12" s="7"/>
       <c r="W12" s="7" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="X12" s="7" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="Y12" s="7"/>
       <c r="Z12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>3</v>
@@ -3931,70 +4521,70 @@
         <v>46329</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="I13" s="7"/>
       <c r="J13" s="7" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="S13" s="7" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="U13" s="7" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="V13" s="7"/>
       <c r="W13" s="7" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="X13" s="7" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="Y13" s="7"/>
       <c r="Z13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>3</v>
@@ -4004,70 +4594,70 @@
         <v>46330</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="U14" s="7" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="V14" s="7"/>
       <c r="W14" s="7"/>
       <c r="X14" s="7" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="Y14" s="7"/>
       <c r="Z14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>3</v>
@@ -4077,70 +4667,70 @@
         <v>46331</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="7" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="U15" s="7" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="V15" s="7"/>
       <c r="W15" s="7" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="X15" s="7" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="Y15" s="7"/>
       <c r="Z15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>3</v>
@@ -4150,72 +4740,72 @@
         <v>46332</v>
       </c>
       <c r="E16" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="R16" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="S16" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="T16" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="U16" s="7" t="s">
         <v>157</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="L16" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="N16" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="O16" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="P16" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q16" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="R16" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="S16" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="T16" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="U16" s="7" t="s">
-        <v>152</v>
       </c>
       <c r="V16" s="7"/>
       <c r="W16" s="7" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="X16" s="7" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="Y16" s="7"/>
       <c r="Z16" s="7"/>
     </row>
-    <row r="17" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>4</v>
@@ -4225,72 +4815,72 @@
         <v>46335</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="P17" s="7" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R17" s="7" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="T17" s="7" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="U17" s="7" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="V17" s="7"/>
       <c r="W17" s="7" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="X17" s="7" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="Y17" s="7"/>
       <c r="Z17" s="7"/>
     </row>
-    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>4</v>
@@ -4300,70 +4890,72 @@
         <v>46336</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="I18" s="7"/>
+        <v>286</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>287</v>
+      </c>
       <c r="J18" s="7" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>259</v>
+        <v>137</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="P18" s="7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="R18" s="7" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="T18" s="7" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="U18" s="7" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="V18" s="7"/>
       <c r="W18" s="7" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="X18" s="7" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="Y18" s="7"/>
       <c r="Z18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>4</v>
@@ -4373,72 +4965,72 @@
         <v>46338</v>
       </c>
       <c r="E19" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="R19" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="S19" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="T19" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="U19" s="7" t="s">
         <v>157</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="N19" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="O19" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="P19" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q19" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="R19" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="S19" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="T19" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="U19" s="7" t="s">
-        <v>152</v>
       </c>
       <c r="V19" s="7"/>
       <c r="W19" s="7" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="X19" s="7" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="Y19" s="7"/>
       <c r="Z19" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C20" s="7" t="n">
         <v>4</v>
@@ -4448,62 +5040,62 @@
         <v>46339</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="O20" s="7" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="P20" s="7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>203</v>
+        <v>121</v>
       </c>
       <c r="R20" s="7" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="T20" s="7" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="U20" s="7" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="V20" s="7"/>
       <c r="W20" s="7" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="X20" s="7" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="Y20" s="7"/>
       <c r="Z20" s="7"/>
@@ -4593,7 +5185,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -4604,248 +5196,385 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>266</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>354</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>156</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>303</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>254</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>279</v>
-      </c>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4863,154 +5592,227 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>380</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>99</v>
+        <v>423</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>381</v>
+        <v>424</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>382</v>
+        <v>425</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>383</v>
+        <v>426</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>427</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>384</v>
+        <v>428</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>385</v>
+        <v>318</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>386</v>
+        <v>429</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>387</v>
+        <v>430</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>431</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>389</v>
+        <v>433</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>390</v>
+        <v>294</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>391</v>
+        <v>434</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>392</v>
+        <v>435</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>436</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>394</v>
+        <v>438</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>395</v>
+        <v>439</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>396</v>
+        <v>440</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>397</v>
+        <v>441</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>442</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>398</v>
+        <v>444</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>399</v>
+        <v>445</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>400</v>
+        <v>446</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>397</v>
+        <v>447</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>448</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>401</v>
+        <v>450</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>402</v>
+        <v>451</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>403</v>
+        <v>452</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>397</v>
+        <v>453</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>454</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>404</v>
+        <v>456</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>405</v>
+        <v>457</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>406</v>
+        <v>458</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>407</v>
+        <v>459</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>172</v>
+        <v>460</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>408</v>
+        <v>463</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>409</v>
+        <v>464</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>410</v>
+        <v>465</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>411</v>
+        <v>466</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>410</v>
+        <v>467</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -5029,257 +5831,137 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>412</v>
+        <v>475</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>413</v>
+        <v>104</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>243</v>
+        <v>476</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>101</v>
+        <v>477</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>414</v>
+        <v>478</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>416</v>
+        <v>479</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>417</v>
+        <v>480</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>418</v>
+        <v>481</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>419</v>
+        <v>482</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>420</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>421</v>
+        <v>484</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>422</v>
+        <v>485</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>418</v>
+        <v>486</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>423</v>
+        <v>487</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>425</v>
+        <v>488</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>426</v>
+        <v>489</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>418</v>
+        <v>490</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>427</v>
+        <v>487</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>429</v>
+        <v>491</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>430</v>
+        <v>492</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>418</v>
+        <v>493</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>431</v>
+        <v>487</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>432</v>
+        <v>462</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>433</v>
+        <v>494</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>434</v>
+        <v>495</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>435</v>
+        <v>496</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>436</v>
+        <v>497</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>438</v>
+        <v>498</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>417</v>
+        <v>499</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>439</v>
+        <v>500</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>440</v>
+        <v>501</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>452</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>454</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>457</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>462</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>464</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>466</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -5298,227 +5980,291 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>467</v>
+        <v>502</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>468</v>
+        <v>503</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>469</v>
+        <v>249</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>470</v>
+        <v>106</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>471</v>
+        <v>504</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>55</v>
+        <v>506</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>473</v>
+        <v>507</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>474</v>
+        <v>508</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>475</v>
+        <v>509</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>56</v>
+        <v>511</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>477</v>
+        <v>512</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>478</v>
+        <v>508</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>479</v>
+        <v>513</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>157</v>
+        <v>515</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>481</v>
+        <v>516</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>482</v>
+        <v>508</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>483</v>
+        <v>517</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>485</v>
+        <v>518</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>524</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>526</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>486</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>487</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>320</v>
+      <c r="A8" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>489</v>
+        <v>532</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>490</v>
+        <v>533</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>492</v>
+        <v>534</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>494</v>
+        <v>536</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>495</v>
+        <v>537</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>497</v>
+        <v>538</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>129</v>
+        <v>540</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>499</v>
+        <v>541</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>501</v>
+        <v>542</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>503</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>505</v>
-      </c>
       <c r="D12" s="7" t="s">
-        <v>506</v>
+        <v>546</v>
       </c>
       <c r="E12" s="7" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>509</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>511</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>513</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>514</v>
-      </c>
       <c r="C14" s="7" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>516</v>
+        <v>553</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>518</v>
+        <v>555</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>519</v>
+        <v>541</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>521</v>
+        <v>556</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>522</v>
+        <v>557</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>558</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>564</v>
       </c>
     </row>
   </sheetData>
@@ -5537,291 +6283,227 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>523</v>
+        <v>565</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>524</v>
+        <v>566</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>525</v>
+        <v>567</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>526</v>
+        <v>568</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>527</v>
+        <v>569</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="n">
-        <v>1</v>
+        <v>570</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
+        <v>60</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>528</v>
+        <v>571</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>529</v>
+        <v>572</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>393</v>
+        <v>573</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="n">
-        <v>2</v>
+        <v>574</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>531</v>
+        <v>575</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>532</v>
+        <v>576</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>533</v>
+        <v>577</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
-        <v>3</v>
+        <v>578</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>534</v>
+        <v>579</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>535</v>
+        <v>580</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>107</v>
+        <v>581</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>530</v>
+        <v>582</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>538</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>539</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>530</v>
+      <c r="A7" s="8" t="s">
+        <v>583</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>530</v>
+      <c r="A8" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>586</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
-        <v>7</v>
+      <c r="A9" s="7" t="s">
+        <v>587</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>543</v>
+        <v>588</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>529</v>
+        <v>589</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>209</v>
+        <v>590</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>530</v>
+        <v>591</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
-        <v>8</v>
+      <c r="A10" s="7" t="s">
+        <v>592</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>544</v>
+        <v>593</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>541</v>
+        <v>594</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>354</v>
+        <v>595</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>530</v>
+        <v>596</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
-        <v>9</v>
+      <c r="A11" s="7" t="s">
+        <v>134</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>545</v>
+        <v>597</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>546</v>
+        <v>598</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>220</v>
+        <v>599</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>530</v>
+        <v>600</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
-        <v>10</v>
+      <c r="A12" s="7" t="s">
+        <v>601</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>547</v>
+        <v>602</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>537</v>
+        <v>603</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>242</v>
+        <v>604</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>530</v>
+        <v>605</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="n">
-        <v>11</v>
+      <c r="A13" s="7" t="s">
+        <v>606</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>548</v>
+        <v>607</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>549</v>
+        <v>608</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>195</v>
+        <v>609</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="n">
-        <v>12</v>
+        <v>610</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>611</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>550</v>
+        <v>612</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>551</v>
+        <v>613</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>303</v>
+        <v>614</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>530</v>
+        <v>615</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="n">
-        <v>13</v>
+      <c r="A15" s="7" t="s">
+        <v>616</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>552</v>
+        <v>617</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>553</v>
+        <v>618</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>554</v>
+        <v>619</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>555</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>556</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>557</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>529</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>558</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>530</v>
+        <v>620</v>
       </c>
     </row>
   </sheetData>
@@ -5840,229 +6522,308 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H1" s="17" t="s">
-        <v>91</v>
+      <c r="A1" s="8" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>413</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>559</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>560</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>453</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="13" t="s">
-        <v>561</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>562</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>435</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>563</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="H5" s="13" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D6" s="13" t="s">
-        <v>439</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>564</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>508</v>
+      <c r="A2" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>623</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>626</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>630</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>633</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D7" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>565</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D8" s="13" t="s">
-        <v>566</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>567</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D9" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>568</v>
+      <c r="A7" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>635</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>636</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>638</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>630</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>639</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D10" s="13" t="s">
-        <v>569</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>570</v>
+      <c r="A10" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>641</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D11" s="13" t="s">
-        <v>571</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>572</v>
+      <c r="A11" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D12" s="13" t="s">
-        <v>573</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>574</v>
+      <c r="A12" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>645</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D13" s="13" t="s">
-        <v>575</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D14" s="13" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="13" t="s">
-        <v>418</v>
+      <c r="A13" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>646</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>630</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>636</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>653</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>654</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>630</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>658</v>
       </c>
     </row>
   </sheetData>

--- a/marketing/Calendario_Editorial_FairHealth.xlsx
+++ b/marketing/Calendario_Editorial_FairHealth.xlsx
@@ -19,7 +19,7 @@
     <sheet name="Listas" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Calendário'!$A$4:$Z$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Calendário'!$A$4:$AA$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -640,7 +640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A41"/>
+  <dimension ref="A1:A42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -656,7 +656,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Versão de 09/10/2026: planejamento MENSAL (um mês por vez). A versão anterior, de 90 dias, está em marketing/arquivo/.</t>
+          <t>Versão de 13/10/2026: o Mês 1 foi reorganizado como a história da marca, em quatro capítulos, e cada post se liga ao anterior e ao seguinte (coluna "Fio da história"). As versões anteriores (90 dias, 09/10 e 12/10) estão em marketing/arquivo/.</t>
         </is>
       </c>
     </row>
@@ -680,226 +680,233 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Cada mês trabalha um argumento do grupo (aba Visão do mês) e cada semana é uma cena: Abertura/Dor ("isso é comigo?"), Virada ("como a Fair Health resolve?"), Prova ("por que acreditar?") e Convite ("como começo?").</t>
+          <t>Cada mês trabalha um argumento do grupo (aba Visão do mês) e cada semana é um capítulo. No Mês 1: Por que existimos, Por dentro do cuidado, O que muda para a empresa e O convite.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>Regra de 13/10: nenhum post entra solto. Cada um retoma o anterior (na primeira frase da legenda ou no primeiro slide) e puxa o próximo (no fim). A pergunta "O que é importante para você?" aparece em todos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>Base: instagram/posicionamento-e-plano-mensal.md (análise da arquitetura de marcas e do posicionamento v3.2).</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-    </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Restrições em vigor (09/10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>1. Não apresentamos o time por enquanto (questão administrativa). A série Quem cuida está na aba Banco de ideias, com status Adiada.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2. Não filmamos clientes: nada gravado dentro das empresas-clientes nem com pessoas atendidas. Os vídeos do mês são de tipografia, motion, gravação de tela ou imagem de banco (aba Formatos).</t>
+          <t>1. Não apresentamos o time por enquanto (questão administrativa). A série Quem cuida está na aba Banco de ideias, com status Adiada.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>3. Nunca citamos nomes reais de pessoas ou empresas nos posts. Quando a história precisa de alguém, usamos personagem fictícia, sinalizada como "história ilustrativa". O artigo da RH Pra Você (25/09/2026) é citado só pelo título e pelo veículo.</t>
+          <t>2. Não filmamos clientes: nada gravado dentro das empresas-clientes nem com pessoas atendidas. Os vídeos do mês são de tipografia, motion, gravação de tela ou imagem de banco (aba Formatos).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>4. Números são bem-vindos, mas o foco é o cuidado: a frase de cuidado vem primeiro e o número entra como contexto, em tom calmo, com a fonte visível (regras na aba Ciência).</t>
+          <t>3. Nunca citamos nomes reais de pessoas ou empresas nos posts. Quando a história precisa de alguém, usamos personagem fictícia, sinalizada como "história ilustrativa". O artigo da RH Pra Você (25/09/2026) é citado só pelo título e pelo veículo.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>5. Artigos científicos e fontes oficiais viram posts que conectam a evidência ao nosso trabalho (aba Ciência). Medicina do Estilo de Vida: 6 pilares, sem espiritualidade (a confirmar).</t>
+          <t>4. Números são bem-vindos, mas o foco é o cuidado: a frase de cuidado vem primeiro e o número entra como contexto, em tom calmo, com a fonte visível (regras na aba Ciência).</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>5. Artigos científicos e fontes oficiais viram posts que conectam a evidência ao nosso trabalho (aba Ciência). Medicina do Estilo de Vida: 7 pilares, com espiritualidade e propósito (decisão da Nina, 12/10).</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Como trabalhamos nesta planilha</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>1. Revisão mensal (conjunta): antes de o mês começar, revisamos temas, títulos, personas e datas. Pauta aprovada muda de "Pauta proposta" para "Pauta aprovada". Ao fim do mês, montamos o próximo a partir do Banco de ideias.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2. Detalhamento semanal: a cada semana, detalhamos texto, roteiro e criativo das peças da semana seguinte e passamos pela validação. A semana 1 já está detalhada.</t>
+          <t>1. Revisão mensal (conjunta): antes de o mês começar, revisamos temas, títulos, personas e datas. Pauta aprovada muda de "Pauta proposta" para "Pauta aprovada". Ao fim do mês, montamos o próximo a partir do Banco de ideias.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>3. Comentários: use a coluna "Comentários da revisão" ou comentários de célula. Não apague pautas descartadas: mude o status para "Descartada".</t>
+          <t>2. Detalhamento semanal: a cada semana, detalhamos texto, roteiro e criativo das peças da semana seguinte e passamos pela validação. A semana 1 já está detalhada.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>3. Comentários: use a coluna "Comentários da revisão" ou comentários de célula. Não apague pautas descartadas: mude o status para "Descartada".</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>4. Datas: a data de início (célula amarela na aba Calendário) recalcula todas as datas sugeridas. Para mudar uma data só, digite a nova data por cima.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-    </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Cadência proposta (a validar)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>4 publicações por semana no feed, alternando vídeo e estático/carrossel (2 vídeos por semana). As três linhas editoriais entram em rodízio: duas peças seguidas nunca são da mesma linha.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>4 publicações por semana no feed. A ordem segue a história (decisão de 13/10): vídeo e carrossel se alternam quando a história deixa, e o equilíbrio de formatos e linhas é conferido no mês inteiro (aba Visão do mês), não peça a peça.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
           <t>Os dias da semana NÃO estão definidos: as datas são uma distribuição sugerida (evitando feriados nacionais). Stories ficam fora da contagem e servem de apoio: link do artigo, caixa de perguntas, repost.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-    </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Marcações</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>[PENDENTE] = informação que ainda precisa ser confirmada. [SUGESTÃO] = posição ou texto proposto que precisa de aprovação.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Coluna "Validação necessária": tudo o que precisa de aval antes de publicar. Afirmações clínicas, benefícios, prazos e resultados passam pela responsável médica.</t>
+          <t>[PENDENTE] = informação que ainda precisa ser confirmada. [SUGESTÃO] = posição ou texto proposto que precisa de aprovação.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>Coluna "Validação necessária": tudo o que precisa de aval antes de publicar. Afirmações clínicas, benefícios, prazos e resultados passam pela responsável médica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
           <t>Usamos números liberados (aba Fontes) e números de estudos científicos e fontes oficiais com a referência completa (aba Ciência). Números do posicionamento sem fonte (23%, R$ 2.400, burnout) ficam de fora.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr"/>
-    </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Fluxo de status</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Ideia → Pauta proposta → Pauta aprovada → Aguardando material → Roteiro pronto → Em produção → Em revisão → Validação médica → Aprovado → Agendado → Publicado (ou Descartada / Aguardando pauta / Adiada)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
-    </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Abas</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Visão do mês: argumento, a história semana a semana e o equilíbrio do mês (contagens automáticas).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Calendário: as 16 pautas do mês, uma por linha, com Argumento, Cena, Persona e "Por que este formato".</t>
+          <t>Visão do mês: argumento, a história semana a semana e o equilíbrio do mês (contagens automáticas).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Formatos: os formatos usados no mês, por que funcionam e o que cada um precisa para ser produzido sem time em cena e sem gravar nas empresas.</t>
+          <t>Calendário: as 16 pautas do mês, uma por linha, com Argumento, Cena, Fio da história, Persona e "Por que este formato". A coluna Comentários traz o ID antigo de cada pauta.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Ciência: estudos e fontes oficiais com referência, o que encontraram, como apresentar o número com suavidade e a ligação com o nosso trabalho.</t>
+          <t>Formatos: os formatos usados no mês, por que funcionam e o que cada um precisa para ser produzido sem time em cena e sem gravar nas empresas.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Fontes: o artigo da RH Pra Você, os números internos liberados e o que não usar.</t>
+          <t>Ciência: estudos e fontes oficiais com referência, o que encontraram, como apresentar o número com suavidade e a ligação com o nosso trabalho.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Banco de ideias: o que ficou para depois (com o motivo) e os temas dos próximos meses.</t>
+          <t>Fontes: o artigo da RH Pra Você, os números internos liberados e o que não usar.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Banco de ideias: o que ficou para depois (com o motivo) e os temas dos próximos meses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Linhas e personas · Pendências · Listas (valores das listas suspensas).</t>
         </is>
@@ -1285,7 +1292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1356,7 +1363,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>"Tudo começa com uma pergunta": quem somos, por que cuidar antes e como o cuidado funciona.</t>
+          <t>"Tudo começa com uma pergunta": a história da marca, contada em quatro capítulos.</t>
         </is>
       </c>
       <c r="C6" s="8" t="n"/>
@@ -1369,12 +1376,12 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Argumento principal</t>
+          <t>A história em uma frase</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Liderança Bem-Estar, com a apresentação da marca. A NR-1 entra como contexto (artigo da RH Pra Você) e a ciência sustenta o mês (OMS, Diabetes Prevention Program, RAND).</t>
+          <t>Uma pergunta nasceu num hospital, mudou para dentro da empresa para cuidar antes, virou quatro frentes de cuidado, mudou o que a empresa enxerga e termina num convite para cada pessoa.</t>
         </is>
       </c>
       <c r="C7" s="8" t="n"/>
@@ -1387,12 +1394,12 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Mensagem do mês</t>
+          <t>Argumento principal</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Todo afastamento tem um antes. A Fair Health cuida nesse antes: dentro da empresa, com gente de verdade, começando por uma pergunta.</t>
+          <t>Apresentação da marca, com Liderança Bem-Estar. A ciência sustenta o mês (OMS, Diabetes Prevention Program, RAND). A NR-1 fica para o Mês 2, que é o mês dela.</t>
         </is>
       </c>
       <c r="C8" s="8" t="n"/>
@@ -1405,12 +1412,12 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Frase-tese</t>
+          <t>Como os posts se ligam</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Não é benefício. É infraestrutura de cuidado.</t>
+          <t>1. Cada post retoma o anterior e puxa o próximo (coluna "Fio da história"). 2. A pergunta "O que é importante para você?" aparece em todos. 3. A semana 2 abre, uma a uma, as quatro frentes apresentadas no "O que é a fairhealth" (M1-04). 4. A Clara, personagem fictícia, costura o plano (M1-07) e o sono (M1-13). 5. O último post do mês recapitula a história em quatro frases (M1-16). 6. [SUGESTÃO] Etiqueta de capítulo na capa.</t>
         </is>
       </c>
       <c r="C9" s="8" t="n"/>
@@ -1423,12 +1430,12 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Restrições</t>
+          <t>Mensagem do mês</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Sem apresentar o time (questão administrativa), sem filmar clientes e sem nomes reais (personagens fictícias quando preciso). Vídeos de tipografia, motion, gravação de tela ou imagem de banco.</t>
+          <t>Todo afastamento tem um antes. A Fair Health cuida nesse antes: dentro da empresa, com gente de verdade, começando por uma pergunta.</t>
         </is>
       </c>
       <c r="C10" s="8" t="n"/>
@@ -1441,12 +1448,12 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Números</t>
+          <t>Frase-tese</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Sim, com suavidade: cuidado primeiro, número como contexto, fonte visível. Um número principal por peça.</t>
+          <t>Não é benefício. É infraestrutura de cuidado.</t>
         </is>
       </c>
       <c r="C11" s="8" t="n"/>
@@ -1459,12 +1466,12 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Datas do calendário</t>
+          <t>Restrições</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>02/11 feriado (Finados): a semana 3 começa na terça. 14/11 (sábado) Dia Mundial do Diabetes: post de ciência na véspera (M1-16) e stories no dia. Novembro Azul: só se houver conexão real.</t>
+          <t>Sem apresentar o time (questão administrativa), sem filmar clientes e sem nomes reais (personagens fictícias quando preciso). Vídeos de tipografia, motion, gravação de tela ou imagem de banco.</t>
         </is>
       </c>
       <c r="C12" s="8" t="n"/>
@@ -1474,157 +1481,113 @@
       <c r="G12" s="8" t="n"/>
       <c r="H12" s="9" t="n"/>
     </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Números</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Sim, com suavidade: cuidado primeiro, número como contexto, fonte visível. Um número principal por peça.</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="9" t="n"/>
+    </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Datas do calendário</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>02/11 feriado (Finados): a semana 3 começa na terça. 14/11 (sábado) Dia Mundial do Diabetes: post de ciência na quinta, 12/11 (M1-15), e stories no dia. Novembro Azul: só se houver conexão real.</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>A história semana a semana</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>Semana</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>Cena</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Capítulo</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Pergunta que responde</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Peças (IDs)</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>Vídeos</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
         <is>
           <t>Institucional</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>Produto</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="I17" s="11" t="inlineStr">
         <is>
           <t>Projetos</t>
         </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Abertura e Dor</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>"Isso é comigo?" A marca se apresenta e o RH se reconhece no problema.</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>M1-01 a M1-04</t>
-        </is>
-      </c>
-      <c r="E16" s="7">
-        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="7">
-        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A16,'Calendário'!$N$5:$N$400,"Vídeo")</f>
-        <v/>
-      </c>
-      <c r="G16" s="7">
-        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A16,'Calendário'!$E$5:$E$400,"Institucional")</f>
-        <v/>
-      </c>
-      <c r="H16" s="7">
-        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A16,'Calendário'!$E$5:$E$400,"Produto")</f>
-        <v/>
-      </c>
-      <c r="I16" s="7">
-        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A16,'Calendário'!$E$5:$E$400,"Projetos, eventos e entregas")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Virada</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>"Como a Fair Health resolve?" Método, tese e o que o RH recebe.</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>M1-05 a M1-08</t>
-        </is>
-      </c>
-      <c r="E17" s="7">
-        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="7">
-        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A17,'Calendário'!$N$5:$N$400,"Vídeo")</f>
-        <v/>
-      </c>
-      <c r="G17" s="7">
-        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A17,'Calendário'!$E$5:$E$400,"Institucional")</f>
-        <v/>
-      </c>
-      <c r="H17" s="7">
-        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A17,'Calendário'!$E$5:$E$400,"Produto")</f>
-        <v/>
-      </c>
-      <c r="I17" s="7">
-        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A17,'Calendário'!$E$5:$E$400,"Projetos, eventos e entregas")</f>
-        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Prova</t>
+          <t>Capítulo 1 · Por que existimos</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>"Por que acreditar?" Adesão, acompanhamento, origem e autoridade.</t>
+          <t>"Quem são vocês e por que existem?" A pergunta, de onde ela veio, por que cuidar antes e quem somos.</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>M1-09 a M1-12</t>
+          <t>M1-01 a M1-04</t>
         </is>
       </c>
       <c r="E18" s="7">
@@ -1632,7 +1595,7 @@
         <v/>
       </c>
       <c r="F18" s="7">
-        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A18,'Calendário'!$N$5:$N$400,"Vídeo")</f>
+        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A18,'Calendário'!$O$5:$O$400,"Vídeo")</f>
         <v/>
       </c>
       <c r="G18" s="7">
@@ -1650,21 +1613,21 @@
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Convite</t>
+          <t>Capítulo 2 · Por dentro do cuidado</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>"Como começo?" Para o colaborador, o líder e o RH, com a ciência por trás do cuidado.</t>
+          <t>"Como o cuidado funciona?" As quatro frentes, uma a uma, seguindo uma pessoa.</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>M1-13 a M1-16</t>
+          <t>M1-05 a M1-08</t>
         </is>
       </c>
       <c r="E19" s="7">
@@ -1672,7 +1635,7 @@
         <v/>
       </c>
       <c r="F19" s="7">
-        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A19,'Calendário'!$N$5:$N$400,"Vídeo")</f>
+        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A19,'Calendário'!$O$5:$O$400,"Vídeo")</f>
         <v/>
       </c>
       <c r="G19" s="7">
@@ -1689,114 +1652,150 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Capítulo 3 · O que muda para a empresa</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>"E para a empresa?" O que o RH vê, a tese, a adesão e em que a gente acredita.</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>M1-09 a M1-12</t>
+        </is>
+      </c>
+      <c r="E20" s="7">
+        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A20)</f>
+        <v/>
+      </c>
+      <c r="F20" s="7">
+        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A20,'Calendário'!$O$5:$O$400,"Vídeo")</f>
+        <v/>
+      </c>
+      <c r="G20" s="7">
+        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A20,'Calendário'!$E$5:$E$400,"Institucional")</f>
+        <v/>
+      </c>
+      <c r="H20" s="7">
+        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A20,'Calendário'!$E$5:$E$400,"Produto")</f>
+        <v/>
+      </c>
+      <c r="I20" s="7">
+        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A20,'Calendário'!$E$5:$E$400,"Projetos, eventos e entregas")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Capítulo 4 · O convite</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>"Como começo?" Um convite para quem é cuidado, para quem lidera e para quem decide, com a ciência por trás.</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>M1-13 a M1-16</t>
+        </is>
+      </c>
+      <c r="E21" s="7">
+        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A21)</f>
+        <v/>
+      </c>
+      <c r="F21" s="7">
+        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A21,'Calendário'!$O$5:$O$400,"Vídeo")</f>
+        <v/>
+      </c>
+      <c r="G21" s="7">
+        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A21,'Calendário'!$E$5:$E$400,"Institucional")</f>
+        <v/>
+      </c>
+      <c r="H21" s="7">
+        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A21,'Calendário'!$E$5:$E$400,"Produto")</f>
+        <v/>
+      </c>
+      <c r="I21" s="7">
+        <f>COUNTIFS('Calendário'!$C$5:$C$400,$A21,'Calendário'!$E$5:$E$400,"Projetos, eventos e entregas")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="E20" s="13">
-        <f>SUM(E16:E19)</f>
+      <c r="E22" s="13">
+        <f>SUM(E18:E21)</f>
         <v/>
       </c>
-      <c r="F20" s="13">
-        <f>SUM(F16:F19)</f>
+      <c r="F22" s="13">
+        <f>SUM(F18:F21)</f>
         <v/>
       </c>
-      <c r="G20" s="13">
-        <f>SUM(G16:G19)</f>
+      <c r="G22" s="13">
+        <f>SUM(G18:G21)</f>
         <v/>
       </c>
-      <c r="H20" s="13">
-        <f>SUM(H16:H19)</f>
+      <c r="H22" s="13">
+        <f>SUM(H18:H21)</f>
         <v/>
       </c>
-      <c r="I20" s="13">
-        <f>SUM(I16:I19)</f>
+      <c r="I22" s="13">
+        <f>SUM(I18:I21)</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>Equilíbrio por argumento e por cena</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Argumento</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>Peças</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>Cena</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>Peças</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="G25" s="14" t="inlineStr">
         <is>
           <t>Pautas com validação médica</t>
         </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>Apresentação</t>
-        </is>
-      </c>
-      <c r="B24" s="15">
-        <f>COUNTIFS('Calendário'!$F$5:$F$400,$A24)</f>
-        <v/>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>Abertura</t>
-        </is>
-      </c>
-      <c r="E24" s="15">
-        <f>COUNTIFS('Calendário'!$G$5:$G$400,$D24)</f>
-        <v/>
-      </c>
-      <c r="G24" s="15">
-        <f>SUMPRODUCT(('Calendário'!$B$5:$B$400&lt;&gt;"")*ISNUMBER(SEARCH("responsável médica",'Calendário'!$T$5:$T$400)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>Liderança Bem-Estar</t>
-        </is>
-      </c>
-      <c r="B25" s="15">
-        <f>COUNTIFS('Calendário'!$F$5:$F$400,$A25)</f>
-        <v/>
-      </c>
-      <c r="D25" s="15" t="inlineStr">
-        <is>
-          <t>Dor</t>
-        </is>
-      </c>
-      <c r="E25" s="15">
-        <f>COUNTIFS('Calendário'!$G$5:$G$400,$D25)</f>
-        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>NR-1</t>
+          <t>Apresentação</t>
         </is>
       </c>
       <c r="B26" s="15">
@@ -1805,18 +1804,22 @@
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>Virada</t>
+          <t>Abertura</t>
         </is>
       </c>
       <c r="E26" s="15">
         <f>COUNTIFS('Calendário'!$G$5:$G$400,$D26)</f>
         <v/>
       </c>
+      <c r="G26" s="15">
+        <f>SUMPRODUCT(('Calendário'!$B$5:$B$400&lt;&gt;"")*ISNUMBER(SEARCH("responsável médica",'Calendário'!$U$5:$U$400)))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>Stop Loss</t>
+          <t>Liderança Bem-Estar</t>
         </is>
       </c>
       <c r="B27" s="15">
@@ -1825,7 +1828,7 @@
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>Prova</t>
+          <t>Dor</t>
         </is>
       </c>
       <c r="E27" s="15">
@@ -1836,7 +1839,7 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>Ambiente positivo</t>
+          <t>NR-1</t>
         </is>
       </c>
       <c r="B28" s="15">
@@ -1845,7 +1848,7 @@
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>Convite</t>
+          <t>Virada</t>
         </is>
       </c>
       <c r="E28" s="15">
@@ -1856,18 +1859,60 @@
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>Marca empregadora</t>
+          <t>Stop Loss</t>
         </is>
       </c>
       <c r="B29" s="15">
         <f>COUNTIFS('Calendário'!$F$5:$F$400,$A29)</f>
         <v/>
       </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>Prova</t>
+        </is>
+      </c>
+      <c r="E29" s="15">
+        <f>COUNTIFS('Calendário'!$G$5:$G$400,$D29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>Ambiente positivo</t>
+        </is>
+      </c>
+      <c r="B30" s="15">
+        <f>COUNTIFS('Calendário'!$F$5:$F$400,$A30)</f>
+        <v/>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>Convite</t>
+        </is>
+      </c>
+      <c r="E30" s="15">
+        <f>COUNTIFS('Calendário'!$G$5:$G$400,$D30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Marca empregadora</t>
+        </is>
+      </c>
+      <c r="B31" s="15">
+        <f>COUNTIFS('Calendário'!$F$5:$F$400,$A31)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
     <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B14:H14"/>
     <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B13:H13"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B12:H12"/>
     <mergeCell ref="B6:H6"/>
@@ -1886,7 +1931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:AA23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1899,22 +1944,23 @@
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="44" customWidth="1" min="18" max="18"/>
-    <col width="34" customWidth="1" min="19" max="19"/>
-    <col width="40" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="50" customWidth="1" min="22" max="22"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="44" customWidth="1" min="19" max="19"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
     <col width="50" customWidth="1" min="23" max="23"/>
-    <col width="40" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="36" customWidth="1" min="26" max="26"/>
+    <col width="50" customWidth="1" min="24" max="24"/>
+    <col width="40" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="36" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1992,80 +2038,85 @@
       </c>
       <c r="K4" s="11" t="inlineStr">
         <is>
+          <t>Fio da história (vem de → leva para)</t>
+        </is>
+      </c>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
           <t>Persona</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="M4" s="11" t="inlineStr">
         <is>
           <t>Necessidade ou pergunta da persona</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr">
+      <c r="N4" s="11" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="O4" s="11" t="inlineStr">
         <is>
           <t>Formato</t>
         </is>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="P4" s="11" t="inlineStr">
         <is>
           <t>Por que este formato</t>
         </is>
       </c>
-      <c r="P4" s="11" t="inlineStr">
+      <c r="Q4" s="11" t="inlineStr">
         <is>
           <t>Canal</t>
         </is>
       </c>
-      <c r="Q4" s="11" t="inlineStr">
+      <c r="R4" s="11" t="inlineStr">
         <is>
           <t>Collab / perfis</t>
         </is>
       </c>
-      <c r="R4" s="11" t="inlineStr">
+      <c r="S4" s="11" t="inlineStr">
         <is>
           <t>Mensagem principal</t>
         </is>
       </c>
-      <c r="S4" s="11" t="inlineStr">
+      <c r="T4" s="11" t="inlineStr">
         <is>
           <t>Fonte</t>
         </is>
       </c>
-      <c r="T4" s="11" t="inlineStr">
+      <c r="U4" s="11" t="inlineStr">
         <is>
           <t>Validação necessária</t>
         </is>
       </c>
-      <c r="U4" s="11" t="inlineStr">
+      <c r="V4" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="V4" s="11" t="inlineStr">
+      <c r="W4" s="11" t="inlineStr">
         <is>
           <t>Texto / legenda</t>
         </is>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="X4" s="11" t="inlineStr">
         <is>
           <t>Roteiro / estrutura</t>
         </is>
       </c>
-      <c r="X4" s="11" t="inlineStr">
+      <c r="Y4" s="11" t="inlineStr">
         <is>
           <t>Criativo (modelo e arte)</t>
         </is>
       </c>
-      <c r="Y4" s="11" t="inlineStr">
+      <c r="Z4" s="11" t="inlineStr">
         <is>
           <t>Responsável</t>
         </is>
       </c>
-      <c r="Z4" s="11" t="inlineStr">
+      <c r="AA4" s="11" t="inlineStr">
         <is>
           <t>Comentários da revisão</t>
         </is>
@@ -2117,69 +2168,74 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
+          <t>Abre a história com a pergunta que guia tudo. Leva para: de onde essa pergunta veio (M1-02).</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
           <t>Colaboradores; RH</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>O que é a Fair Health e o que ela faz dentro da empresa?</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>Apresentar a marca e o jeito de cuidar</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>Vídeo</t>
         </is>
       </c>
-      <c r="O5" s="7" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>Vídeo de abertura com a pergunta da marca: apresenta em 30 s o que é, onde fica e como começa. Texto na tela para quem assiste sem som.</t>
         </is>
       </c>
-      <c r="P5" s="7" t="inlineStr">
+      <c r="Q5" s="7" t="inlineStr">
         <is>
           <t>Instagram + LinkedIn</t>
         </is>
       </c>
-      <c r="Q5" s="7" t="inlineStr">
+      <c r="R5" s="7" t="inlineStr">
         <is>
           <t>FairJob</t>
         </is>
       </c>
-      <c r="R5" s="7" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>A Fair Health leva o cuidado para dentro da empresa, e todo cuidado começa com uma pergunta: o que é importante para você?</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="T5" s="7" t="inlineStr">
         <is>
           <t>Posicionamento Fair Health v3.2 (promessa e pergunta).</t>
         </is>
       </c>
-      <c r="T5" s="7" t="inlineStr">
+      <c r="U5" s="7" t="inlineStr">
         <is>
           <t>Roteiro e legenda citam assistentes sociais: confirmar se fazem parte do atendimento (o posicionamento cita médico e psicológico). Sem time em cena e sem gravar nas empresas-clientes (decisão de 09/10). Definir onde gravar (local próprio ou neutro) ou montar com fotos e tipografia.</t>
         </is>
       </c>
-      <c r="U5" s="7" t="inlineStr">
+      <c r="V5" s="7" t="inlineStr">
         <is>
           <t>Roteiro pronto</t>
         </is>
       </c>
-      <c r="V5" s="7" t="inlineStr">
+      <c r="W5" s="7" t="inlineStr">
         <is>
           <t>Antes de qualquer exame, uma conversa.
 Esse é o Escritório do Cuidado: um espaço dentro da empresa, com médicos, psicólogos e assistentes sociais, perto de quem trabalha.
 Aqui, todo cuidado começa com a mesma pergunta: o que é importante para você? A partir da resposta, montamos juntos um plano que cabe na sua rotina e seguimos acompanhando.
-Seja bem-vindo. Nos próximos dias, a gente mostra como esse cuidado funciona.
+Essa pergunta tem história. Ela não nasceu numa empresa: nasceu num hospital. No próximo post, a gente conta.
 #fairhealth #saudecorporativa #cuidadocentradonapessoa #medicinadoestilodevida #saudedotrabalhador</t>
         </is>
       </c>
-      <c r="W5" s="7" t="inlineStr">
+      <c r="X5" s="7" t="inlineStr">
         <is>
           <t>Reel de 30 a 34 s (instagram/primeiros-posts-acolhimento.md, ID 1).
 0–3 s: "Antes de qualquer exame, a gente começa com uma conversa." Porta se abrindo.
@@ -2190,13 +2246,13 @@
 30–34 s: logo e assinatura.</t>
         </is>
       </c>
-      <c r="X5" s="7" t="inlineStr">
+      <c r="Y5" s="7" t="inlineStr">
         <is>
           <t>Vídeo 1080x1920. Texto na tela dentro da área segura. Capa no modelo M1 (Tiffany, pergunta), conferindo o recorte da grade. LinkedIn: mesmo vídeo, legenda adaptada para RH.</t>
         </is>
       </c>
-      <c r="Y5" s="7" t="n"/>
-      <c r="Z5" s="7" t="inlineStr">
+      <c r="Z5" s="7" t="n"/>
+      <c r="AA5" s="7" t="inlineStr">
         <is>
           <t>Aprovado na revisão de 09/10. Ajustes pelas restrições de 09/10: a legenda não promete mais apresentar o time ("você vai conhecer quem cuida" virou "a gente mostra como esse cuidado funciona") e, no roteiro, a pergunta entra na tela em voz em off (antes cada integrante dizia um pedaço).</t>
         </is>
@@ -2222,7 +2278,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Produto</t>
+          <t>Institucional</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -2237,99 +2293,106 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Escritório do Cuidado</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>Como funciona o cuidado (1/3): o percurso</t>
-        </is>
-      </c>
+          <t>Origem</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="n"/>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Aqui, o cuidado começa com uma pergunta</t>
+          <t>Essa pergunta nasceu num hospital</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>Colaboradores</t>
+          <t>Vem de: a pergunta (M1-01). Leva para: por que levar esse cuidado para dentro da empresa, e por que antes (M1-03).</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>O que acontece quando eu vou ao Escritório do Cuidado? Vou ser julgado? O que eu contar fica entre nós?</t>
+          <t>RH; Medicina do Trabalho</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>Explicar o percurso do atendimento e reduzir a barreira de ir</t>
+          <t>De onde vem esse modelo? É só mais um programa de bem-estar?</t>
         </is>
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
+          <t>Dar lastro à marca com a história do modelo</t>
+        </is>
+      </c>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
           <t>Carrossel</t>
         </is>
       </c>
-      <c r="O6" s="7" t="inlineStr">
-        <is>
-          <t>Carrossel passo a passo: o formato mais salvo em conteúdo explicativo. Responde as objeções (julgamento, sigilo) uma por slide.</t>
-        </is>
-      </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
+          <t>Linha do tempo em carrossel: a história de origem se lê no ritmo de quem arrasta, um marco por slide, sem precisar mostrar pessoas. Logo depois da pergunta, responde "de onde vem isso?".</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
           <t>Instagram + LinkedIn</t>
         </is>
       </c>
-      <c r="Q6" s="7" t="inlineStr">
+      <c r="R6" s="7" t="inlineStr">
         <is>
           <t>FairJob</t>
         </is>
       </c>
-      <c r="R6" s="7" t="inlineStr">
-        <is>
-          <t>Primeiro a gente te ouve e entende sua rotina; depois monta o plano com você e acompanha. O que você conta fica entre você e quem cuida.</t>
-        </is>
-      </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>Cartilha do Escritório do Cuidado.</t>
+          <t>O modelo nasceu em 2009, num hospital, para colocar o paciente no centro do cuidado. Hoje, coloca quem trabalha no centro, dentro da empresa.</t>
         </is>
       </c>
       <c r="T6" s="7" t="inlineStr">
         <is>
-          <t>Responsável médica confere as etapas citadas (anamnese, bioimpedância, smartband por 48 horas, retorno).</t>
+          <t>Histórico do Escritório do Paciente (2009); caso do hospital onde o modelo começou (liberado; ver aba Fontes).</t>
         </is>
       </c>
       <c r="U6" s="7" t="inlineStr">
         <is>
-          <t>Em revisão</t>
+          <t>Sem nomes de pessoas nem do hospital. Não usar "validado no SUS" até confirmar a fonte. Conferir datas.</t>
         </is>
       </c>
       <c r="V6" s="7" t="inlineStr">
         <is>
-          <t>Aqui, o cuidado começa com uma pergunta: o que é importante para você?
-Antes de exame, antes de número, a gente quer saber da sua rotina, do seu trabalho, do que anda pesando e do que você gostaria de mudar.
-O Escritório do Cuidado fica dentro da empresa, perto de onde você já está. Lá, médicos e psicólogos se revezam para montar com você um cuidado que caiba na sua vida, com base na Medicina do Estilo de Vida.
-O objetivo da fairhealth é melhorar a qualidade de vida de quem trabalha, com um cuidado feito para cada pessoa e acompanhado de perto.
-E o que você conta fica entre você e quem cuida.
-Arrasta para o lado para ver como funciona.
+          <t>Pauta proposta</t>
+        </is>
+      </c>
+      <c r="W6" s="7" t="inlineStr">
+        <is>
+          <t>Essa pergunta tem história.
+Em 2009, num hospital, nasceu o Escritório do Paciente: um jeito de colocar o paciente, de verdade, no centro do cuidado. Antes de propor qualquer coisa, a equipe perguntava: o que é importante para você?
+Funcionou num lugar de recursos escassos e mostrou que podia ser repetido em outros lugares.
+Anos depois, a mesma ideia mudou de endereço. Saiu do hospital e foi para dentro da empresa, onde as pessoas passam boa parte do dia. Virou o Escritório do Cuidado.
+Por que dentro da empresa? E por que antes? No próximo post.
 #fairhealth #saudecorporativa #cuidadocentradonapessoa #medicinadoestilodevida #saudedotrabalhador</t>
         </is>
       </c>
-      <c r="W6" s="7" t="inlineStr">
-        <is>
-          <t>10 slides: 1 capa (pergunta) · 2 fica dentro da empresa · 3 gente que cuida de gente · 4 Passo 1: a gente te conhece · 5 Passo 2: o que é importante para você? · 6 Passo 3: entender antes de propor (bioimpedância e smartband por 48 h) · 7 Passo 4: o plano é seu · 8 Passo 5: retorno e acompanhamento · 9 sigilo · 10 convite para comentar.</t>
-        </is>
-      </c>
       <c r="X6" s="7" t="inlineStr">
         <is>
-          <t>Arte no Canva (design DAHW6JfDldU, 11 páginas): escolher entre as versões originais e as novas dos slides 1, 5, 7, 9 e 10. Modelos M1, M2 e M3. LinkedIn: exportar em PDF.</t>
-        </is>
-      </c>
-      <c r="Y6" s="7" t="n"/>
-      <c r="Z6" s="7" t="inlineStr">
-        <is>
-          <t>Conferir o slide 3 ("gente que cuida de gente"): não pode ter foto ou nome de integrante do time.</t>
+          <t>Carrossel de 7 slides, linha do tempo (modelo M2), sem fotos de pessoas.
+1 Capa: "Essa pergunta nasceu num hospital."
+2 2009: o Escritório do Paciente. O paciente no centro do cuidado.
+3 O que o hospital ensinou: ouvir antes de propor.
+4 Funcionou com poucos recursos e podia ser repetido.
+5 2024 e 2025: o modelo sai do hospital e entra na empresa. Nasce o Escritório do Cuidado.
+6 Mesma pergunta: "O que é importante para você?"
+7 "Por que dentro da empresa? E por que antes?" (ponte para o próximo post) + logo.</t>
+        </is>
+      </c>
+      <c r="Y6" s="7" t="inlineStr">
+        <is>
+          <t>Modelo M2 (linha do tempo) com o fio contínuo ligando os marcos. Etiqueta de capítulo na capa [SUGESTÃO].</t>
+        </is>
+      </c>
+      <c r="Z6" s="7" t="n"/>
+      <c r="AA6" s="7" t="inlineStr">
+        <is>
+          <t>Antes: M1-11 (ordem de 12/10).</t>
         </is>
       </c>
     </row>
@@ -2379,72 +2442,77 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
+          <t>Vem de: a origem e a pergunta "por que antes?" (M1-02). Leva para: quem é a fairhealth (M1-04).</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
           <t>RH; Lideranças</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>Por que as pessoas só aparecem quando já estão doentes ou afastadas?</t>
         </is>
       </c>
-      <c r="M7" s="7" t="inlineStr">
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>Plantar o fio do mês ("cuidar antes") e fazer o RH se reconhecer na dor</t>
         </is>
       </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t>Vídeo</t>
         </is>
       </c>
-      <c r="O7" s="7" t="inlineStr">
+      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>Reel de tipografia animada: não depende de filmagem nem de rosto, o gancho está na primeira frase e a cadeia do "antes" prende até o fim. Fácil de adaptar para o LinkedIn.</t>
         </is>
       </c>
-      <c r="P7" s="7" t="inlineStr">
+      <c r="Q7" s="7" t="inlineStr">
         <is>
           <t>Instagram + LinkedIn</t>
         </is>
       </c>
-      <c r="Q7" s="7" t="inlineStr">
+      <c r="R7" s="7" t="inlineStr">
         <is>
           <t>FairJob</t>
         </is>
       </c>
-      <c r="R7" s="7" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>Todo afastamento tem um antes. A Fair Health cuida nesse antes, dentro da empresa, começando por uma pergunta.</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="T7" s="7" t="inlineStr">
         <is>
           <t>Posicionamento Fair Health v3.2 (eixo "antes"). Ministério da Previdência Social: 472.328 licenças por transtornos mentais em 2024, maior número da série iniciada em 2014 (dados divulgados em 2025; conferir no painel oficial de dados abertos antes de publicar).</t>
         </is>
       </c>
-      <c r="T7" s="7" t="inlineStr">
+      <c r="U7" s="7" t="inlineStr">
         <is>
           <t>Sem promessa de evitar doença (CFM): o texto fala de cuidado, não de resultado. Número suave: cuidado primeiro, número como contexto, fonte visível e discreta (aba Ciência). Conferir o número no painel oficial.</t>
         </is>
       </c>
-      <c r="U7" s="7" t="inlineStr">
+      <c r="V7" s="7" t="inlineStr">
         <is>
           <t>Pauta proposta</t>
         </is>
       </c>
-      <c r="V7" s="7" t="inlineStr">
+      <c r="W7" s="7" t="inlineStr">
         <is>
           <t>Antes do afastamento, teve um atestado.
 Antes do atestado, teve uma semana pesada.
 Antes da semana pesada, teve uma noite sem dormir.
 E antes de tudo isso, ninguém perguntou: o que é importante para você?
 Em 2024, o Brasil registrou mais de 470 mil licenças do trabalho por saúde mental, o maior número em dez anos (Ministério da Previdência Social). Cada uma delas teve um antes.
-A Fair Health existe para cuidar nesse antes. Dentro da empresa, perto de quem trabalha, com médicos e psicólogos e um plano feito para cada pessoa.
-Cuidar antes também é papel da liderança. Na sua empresa, quem faz essa pergunta?
+É por isso que o cuidado saiu do hospital e foi para dentro da empresa: para chegar nesse antes, perto de quem trabalha.
+No próximo post, a gente se apresenta: o que somos, o que fazemos e o que oferecemos.
 #fairhealth #saudecorporativa #cuidadocentradonapessoa #medicinadoestilodevida #saudedotrabalhador</t>
         </is>
       </c>
-      <c r="W7" s="7" t="inlineStr">
+      <c r="X7" s="7" t="inlineStr">
         <is>
           <t>Reel de 22 a 26 s, só tipografia sobre o fundo Tiffany, frase a frase, com corte seco.
 0–3 s: "Antes do afastamento, teve um atestado."
@@ -2457,13 +2525,13 @@
 Trilha calma, sem locução (ou voz em off opcional).</t>
         </is>
       </c>
-      <c r="X7" s="7" t="inlineStr">
+      <c r="Y7" s="7" t="inlineStr">
         <is>
           <t>Modelo M9 (vídeo) só com tipografia Raleway. Capa: "Antes do afastamento, teve um sinal". Sem imagem de banco.</t>
         </is>
       </c>
-      <c r="Y7" s="7" t="n"/>
       <c r="Z7" s="7" t="n"/>
+      <c r="AA7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -2485,90 +2553,1938 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
+          <t>Institucional</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Apresentação</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Abertura</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Apresentação da fairhealth (o que é, o que faz, o que oferece)</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>O que é a fairhealth?</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>Vem de: por que cuidar antes (M1-03). Leva para: a semana que abre cada uma das quatro frentes, começando pelo Escritório do Cuidado (M1-05).</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>RH; Colaboradores</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>Quem é a fairhealth, o que ela faz e o que oferece?</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>Apresentar a marca inteira num post só e fechar o capítulo 1</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>Carrossel</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>Carrossel de 10 slides guiado por três perguntas (o que é, o que fazemos, o que oferecemos): é o post de referência da marca. [SUGESTÃO] Fixar no perfil.</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>Instagram + LinkedIn</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>FairJob</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>A fairhealth é medicina preventiva dentro da empresa: médicos e psicólogos, um plano de cuidado para cada pessoa e quatro frentes que funcionam juntas.</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>One-pager "Saúde e Bem-Estar para sua empresa baseado na Medicina do Estilo de Vida" e posicionamento v3.2 (11/10). Originais fora do repositório.</t>
+        </is>
+      </c>
+      <c r="U8" s="7" t="inlineStr">
+        <is>
+          <t>Origem e licença das fotos dos pilares. Slide 9: NR-1 sem promessa de conformidade.</t>
+        </is>
+      </c>
+      <c r="V8" s="7" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+      <c r="W8" s="7" t="inlineStr">
+        <is>
+          <t>O que é a fairhealth? Medicina preventiva, dentro da empresa.
+Nesta semana, você conheceu a pergunta que guia o nosso cuidado, de onde ela veio e por que cuidar antes. Agora, a gente se apresenta.
+O que somos: a solução de cuidado do ecossistema fairjob. Atendimento individualizado, com tecnologia e acompanhamento contínuo, para melhorar a qualidade de vida dos colaboradores. A base é a Medicina do Estilo de Vida, com sete pilares e a pessoa no centro.
+O que fazemos: levamos médicos e psicólogos para dentro da empresa, em plantões alternados. Cada pessoa passa por uma escuta, anamnese e medições, e recebe um plano de cuidado individualizado, com acompanhamento contínuo.
+O que oferecemos: quatro frentes que funcionam juntas. O Escritório do Cuidado, o Programa de Medicina do Estilo de Vida, uma plataforma digital e wearables.
+Na semana que vem, a gente abre cada uma delas, começando pela porta do Escritório do Cuidado.
+Quer levar esse cuidado para a sua empresa? Fale com a gente pelo direct.
+Fazemos o certo pelos motivos certos.
+#fairhealth #saudecorporativa #medicinadoestilodevida #escritoriodocuidado #gestaodepessoas</t>
+        </is>
+      </c>
+      <c r="X8" s="7" t="inlineStr">
+        <is>
+          <t>10 slides (arte final de 12/10): 1 capa · 2 medicina preventiva dentro da empresa (Venn) · 3 cuidar antes (linha do tempo) · 4 a base é a Medicina do Estilo de Vida · 5 sete pilares, a pessoa no centro · 6 médicos e psicólogos dentro da empresa · 7 cada pessoa recebe um plano de cuidado · 8 quatro frentes, um cuidado só · 9 e para a empresa? · 10 como começar, convite e assinatura.</t>
+        </is>
+      </c>
+      <c r="Y8" s="7" t="inlineStr">
+        <is>
+          <t>Canva: design DAHXwcr37Ok (https://www.canva.com/d/puyL8wniGObsaCu), 10 páginas, pronto. Repositório: instagram/posts/o-que-e-a-fairhealth/ (README e texto.md).</t>
+        </is>
+      </c>
+      <c r="Z8" s="7" t="n"/>
+      <c r="AA8" s="7" t="inlineStr">
+        <is>
+          <t>Entrou no calendário em 13/10, na reorganização do mês como história. A legenda foi ajustada para a nova ordem: o Escritório do Cuidado agora vem depois, na semana 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>M1-05</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Mês 1</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="17">
+        <f>$D$2+(C9-1)*7+0</f>
+        <v/>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Apresentação</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Virada</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Escritório do Cuidado</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Por dentro das quatro frentes (1/4): Escritório do Cuidado</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Aqui, o cuidado começa com uma pergunta</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Vem de: as quatro frentes apresentadas em "O que é a fairhealth" (M1-04). Abre a primeira: o Escritório do Cuidado. Leva para: a base do cuidado, a Medicina do Estilo de Vida (M1-06).</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>Colaboradores</t>
+        </is>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>O que acontece quando eu vou ao Escritório do Cuidado? Vou ser julgado? O que eu contar fica entre nós?</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>Explicar o percurso do atendimento e reduzir a barreira de ir</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>Carrossel</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>Carrossel passo a passo: o formato mais salvo em conteúdo explicativo. Responde as objeções (julgamento, sigilo) uma por slide.</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>Instagram + LinkedIn</t>
+        </is>
+      </c>
+      <c r="R9" s="7" t="inlineStr">
+        <is>
+          <t>FairJob</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>Primeiro a gente te ouve e entende sua rotina; depois monta o plano com você e acompanha. O que você conta fica entre você e quem cuida.</t>
+        </is>
+      </c>
+      <c r="T9" s="7" t="inlineStr">
+        <is>
+          <t>Cartilha do Escritório do Cuidado.</t>
+        </is>
+      </c>
+      <c r="U9" s="7" t="inlineStr">
+        <is>
+          <t>Responsável médica confere as etapas citadas (anamnese, bioimpedância, smartband por 48 horas, retorno).</t>
+        </is>
+      </c>
+      <c r="V9" s="7" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+      <c r="W9" s="7" t="inlineStr">
+        <is>
+          <t>Aqui, o cuidado começa com uma pergunta: o que é importante para você?
+Na semana passada, a gente se apresentou. Agora, abre a porta da primeira frente: o Escritório do Cuidado.
+Antes de exame, antes de número, a gente quer saber da sua rotina, do seu trabalho, do que anda pesando e do que você gostaria de mudar.
+O Escritório do Cuidado fica dentro da empresa, perto de onde você já está. Lá, médicos e psicólogos se revezam para montar com você um cuidado que caiba na sua vida, com base na Medicina do Estilo de Vida.
+E o que você conta fica entre você e quem cuida.
+Arrasta para o lado para ver como funciona. No próximo post: a base de tudo isso, a Medicina do Estilo de Vida.
+#fairhealth #saudecorporativa #cuidadocentradonapessoa #medicinadoestilodevida #saudedotrabalhador</t>
+        </is>
+      </c>
+      <c r="X9" s="7" t="inlineStr">
+        <is>
+          <t>10 slides: 1 capa (pergunta) · 2 fica dentro da empresa · 3 gente que cuida de gente · 4 Passo 1: a gente te conhece · 5 Passo 2: o que é importante para você? · 6 Passo 3: entender antes de propor (bioimpedância e smartband por 48 h) · 7 Passo 4: o plano é seu · 8 Passo 5: retorno e acompanhamento · 9 sigilo · 10 convite para comentar.</t>
+        </is>
+      </c>
+      <c r="Y9" s="7" t="inlineStr">
+        <is>
+          <t>Arte no Canva (design DAHW6JfDldU, 11 páginas): escolher entre as versões originais e as novas dos slides 1, 5, 7, 9 e 10. Modelos M1, M2 e M3. LinkedIn: exportar em PDF.</t>
+        </is>
+      </c>
+      <c r="Z9" s="7" t="n"/>
+      <c r="AA9" s="7" t="inlineStr">
+        <is>
+          <t>Antes: M1-02 (ordem de 12/10). Conferir o slide 3 ("gente que cuida de gente"): não pode ter foto ou nome de integrante do time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>M1-06</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Mês 1</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="17">
+        <f>$D$2+(C10-1)*7+1</f>
+        <v/>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Liderança Bem-Estar</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Virada</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Medicina do Estilo de Vida (Programa MEV)</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Por dentro das quatro frentes (2/4): Programa de Medicina do Estilo de Vida</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Medicina do Estilo de Vida em 1 minuto</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Vem de: o Escritório do Cuidado, onde o plano é montado "com base na Medicina do Estilo de Vida" (M1-05). Retoma a rosca dos sete pilares do M1-04. Leva para: como os pilares viram o plano de uma pessoa (M1-07).</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>Colaboradores; RH</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>O que é Medicina do Estilo de Vida? É dieta? É academia?</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>Apresentar a base científica do cuidado e abrir a série dos pilares</t>
+        </is>
+      </c>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>Vídeo</t>
+        </is>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>Explicador animado com ícones (motion): conceito novo explicado em 1 minuto, sem rosto. Responde ao mito "é só dieta e academia".</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>Instagram + LinkedIn</t>
+        </is>
+      </c>
+      <c r="R10" s="7" t="inlineStr">
+        <is>
+          <t>FairJob</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>Sete pilares, uma pessoa inteira: alimentação saudável, movimento, gerenciamento de estresse, sono de qualidade, manejo de vícios, relacionamentos e espiritualidade e propósito. O plano olha para todos, a partir da rotina real.</t>
+        </is>
+      </c>
+      <c r="T10" s="7" t="inlineStr">
+        <is>
+          <t>ACLM (American College of Lifestyle Medicine), 6 pilares; CBMEV (Colégio Brasileiro de Medicina do Estilo de Vida); cartilha do Escritório do Cuidado.</t>
+        </is>
+      </c>
+      <c r="U10" s="7" t="inlineStr">
+        <is>
+          <t>7 pilares (decisão da Nina, 12/10), com os mesmos nomes do carrossel "O que é a fairhealth". Responsável médica valida a definição de MEV.</t>
+        </is>
+      </c>
+      <c r="V10" s="7" t="inlineStr">
+        <is>
+          <t>Pauta proposta</t>
+        </is>
+      </c>
+      <c r="W10" s="7" t="n"/>
+      <c r="X10" s="7" t="inlineStr">
+        <is>
+          <t>Reel de 45 a 60 s, motion com ícones, voz em off.
+0–3 s: "Medicina do Estilo de Vida é dieta e academia? Não só."
+3–10 s: definição curta, com fonte na tela.
+10–42 s: os 7 pilares, um ícone e uma frase por pilar: alimentação saudável · movimento · gerenciamento de estresse · sono de qualidade · manejo de vícios · relacionamentos · espiritualidade e propósito.
+42–50 s: "Os pilares conversam entre si: o cuidado olha para a pessoa inteira."
+50–60 s: "No plano de cada pessoa, os pilares viram ações. No próximo post, como nasce esse plano." + logo.</t>
+        </is>
+      </c>
+      <c r="Y10" s="7" t="inlineStr">
+        <is>
+          <t>Modelo M9 com ícones lineares em verde-escuro sobre Tiffany. A ordem e os nomes dos pilares seguem a rosca do M1-04.</t>
+        </is>
+      </c>
+      <c r="Z10" s="7" t="n"/>
+      <c r="AA10" s="7" t="inlineStr">
+        <is>
+          <t>Antes: M1-05 (ordem de 12/10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>M1-07</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Mês 1</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="17">
+        <f>$D$2+(C11-1)*7+3</f>
+        <v/>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Apresentação</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Virada</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Plano Individualizado de Cuidado</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Por dentro das quatro frentes (3/4): o plano e a plataforma digital</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>O plano é seu: como nasce o Plano Individualizado de Cuidado</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Vem de: os sete pilares (M1-06). Mostra como eles viram o plano de uma pessoa, a Clara (personagem fictícia), e onde esse plano fica (plataforma digital). Leva para: o que acontece depois da consulta (M1-08). A Clara volta no M1-13 (sono).</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>Colaboradores</t>
+        </is>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>Vou receber uma lista de regras impossíveis de seguir?</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>Explicar como o plano é montado com a pessoa (decisão compartilhada)</t>
+        </is>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t>Carrossel</t>
+        </is>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>Carrossel com card de interface (M3), já testado no carrossel de acolhimento, contado pela história de uma personagem fictícia: história prende mais que explicação e mostra o plano como algo possível.</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>Instagram + LinkedIn</t>
+        </is>
+      </c>
+      <c r="R11" s="7" t="inlineStr">
+        <is>
+          <t>FairJob</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>O plano parte do que é importante para você e da sua rotina real, com ações nos pilares da MEV, e muda quando a vida muda.</t>
+        </is>
+      </c>
+      <c r="T11" s="7" t="inlineStr">
+        <is>
+          <t>Cartilha do Escritório do Cuidado. Personagem fictícia.</t>
+        </is>
+      </c>
+      <c r="U11" s="7" t="inlineStr">
+        <is>
+          <t>Responsável médica valida etapas e prazos. Nome único do plano: "Plano Individualizado de Cuidado" ou "Plano de Cuidado Personalizado"? Indicar no slide e na legenda que é uma história ilustrativa (personagem fictícia), para não parecer depoimento.</t>
+        </is>
+      </c>
+      <c r="V11" s="7" t="inlineStr">
+        <is>
+          <t>Pauta proposta</t>
+        </is>
+      </c>
+      <c r="W11" s="7" t="n"/>
+      <c r="X11" s="7" t="inlineStr">
+        <is>
+          <t>8 slides, com a Clara (personagem fictícia, 41 anos, supervisora de turno).
+1 Capa: "O plano é seu."
+2 No último post, os sete pilares. Aqui, como eles viram um plano para uma pessoa.
+3 A Clara chegou dizendo: "Quero voltar a ter energia para brincar com meu filho." Isso é o que importa para ela.
+4 Card do plano da Clara: 3 ações pequenas (dormir 30 min mais cedo, caminhada de 10 min no almoço, conversa quinzenal com a psicóloga).
+5 Cabe na rotina real: no turno dela, não numa rotina ideal.
+6 O plano, o histórico e as metas ficam na plataforma digital.
+7 Muda quando a vida muda, e alguém acompanha, sem julgamento.
+8 "E depois da consulta? O cuidado continua." (ponte) Rodapé: "História ilustrativa. Personagem fictícia."</t>
+        </is>
+      </c>
+      <c r="Y11" s="7" t="inlineStr">
+        <is>
+          <t>Modelo M3 (card de interface do plano). Sem foto de pessoa: a personagem aparece só no texto e no card.</t>
+        </is>
+      </c>
+      <c r="Z11" s="7" t="n"/>
+      <c r="AA11" s="7" t="inlineStr">
+        <is>
+          <t>Antes: M1-08 (ordem de 12/10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>M1-08</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Mês 1</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="17">
+        <f>$D$2+(C12-1)*7+4</f>
+        <v/>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Apresentação</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Virada</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Tecnologia: wearables</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Por dentro das quatro frentes (4/4): wearables</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>O cuidado não para quando a consulta acaba</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Vem de: o plano da Clara e a pergunta "e depois da consulta?" (M1-07). Fecha as quatro frentes. Leva para: se os dados ficam no atendimento, o que o RH vê (M1-09).</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>Colaboradores; RH</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>Para que serve a pulseira? Vão me vigiar?</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>Explicar o acompanhamento com tecnologia e a regra de privacidade</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>Carrossel</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>Carrossel explicativo com a objeção no título ("vão me vigiar?"): responde a dúvida mais comum antes que ela vire resistência.</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>Instagram + LinkedIn</t>
+        </is>
+      </c>
+      <c r="R12" s="7" t="inlineStr">
+        <is>
+          <t>FairJob</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>A smartband e a bioimpedância ajudam a olhar, junto com a pessoa, como foram as últimas semanas. Os dados ficam no atendimento; o RH vê só o grupo.</t>
+        </is>
+      </c>
+      <c r="T12" s="7" t="inlineStr">
+        <is>
+          <t>Cartilha do Escritório do Cuidado.</t>
+        </is>
+      </c>
+      <c r="U12" s="7" t="inlineStr">
+        <is>
+          <t>[PENDENTE] Quais dados a smartband registra e se todos os atendidos usam a pulseira (instagram/posts/wearables/README.md).</t>
+        </is>
+      </c>
+      <c r="V12" s="7" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+      <c r="W12" s="7" t="n"/>
+      <c r="X12" s="7" t="n"/>
+      <c r="Y12" s="7" t="inlineStr">
+        <is>
+          <t>Arte pronta em instagram/posts/wearables (8 slides). Capa: foto de pulso sem rosto (modelo com autorização, fora das empresas-clientes) ou capa só tipográfica.</t>
+        </is>
+      </c>
+      <c r="Z12" s="7" t="n"/>
+      <c r="AA12" s="7" t="inlineStr">
+        <is>
+          <t>Antes: M1-10 (ordem de 12/10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>M1-09</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Mês 1</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="17">
+        <f>$D$2+(C13-1)*7+1</f>
+        <v/>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
           <t>Projetos, eventos e entregas</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>NR-1</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Prova</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>Entregas para o RH</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Tecnologia a favor da pessoa</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>O que o RH vê (e o que não vê)</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>Vem de: "os dados ficam no atendimento; o RH vê só o grupo" (M1-08). Muda o ponto de vista: da pessoa para a empresa. Leva para: por que isso não é mais um benefício (M1-10).</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>RH; Risco e Compliance</t>
+        </is>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>O que eu recebo para acompanhar o programa? Vou ver dados individuais?</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>Mostrar a entrega para a empresa e a regra de privacidade</t>
+        </is>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>Vídeo</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>Gravação de tela de um painel genérico, com texto na tela: mostra o produto de verdade sem expor ninguém e responde a dúvida que trava a decisão do RH.</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>Instagram + LinkedIn</t>
+        </is>
+      </c>
+      <c r="R13" s="7" t="inlineStr">
+        <is>
+          <t>FairJob; fairdata</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>O RH acompanha o cuidado por indicadores do grupo, anonimizados e integrados à fairdata. O que cada pessoa conta fica no atendimento.</t>
+        </is>
+      </c>
+      <c r="T13" s="7" t="inlineStr">
+        <is>
+          <t>Posicionamento Fair Health v3.2 (fairdata).</t>
+        </is>
+      </c>
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>Time confirma quais indicadores entram no relatório. Painel com dados fictícios e aviso "dados ilustrativos". Não prometer conformidade com a NR-1.</t>
+        </is>
+      </c>
+      <c r="V13" s="7" t="inlineStr">
+        <is>
+          <t>Pauta proposta</t>
+        </is>
+      </c>
+      <c r="W13" s="7" t="n"/>
+      <c r="X13" s="7" t="inlineStr">
+        <is>
+          <t>Reel de 25 a 30 s, gravação de tela.
+0–3 s: "Os dados de cada pessoa ficam no atendimento. Então, o que o RH vê?"
+3–15 s: rolagem pelo painel (adesão, retorno, temas mais procurados), dados ilustrativos.
+15–22 s: "O que o RH não vê: o que cada pessoa contou."
+22–30 s: "Indicadores do grupo para cuidar antes." + logo.</t>
+        </is>
+      </c>
+      <c r="Y13" s="7" t="inlineStr">
+        <is>
+          <t>Modelo M9. Painel montado com dados fictícios, moldura de navegador ou de notebook.</t>
+        </is>
+      </c>
+      <c r="Z13" s="7" t="n"/>
+      <c r="AA13" s="7" t="inlineStr">
+        <is>
+          <t>Antes: M1-07 (ordem de 12/10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>M1-10</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Mês 1</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="17">
+        <f>$D$2+(C14-1)*7+2</f>
+        <v/>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Institucional</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Liderança Bem-Estar</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Prova</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>Tese da marca</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Não é benefício. É infraestrutura de cuidado.</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>Vem de: o RH acompanha por indicadores do grupo (M1-09). Junta tudo o que veio antes numa frase. Leva para: e as pessoas usam? (M1-11).</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>RH; RI e C-Level</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>Isso é mais um benefício para a lista? Por que seria diferente do que já temos?</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>Fixar a frase-tese e posicionar a categoria sem citar concorrentes</t>
+        </is>
+      </c>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>Carrossel</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>Carrossel comparativo de duas colunas (isto × aquilo): a diferença fica clara em segundos e o post é salvo e repassado ao decisor.</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>Instagram + LinkedIn</t>
+        </is>
+      </c>
+      <c r="R14" s="7" t="inlineStr">
+        <is>
+          <t>FairJob</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>Benefício é algo que a pessoa usa se lembrar. Infraestrutura de cuidado está dentro da empresa todo dia, começa antes do problema e tem gente acompanhando.</t>
+        </is>
+      </c>
+      <c r="T14" s="7" t="inlineStr">
+        <is>
+          <t>Posicionamento Fair Health v3.2 (diferenciais).</t>
+        </is>
+      </c>
+      <c r="U14" s="7" t="inlineStr">
+        <is>
+          <t>Não citar marcas de terceiros nem operadoras. Sem números.</t>
+        </is>
+      </c>
+      <c r="V14" s="7" t="inlineStr">
+        <is>
+          <t>Pauta proposta</t>
+        </is>
+      </c>
+      <c r="W14" s="7" t="n"/>
+      <c r="X14" s="7" t="inlineStr">
+        <is>
+          <t>6 slides.
+1 Capa: "Não é benefício. É infraestrutura de cuidado."
+2 Benefício: a pessoa usa se lembrar. Infraestrutura: está lá todo dia, dentro da empresa.
+3 Benefício: espera o problema aparecer. Infraestrutura: começa antes.
+4 Benefício: é um cartão. Infraestrutura: é gente acompanhando, com um plano para cada pessoa.
+5 Benefício: termina na adesão. Infraestrutura: o RH acompanha o cuidado por indicadores do grupo.
+6 "Infraestrutura só faz sentido se as pessoas usam. No próximo post, o que vimos numa indústria que atendemos." (ponte)</t>
+        </is>
+      </c>
+      <c r="Y14" s="7" t="inlineStr">
+        <is>
+          <t>Modelo M1 na capa e comparativo em duas colunas (Tiffany × verde-escuro) nos slides 2 a 5.</t>
+        </is>
+      </c>
+      <c r="Z14" s="7" t="n"/>
+      <c r="AA14" s="7" t="inlineStr">
+        <is>
+          <t>Antes: M1-06 (ordem de 12/10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>M1-11</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Mês 1</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="17">
+        <f>$D$2+(C15-1)*7+3</f>
+        <v/>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Projetos, eventos e entregas</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Liderança Bem-Estar</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Prova</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Adesão (número liberado)</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Quando o cuidado está perto, as pessoas voltam</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>Vem de: "infraestrutura só faz sentido se as pessoas usam" (M1-10). Prova com o número liberado. Leva para: por que as pessoas voltam, em que a gente acredita (M1-12).</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>RH; Diretoria financeira</t>
+        </is>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>Programa de saúde que ninguém usa é custo. As pessoas usam isso de verdade?</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>Provar adesão com número liberado, contado como cuidado e não como resultado</t>
+        </is>
+      </c>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>Vídeo</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>Número contado como história: primeiro a cena de cuidado, depois o número, em tom calmo. É a prova que o RH leva para a diretoria, sem cara de anúncio.</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>Instagram + LinkedIn</t>
+        </is>
+      </c>
+      <c r="R15" s="7" t="inlineStr">
+        <is>
+          <t>FairJob</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>Quando o cuidado está perto e começa por uma conversa, as pessoas voltam: numa indústria atendida, 8 em cada 10 pessoas voltaram para mais de um atendimento.</t>
+        </is>
+      </c>
+      <c r="T15" s="7" t="inlineStr">
+        <is>
+          <t>Dados internos de um cliente do setor industrial, 1º semestre de 2026 (liberados; ver aba Fontes). Sempre agregado e sem o nome da empresa.</t>
+        </is>
+      </c>
+      <c r="U15" s="7" t="inlineStr">
+        <is>
+          <t>Nenhum nome real de pessoa ou empresa no post (decisão de 09/10). Usar "uma indústria". Número suave: cuidado primeiro, número como contexto, fonte visível e discreta (aba Ciência).</t>
+        </is>
+      </c>
+      <c r="V15" s="7" t="inlineStr">
+        <is>
+          <t>Pauta proposta</t>
+        </is>
+      </c>
+      <c r="W15" s="7" t="n"/>
+      <c r="X15" s="7" t="inlineStr">
+        <is>
+          <t>Reel de 18 a 22 s, tipografia e números suaves.
+0–4 s: "Ninguém volta a um lugar onde não se sentiu cuidado."
+4–9 s: "Numa indústria que atendemos, no primeiro semestre de 2026..."
+9–14 s: "8 em cada 10 pessoas voltaram para mais de um atendimento." (número em destaque, sem exagero)
+14–18 s: em texto menor: "A adesão chegou a 98%."
+18–22 s: "Cuidado que as pessoas procuram." + fonte discreta + logo.</t>
+        </is>
+      </c>
+      <c r="Y15" s="7" t="inlineStr">
+        <is>
+          <t>Modelo M6 (dado com fonte) animado, em ritmo lento. Número em verde-escuro, nunca em vermelho; sem setas para cima nem efeito de "conquista".</t>
+        </is>
+      </c>
+      <c r="Z15" s="7" t="n"/>
+      <c r="AA15" s="7" t="inlineStr">
+        <is>
+          <t>Antes: M1-09 (ordem de 12/10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>M1-12</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Mês 1</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="17">
+        <f>$D$2+(C16-1)*7+4</f>
+        <v/>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Institucional</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Apresentação</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Prova</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Em que a gente acredita (manifesto do slogan)</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Fazemos o certo pelos motivos certos</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>Vem de: "quando o cuidado está perto, as pessoas voltam" (M1-11). Leva para: o capítulo 4, um convite para cada pessoa: quem é cuidado, quem lidera e quem decide (M1-13).</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>RH; Colaboradores; RI e C-Level</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>Por que confiar nessa marca? O que move a fairhealth?</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>Dizer em que a marca acredita e fechar o capítulo 3 com o slogan</t>
+        </is>
+      </c>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>Carrossel</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>Carrossel de crenças, uma por slide: depois da prova, explica o porquê. É a peça que transforma o slogan em compromisso.</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>Instagram + LinkedIn</t>
+        </is>
+      </c>
+      <c r="R16" s="7" t="inlineStr">
+        <is>
+          <t>FairJob</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>A pessoa no centro, não o protocolo. Proximidade gera adesão. Tecnologia a serviço das pessoas. Cuidar antes. E o retorno para a empresa é consequência, não ponto de partida.</t>
+        </is>
+      </c>
+      <c r="T16" s="7" t="inlineStr">
+        <is>
+          <t>Essência da fairhealth (instagram/essencia.md: "Em que a gente acredita", a partir do site e da apresentação institucional).</t>
+        </is>
+      </c>
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>Sócios aprovam as crenças como manifesto da marca. Sem números. Não citar operadoras nem marcas de terceiros.</t>
+        </is>
+      </c>
+      <c r="V16" s="7" t="inlineStr">
+        <is>
+          <t>Pauta proposta</t>
+        </is>
+      </c>
+      <c r="W16" s="7" t="inlineStr">
+        <is>
+          <t>Fazemos o certo pelos motivos certos.
+O que a gente acredita, em cinco frases:
+A pessoa no centro, não o protocolo.
+Proximidade gera adesão: por isso o cuidado fica dentro da empresa.
+Tecnologia serve às pessoas, não o contrário.
+Cuidar antes, e não só depois que a doença aparece.
+O retorno para a empresa é consequência, não ponto de partida.
+É por isso que, numa indústria que atendemos, as pessoas voltaram. Não porque foram chamadas, mas porque se sentiram cuidadas.
+Na semana que vem, um convite para cada um: para quem é cuidado, para quem lidera e para quem decide.
+#fairhealth #saudecorporativa #medicinadoestilodevida #escritoriodocuidado #gestaodepessoas</t>
+        </is>
+      </c>
+      <c r="X16" s="7" t="inlineStr">
+        <is>
+          <t>7 slides.
+1 Capa: "Fazemos o certo pelos motivos certos."
+2 A pessoa no centro, não o protocolo.
+3 Proximidade gera adesão: a maior barreira ao cuidado é tempo e acesso.
+4 Tecnologia serve às pessoas, não o contrário. Cuidado presencial e relação genuína.
+5 Cuidar antes.
+6 O retorno para a empresa é consequência, não ponto de partida.
+7 "O que é importante para você?" + logo.</t>
+        </is>
+      </c>
+      <c r="Y16" s="7" t="inlineStr">
+        <is>
+          <t>Modelo M2 (uma frase por slide), tipografia Raleway, fio contínuo atravessando os slides. Sem foto.</t>
+        </is>
+      </c>
+      <c r="Z16" s="7" t="n"/>
+      <c r="AA16" s="7" t="inlineStr">
+        <is>
+          <t>Peça nova (13/10) para fechar o capítulo 3. Substitui, no Mês 1, as duas peças do artigo sobre NR-1, que foram para o Mês 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>M1-13</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Mês 1</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="17">
+        <f>$D$2+(C17-1)*7+0</f>
+        <v/>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Liderança Bem-Estar</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Convite</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Pilar: sono</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Pilares da MEV (1/7: sono)</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Dormir não é tempo perdido</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>Vem de: as crenças e o anúncio do capítulo 4 (M1-12). Primeiro convite: para quem é cuidado. Retoma a Clara (M1-07): a primeira ação do plano dela era dormir 30 minutos mais cedo. Leva para: o convite para quem lidera (M1-14). Abre a série dos pilares, que segue no Mês 2.</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>Colaboradores</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>Por que eu acordo cansado? O que dá para mudar na rotina?</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>Educar sobre o pilar sono e convidar o colaborador a procurar o Escritório</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>Vídeo</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>Reel de "3 hábitos" com texto na tela sobre imagens de banco: dica prática e salvável, sem rosto e sem gravar nas empresas.</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="R17" s="7" t="inlineStr">
+        <is>
+          <t>FairJob</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>Dormir não é tempo perdido. A faixa saudável para adultos fica entre 7 e 9 horas por noite. No Escritório do Cuidado, o sono entra no plano a partir da sua rotina real.</t>
+        </is>
+      </c>
+      <c r="T17" s="7" t="inlineStr">
+        <is>
+          <t>Guia "Saúde mental: o cuidado no dia a dia" (higiene do sono; OMS, APA, IPq-USP). Hafner M. et al. Why sleep matters: the economic costs of insufficient sleep. RAND Europe, 2016 (RR-1791). https://www.rand.org/news/press/2016/11/30.html</t>
+        </is>
+      </c>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>Responsável médica valida as orientações. Sem promessa clínica. Número suave: cuidado primeiro, número como contexto, fonte visível e discreta (aba Ciência).</t>
+        </is>
+      </c>
+      <c r="V17" s="7" t="inlineStr">
+        <is>
+          <t>Pauta proposta</t>
+        </is>
+      </c>
+      <c r="W17" s="7" t="n"/>
+      <c r="X17" s="7" t="inlineStr">
+        <is>
+          <t>Reel de 24 a 29 s.
+0–3 s: "Acorda cansado mesmo dormindo?"
+3–6 s: "Lembra da Clara? A primeira ação do plano dela era dormir 30 minutos mais cedo." (história ilustrativa)
+6–9 s: em texto calmo: "Para adultos, o sono saudável fica entre 7 e 9 horas." (fonte discreta: RAND Europe, 2016)
+9–21 s: 3 hábitos, um por cena (tela antes de dormir, horário regular, cafeína à tarde).
+21–29 s: "Se o cansaço não passa, conversa com a gente no Escritório do Cuidado." + logo.
+Legenda (opcional, para o RH no LinkedIn): um estudo da RAND Europe estimou que a falta de sono custa mais de 1 milhão de dias de trabalho por ano só nos Estados Unidos.</t>
+        </is>
+      </c>
+      <c r="Y17" s="7" t="inlineStr">
+        <is>
+          <t>Modelo M9 com etiqueta "PILARES · SONO". Imagens de banco (quarto, celular à noite), sem rosto identificável.</t>
+        </is>
+      </c>
+      <c r="Z17" s="7" t="n"/>
+      <c r="AA17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>M1-14</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Mês 1</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="17">
+        <f>$D$2+(C18-1)*7+1</f>
+        <v/>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Institucional</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Liderança Bem-Estar</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Convite</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>A pergunta (com a recomendação da OMS)</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Ciência no cuidado</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Uma pergunta que todo líder pode fazer</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Vem de: o convite para quem é cuidado (M1-13). Segundo convite: para quem lidera, com a mesma pergunta da marca. Leva para: a ciência por trás do cuidado (M1-15).</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>Lideranças; RH</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>Como a liderança pode cuidar do time no dia a dia, sem ser médica nem psicóloga?</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>Levar a pergunta da marca para a liderança, com o respaldo da recomendação da OMS, e gerar conversa</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>Carrossel</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>Carrossel de ciência aplicada: a recomendação de uma fonte respeitada (OMS) vira um gesto simples que o líder pode repetir. Fecha com pergunta aberta, que gera comentários.</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>Instagram + LinkedIn</t>
+        </is>
+      </c>
+      <c r="R18" s="7" t="inlineStr">
+        <is>
+          <t>FairJob</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>A OMS recomenda preparar as lideranças para prevenir ambientes de estresse e acolher quem está em sofrimento. Um bom começo cabe numa pergunta: o que é importante para você?</t>
+        </is>
+      </c>
+      <c r="T18" s="7" t="inlineStr">
+        <is>
+          <t>OMS. Guidelines on mental health at work, 28/09/2022 (com a OIT: policy brief "Mental health at work"). https://www.who.int/news/item/28-09-2022-who-and-ilo-call-for-new-measures-to-tackle-mental-health-issues-at-work</t>
+        </is>
+      </c>
+      <c r="U18" s="7" t="inlineStr">
+        <is>
+          <t>Conferir a redação da recomendação nas diretrizes da OMS. O líder não substitui o cuidado clínico: deixar claro onde pedir ajuda.</t>
+        </is>
+      </c>
+      <c r="V18" s="7" t="inlineStr">
+        <is>
+          <t>Pauta proposta</t>
+        </is>
+      </c>
+      <c r="W18" s="7" t="n"/>
+      <c r="X18" s="7" t="inlineStr">
+        <is>
+          <t>6 slides.
+1 Capa: "Uma pergunta que todo líder pode fazer."
+2 Ontem, o convite foi para quem é cuidado. Hoje, para quem lidera. Em 2022, a OMS publicou suas primeiras diretrizes sobre saúde mental no trabalho. Uma das recomendações: preparar as lideranças.
+3 Para quê? Para prevenir ambientes de estresse e acolher quem está em sofrimento.
+4 Não é virar terapeuta. É perguntar, ouvir e saber para onde encaminhar.
+5 Um bom começo: "O que é importante para você?", a mesma pergunta com que esta história começou.
+6 Líder, quando foi a última vez que você fez essa pergunta? Conta nos comentários. Fonte: OMS, 2022.
+Stories no mesmo dia com caixa de perguntas.</t>
+        </is>
+      </c>
+      <c r="Y18" s="7" t="inlineStr">
+        <is>
+          <t>Modelo M1 na capa e M2 nos demais; fonte no rodapé (M6).</t>
+        </is>
+      </c>
+      <c r="Z18" s="7" t="n"/>
+      <c r="AA18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>M1-15</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Mês 1</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="17">
+        <f>$D$2+(C19-1)*7+3</f>
+        <v/>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Liderança Bem-Estar</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Convite</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Ciência: estilo de vida e diabetes (Dia Mundial do Diabetes, 14/11)</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Ciência no cuidado</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Estilo de vida também é tratamento sério</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Vem de: o convite para quem lidera (M1-14). Mostra, com um estudo clássico, por que o cuidado começa pela rotina, o fio do mês inteiro. Leva para: como esse cuidado chega à sua empresa (M1-16).</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>Colaboradores; RH; Medicina do Trabalho</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>Mudar hábitos faz diferença de verdade ou é só conselho?</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>Mostrar a base científica da MEV com um estudo clássico, na véspera do Dia Mundial do Diabetes</t>
+        </is>
+      </c>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>Carrossel</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>Carrossel "o que a ciência diz": um estudo, uma ideia, a fonte completa. Conecta uma data do calendário ao nosso trabalho com evidência, sem oportunismo.</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>Instagram + LinkedIn</t>
+        </is>
+      </c>
+      <c r="R19" s="7" t="inlineStr">
+        <is>
+          <t>FairJob</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>Num estudo clássico, publicado no New England Journal of Medicine, mudanças de estilo de vida reduziram em 58% os novos casos de diabetes tipo 2 em pessoas com risco, em comparação com o placebo. É por isso que o nosso cuidado começa pela rotina.</t>
+        </is>
+      </c>
+      <c r="T19" s="7" t="inlineStr">
+        <is>
+          <t>Diabetes Prevention Program Research Group. Reduction in the incidence of type 2 diabetes with lifestyle intervention or metformin. N Engl J Med. 2002;346(6):393-403. doi:10.1056/NEJMoa012512</t>
+        </is>
+      </c>
+      <c r="U19" s="7" t="inlineStr">
+        <is>
+          <t>Responsável médica valida a leitura do estudo. Deixar claro que o estudo foi com adultos com pré-diabetes (risco aumentado) e que não é promessa individual. Número suave: cuidado primeiro, número como contexto, fonte visível e discreta (aba Ciência).</t>
+        </is>
+      </c>
+      <c r="V19" s="7" t="inlineStr">
+        <is>
+          <t>Pauta proposta</t>
+        </is>
+      </c>
+      <c r="W19" s="7" t="n"/>
+      <c r="X19" s="7" t="inlineStr">
+        <is>
+          <t>7 slides.
+1 Capa: "Estilo de vida também é tratamento sério."
+2 Neste sábado, 14/11, é o Dia Mundial do Diabetes. Vale lembrar de um estudo que mudou a forma de cuidar.
+3 Mais de 3 mil adultos com risco aumentado de diabetes tipo 2 foram acompanhados por quase 3 anos.
+4 Quem mudou a rotina (alimentação e 150 minutos de atividade física por semana) teve 58% menos casos novos do que o grupo placebo.
+5 Em texto menor: mais do que o grupo que recebeu medicamento (31%).
+6 Não é promessa: é a ciência dizendo que a rotina importa. Por isso o nosso cuidado começa nela, com um plano feito para cada pessoa.
+7 "Amanhã: como esse cuidado chega à sua empresa." Fonte completa: Diabetes Prevention Program, N Engl J Med, 2002.</t>
+        </is>
+      </c>
+      <c r="Y19" s="7" t="inlineStr">
+        <is>
+          <t>Modelo M6 (dado com fonte) suave nos slides 4 e 5, M2 nos demais. Números em verde-escuro, sem destaque alarmista.</t>
+        </is>
+      </c>
+      <c r="Z19" s="7" t="n"/>
+      <c r="AA19" s="7" t="inlineStr">
+        <is>
+          <t>Antes: M1-16 (ordem de 12/10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>M1-16</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Mês 1</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="17">
+        <f>$D$2+(C20-1)*7+4</f>
+        <v/>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Projetos, eventos e entregas</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Apresentação</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Convite</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Como começa numa empresa</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Como chega a uma empresa</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Uma pergunta, um hospital, um escritório. E agora, a sua empresa</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Vem de: a ciência por trás do cuidado (M1-15). Fecha o mês recontando a história (M1-01, M1-02, M1-05 e M1-07) e faz o convite para quem decide. Leva para: o próximo capítulo, "Prevenção também é investimento" (M2-01, 16/11).</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>RH; Diretoria financeira</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>Quero isso na minha empresa. Por onde começa?</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>Fechar o capítulo do mês: relembrar a história em poucos segundos e deixar claro o primeiro passo para o RH</t>
+        </is>
+      </c>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>Vídeo</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>Reel de fechamento: recapitula o mês em quatro frases (quem acompanhou reconhece cada post) e termina no caminho comercial. É o terceiro convite: para quem decide.</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>Instagram + LinkedIn</t>
+        </is>
+      </c>
+      <c r="R20" s="7" t="inlineStr">
+        <is>
+          <t>FairJob</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>Uma pergunta, um hospital, um escritório dentro da empresa, um plano para cada pessoa. Para levar esse cuidado à sua empresa: diagnóstico, proposta personalizada e implementação. Fale com a gente pelo direct.</t>
+        </is>
+      </c>
+      <c r="T20" s="7" t="inlineStr">
+        <is>
+          <t>Executive Summary (etapas comerciais).</t>
+        </is>
+      </c>
+      <c r="U20" s="7" t="inlineStr">
+        <is>
+          <t>"Diagnóstico" sem "gratuito" (decisão de 12/10). Não citar prazos de cada etapa sem confirmação. Confirmar quem responde o direct.</t>
+        </is>
+      </c>
+      <c r="V20" s="7" t="inlineStr">
+        <is>
+          <t>Pauta proposta</t>
+        </is>
+      </c>
+      <c r="W20" s="7" t="n"/>
+      <c r="X20" s="7" t="inlineStr">
+        <is>
+          <t>Reel de 25 a 30 s, motion.
+0–8 s: recapitulação, uma frase por corte: "Uma pergunta." · "Um hospital." · "Um escritório dentro da empresa." · "Um plano para cada pessoa."
+8–11 s: "E agora, a sua empresa."
+11–15 s: PASSO 1 · Diagnóstico
+15–19 s: PASSO 2 · Proposta personalizada
+19–23 s: PASSO 3 · Implementação e primeiros atendimentos
+23–30 s: "Fale com a gente pelo direct." + "Fazemos o certo pelos motivos certos." + logo.</t>
+        </is>
+      </c>
+      <c r="Y20" s="7" t="inlineStr">
+        <is>
+          <t>Modelo M2 (passos) animado e M1 no fim. Os três passos repetem o último slide do M1-04, de propósito.</t>
+        </is>
+      </c>
+      <c r="Z20" s="7" t="n"/>
+      <c r="AA20" s="7" t="inlineStr">
+        <is>
+          <t>Antes: M1-15 (ordem de 12/10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>M2-01</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Mês 2</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" s="17">
+        <f>$D$2+(C21-1)*7+0</f>
+        <v/>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Projetos, eventos e entregas</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Stop Loss</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Prova</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Ciência: prevenção como investimento</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Ciência no cuidado</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Prevenção também é investimento</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Vem de: o fechamento do Mês 1 (M1-16) e a crença "o retorno é consequência, não ponto de partida" (M1-12). Leva para: o capítulo da NR-1 (M2-02).</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>RH; Diretoria financeira</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>Prevenção dá retorno para a empresa ou é só mais um custo?</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>Mostrar, com estudos externos e a fonte visível, que prevenção também é investimento</t>
+        </is>
+      </c>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>Foto única</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>A arte já está pronta: é o slide de números que saiu do carrossel "O que é a fairhealth" para ele caber em 10 fotos. Um post só dele dá espaço para explicar cada estudo com calma.</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>Instagram + LinkedIn</t>
+        </is>
+      </c>
+      <c r="R21" s="7" t="inlineStr">
+        <is>
+          <t>FairJob</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>O que os estudos apontam: −28% de absenteísmo (Harvard Business Review, 2022) e −22% de custos com saúde (SHRM, 2023).</t>
+        </is>
+      </c>
+      <c r="T21" s="7" t="inlineStr">
+        <is>
+          <t>Harvard Business Review (2022); SHRM (2023). Números oficiais desde 25/09 (instagram/voice.md).</t>
+        </is>
+      </c>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>Confirmar o que cada estudo mediu (tipo de programa e população) antes de publicar. São estudos externos, nunca resultado da Fair Health. Número suave: cuidado primeiro, número como contexto, fonte visível e discreta (aba Ciência).</t>
+        </is>
+      </c>
+      <c r="V21" s="7" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+      <c r="W21" s="7" t="inlineStr">
+        <is>
+          <t>Prevenção também é investimento.
+Cuidar antes faz bem para as pessoas. E os estudos mostram que também faz diferença para a empresa:
+−28% de absenteísmo (Harvard Business Review, 2022)
+−22% de custos com saúde (SHRM, 2023)
+São números de estudos externos, não uma promessa de resultado.
+É esse o trabalho da fairhealth: medicina preventiva, dentro da empresa, com um plano de cuidado para cada pessoa.
+Quer conversar sobre isso na sua empresa? Fale com a gente pelo direct.
+#fairhealth #saudecorporativa #medicinapreventiva #absenteismo #gestaodepessoas</t>
+        </is>
+      </c>
+      <c r="X21" s="7" t="inlineStr">
+        <is>
+          <t>Foto única 1080x1350, já pronta. Se quisermos explicar melhor cada estudo, vira um carrossel curto: capa, um número por slide com a fonte, fechamento.</t>
+        </is>
+      </c>
+      <c r="Y21" s="7" t="inlineStr">
+        <is>
+          <t>Canva: design DAHX17FZzNQ, "Prevenção também é investimento · post M2-01" (https://www.canva.com/d/E6Gp2hFDhnNw1ME). Tirar as bolinhas de paginação e a etiqueta do carrossel. Repositório: instagram/posts/o-que-e-a-fairhealth/png-v10/d10.png.</t>
+        </is>
+      </c>
+      <c r="Z21" s="7" t="n"/>
+      <c r="AA21" s="7" t="inlineStr">
+        <is>
+          <t>Decisão da Nina (12/10): o slide de números saiu do carrossel "O que é a fairhealth" (limite de 10 fotos do Instagram) e vira um post separado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>M2-02</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Mês 2</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" s="17">
+        <f>$D$2+(C22-1)*7+1</f>
+        <v/>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Projetos, eventos e entregas</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>NR-1</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>Dor</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>Na imprensa: artigo sobre riscos psicossociais</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>Saúde mental é de todos (1/2)</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>O trabalho não é o único vilão</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr">
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>Abre o capítulo da NR-1 no Mês 2. Vem de: prevenção também é investimento (M2-01). A ligação com a marca fica no último slide: a parte da empresa começa antes. Leva para: a pergunta maior (M2-03).</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>RH; Lideranças; Risco e Compliance</t>
         </is>
       </c>
-      <c r="L8" s="7" t="inlineStr">
+      <c r="M22" s="7" t="inlineStr">
         <is>
           <t>A NR-1 colocou os riscos psicossociais na conta da empresa. O que é responsabilidade da empresa e o que não é?</t>
         </is>
       </c>
-      <c r="M8" s="7" t="inlineStr">
+      <c r="N22" s="7" t="inlineStr">
         <is>
           <t>Trazer a NR-1 com uma visão madura e transferir a autoridade da publicação para a marca</t>
         </is>
       </c>
-      <c r="N8" s="7" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
         <is>
           <t>Carrossel</t>
         </is>
       </c>
-      <c r="O8" s="7" t="inlineStr">
+      <c r="P22" s="7" t="inlineStr">
         <is>
           <t>Carrossel-resumo de artigo publicado: formato muito compartilhado entre profissionais de RH. Leva a autoridade do veículo para a marca, sem citar pessoas.</t>
         </is>
       </c>
-      <c r="P8" s="7" t="inlineStr">
+      <c r="Q22" s="7" t="inlineStr">
         <is>
           <t>Instagram + LinkedIn</t>
         </is>
       </c>
-      <c r="Q8" s="7" t="inlineStr">
+      <c r="R22" s="7" t="inlineStr">
         <is>
           <t>FairJob; RH Pra Você (marcar o veículo, se fizer sentido)</t>
         </is>
       </c>
-      <c r="R8" s="7" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>A NR-1 formalizou que o trabalho pode adoecer, e a empresa responde pelo ambiente que constrói. Mas saúde mental é multifatorial: é, ao mesmo tempo, de cada um e de todos.</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="T22" s="7" t="inlineStr">
         <is>
           <t>Artigo "Riscos psicossociais no ambiente de trabalho e saúde", RH Pra Você, 25/09/2026. https://rhpravoce.com.br/colab/riscos-psicossociais-no-ambiente-de-trabalho-2 Dado do slide 4: Global Burden of Disease (citado no artigo).</t>
         </is>
       </c>
-      <c r="T8" s="7" t="inlineStr">
+      <c r="U22" s="7" t="inlineStr">
         <is>
           <t>Citar só o artigo (título e veículo), sem o nome do autor. Nenhum nome real de pessoa ou empresa no post (decisão de 09/10). Conferir as citações literais com o artigo. Número suave: cuidado primeiro, número como contexto, fonte visível e discreta (aba Ciência).</t>
         </is>
       </c>
-      <c r="U8" s="7" t="inlineStr">
+      <c r="V22" s="7" t="inlineStr">
         <is>
           <t>Pauta proposta</t>
         </is>
       </c>
-      <c r="V8" s="7" t="inlineStr">
+      <c r="W22" s="7" t="inlineStr">
         <is>
           <t>O trabalho pode adoecer. Mas não é o único vilão.
 Desde maio de 2026, a NR-1 exige que as empresas identifiquem, avaliem e gerenciem os riscos psicossociais. É um avanço necessário: assédio, excesso de pressão, jornadas inadequadas e lideranças despreparadas têm impacto real na saúde mental.
@@ -2579,7 +4495,7 @@
 #fairhealth #nr1 #riscospsicossociais #saudementalnotrabalho #rh</t>
         </is>
       </c>
-      <c r="W8" s="7" t="inlineStr">
+      <c r="X22" s="7" t="inlineStr">
         <is>
           <t>8 slides.
 1 Capa: "O trabalho pode adoecer. Mas não é o único vilão." + "Da RH Pra Você".
@@ -2592,1597 +4508,150 @@
 8 A parte da empresa começa antes: um cuidado dentro do trabalho, que começa com uma pergunta. Link nos stories.</t>
         </is>
       </c>
-      <c r="X8" s="7" t="inlineStr">
+      <c r="Y22" s="7" t="inlineStr">
         <is>
           <t>Modelo M8 (citação) nos slides 4 e 7 e M2 nos demais. Sem foto. Stories no mesmo dia com o link do artigo.</t>
         </is>
       </c>
-      <c r="Y8" s="7" t="n"/>
-      <c r="Z8" s="7" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>M1-05</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Mês 1</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" s="17">
-        <f>$D$2+(C9-1)*7+0</f>
+      <c r="Z22" s="7" t="n"/>
+      <c r="AA22" s="7" t="inlineStr">
+        <is>
+          <t>Antes: M1-04 (ordem de 12/10). Saiu do Mês 1 em 13/10: o Mês 1 conta a história da marca, e o Mês 2 é o mês da NR-1. Data e posição a revisar quando o Mês 2 for montado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>M2-03</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Mês 2</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" s="17">
+        <f>$D$2+(C23-1)*7+3</f>
         <v/>
       </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Liderança Bem-Estar</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>Virada</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>Medicina do Estilo de Vida</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>Pilares da MEV (abertura)</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>Medicina do Estilo de Vida em 1 minuto</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>Colaboradores; RH</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>O que é Medicina do Estilo de Vida? É dieta? É academia?</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="inlineStr">
-        <is>
-          <t>Apresentar a base científica do cuidado e abrir a série dos pilares</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>Vídeo</t>
-        </is>
-      </c>
-      <c r="O9" s="7" t="inlineStr">
-        <is>
-          <t>Explicador animado com ícones (motion): conceito novo explicado em 1 minuto, sem rosto. Responde ao mito "é só dieta e academia".</t>
-        </is>
-      </c>
-      <c r="P9" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Projetos, eventos e entregas</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>NR-1</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Prova</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Na imprensa: artigo sobre riscos psicossociais</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Saúde mental é de todos (2/2)</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>A pergunta maior</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Vem de: o artigo sobre riscos psicossociais (M2-02). Liga a pergunta do artigo à pergunta da marca ("o que é importante para você?").</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>RH; Lideranças</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>Como olhar para a saúde mental do time sem simplificar?</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>Reaproveitar o artigo com uma frase forte e reforçar a autoridade</t>
+        </is>
+      </c>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>Foto única</t>
+        </is>
+      </c>
+      <c r="P23" s="7" t="inlineStr">
+        <is>
+          <t>Card de citação: uma frase forte, fácil de compartilhar nos stories e no LinkedIn. Reaproveita o artigo sem repetir o carrossel.</t>
+        </is>
+      </c>
+      <c r="Q23" s="7" t="inlineStr">
         <is>
           <t>Instagram + LinkedIn</t>
         </is>
       </c>
-      <c r="Q9" s="7" t="inlineStr">
+      <c r="R23" s="7" t="inlineStr">
         <is>
           <t>FairJob</t>
         </is>
       </c>
-      <c r="R9" s="7" t="inlineStr">
-        <is>
-          <t>Seis pilares, uma pessoa inteira: alimentação, atividade física, sono, manejo do estresse, relacionamentos e evitar substâncias de risco. O plano olha para todos, a partir da rotina real.</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>ACLM (American College of Lifestyle Medicine), 6 pilares; CBMEV (Colégio Brasileiro de Medicina do Estilo de Vida); cartilha do Escritório do Cuidado.</t>
-        </is>
-      </c>
-      <c r="T9" s="7" t="inlineStr">
-        <is>
-          <t>6 pilares, sem espiritualidade (decisão de 09/10, ainda a confirmar). Responsável médica valida a definição de MEV e os nomes dos pilares.</t>
-        </is>
-      </c>
-      <c r="U9" s="7" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>"Antes de perguntar apenas o que o trabalho está fazendo com a saúde mental das pessoas, deveríamos fazer uma pergunta maior: o que a nossa forma de viver em sociedade está fazendo com a saúde mental das pessoas?"</t>
+        </is>
+      </c>
+      <c r="T23" s="7" t="inlineStr">
+        <is>
+          <t>Artigo "Riscos psicossociais no ambiente de trabalho e saúde", RH Pra Você, 25/09/2026. https://rhpravoce.com.br/colab/riscos-psicossociais-no-ambiente-de-trabalho-2</t>
+        </is>
+      </c>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>Citação literal conferida com o artigo. Crédito só ao artigo e ao veículo, sem nome do autor. Nenhum nome real de pessoa ou empresa no post (decisão de 09/10).</t>
+        </is>
+      </c>
+      <c r="V23" s="7" t="inlineStr">
         <is>
           <t>Pauta proposta</t>
         </is>
       </c>
-      <c r="V9" s="7" t="n"/>
-      <c r="W9" s="7" t="inlineStr">
-        <is>
-          <t>Reel de 45 a 60 s, motion com ícones, voz em off.
-0–3 s: "Medicina do Estilo de Vida é dieta e academia? Não só."
-3–10 s: definição curta, com fonte na tela.
-10–40 s: os 6 pilares, um ícone e uma frase por pilar: alimentação · atividade física · sono · manejo do estresse · relacionamentos · evitar substâncias de risco.
-40–50 s: "Os pilares conversam entre si: o plano olha para a pessoa inteira."
-50–60 s: "No Escritório do Cuidado, começa com uma pergunta." + logo.</t>
-        </is>
-      </c>
-      <c r="X9" s="7" t="inlineStr">
-        <is>
-          <t>Modelo M9 com ícones lineares em verde-escuro sobre Tiffany. Etiqueta "PILARES".</t>
-        </is>
-      </c>
-      <c r="Y9" s="7" t="n"/>
-      <c r="Z9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>M1-06</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Mês 1</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="17">
-        <f>$D$2+(C10-1)*7+1</f>
-        <v/>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Institucional</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>Liderança Bem-Estar</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>Virada</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>Tese da marca</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>Não é benefício. É infraestrutura de cuidado.</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>RH; RI e C-Level</t>
-        </is>
-      </c>
-      <c r="L10" s="7" t="inlineStr">
-        <is>
-          <t>Isso é mais um benefício para a lista? Por que seria diferente do que já temos?</t>
-        </is>
-      </c>
-      <c r="M10" s="7" t="inlineStr">
-        <is>
-          <t>Fixar a frase-tese e posicionar a categoria sem citar concorrentes</t>
-        </is>
-      </c>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>Carrossel</t>
-        </is>
-      </c>
-      <c r="O10" s="7" t="inlineStr">
-        <is>
-          <t>Carrossel comparativo de duas colunas (isto × aquilo): a diferença fica clara em segundos e o post é salvo e repassado ao decisor.</t>
-        </is>
-      </c>
-      <c r="P10" s="7" t="inlineStr">
-        <is>
-          <t>Instagram + LinkedIn</t>
-        </is>
-      </c>
-      <c r="Q10" s="7" t="inlineStr">
-        <is>
-          <t>FairJob</t>
-        </is>
-      </c>
-      <c r="R10" s="7" t="inlineStr">
-        <is>
-          <t>Benefício é algo que a pessoa usa se lembrar. Infraestrutura de cuidado está dentro da empresa todo dia, começa antes do problema e tem gente acompanhando.</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>Posicionamento Fair Health v3.2 (diferenciais).</t>
-        </is>
-      </c>
-      <c r="T10" s="7" t="inlineStr">
-        <is>
-          <t>Não citar marcas de terceiros nem operadoras. Sem números.</t>
-        </is>
-      </c>
-      <c r="U10" s="7" t="inlineStr">
-        <is>
-          <t>Pauta proposta</t>
-        </is>
-      </c>
-      <c r="V10" s="7" t="n"/>
-      <c r="W10" s="7" t="inlineStr">
-        <is>
-          <t>6 slides.
-1 Capa: "Não é benefício. É infraestrutura de cuidado."
-2 Benefício: a pessoa usa se lembrar. Infraestrutura: está lá todo dia, dentro da empresa.
-3 Benefício: espera o problema aparecer. Infraestrutura: começa antes.
-4 Benefício: é um cartão. Infraestrutura: é gente acompanhando, com um plano para cada pessoa.
-5 Benefício: termina na adesão. Infraestrutura: o RH acompanha o cuidado por indicadores do grupo.
-6 "O que é importante para você?" Comente CUIDADO para saber como funciona.</t>
-        </is>
-      </c>
-      <c r="X10" s="7" t="inlineStr">
-        <is>
-          <t>Modelo M1 na capa e comparativo em duas colunas (Tiffany × verde-escuro) nos slides 2 a 5.</t>
-        </is>
-      </c>
-      <c r="Y10" s="7" t="n"/>
-      <c r="Z10" s="7" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>M1-07</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Mês 1</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="17">
-        <f>$D$2+(C11-1)*7+3</f>
-        <v/>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Projetos, eventos e entregas</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>NR-1</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>Virada</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>Entregas para o RH</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Tecnologia a favor da pessoa</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>O que o RH vê (e o que não vê)</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>RH; Risco e Compliance</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>O que eu recebo para acompanhar o programa? Vou ver dados individuais?</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>Mostrar a entrega para a empresa e a regra de privacidade</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>Vídeo</t>
-        </is>
-      </c>
-      <c r="O11" s="7" t="inlineStr">
-        <is>
-          <t>Gravação de tela de um painel genérico, com texto na tela: mostra o produto de verdade sem expor ninguém e responde a dúvida que trava a decisão do RH.</t>
-        </is>
-      </c>
-      <c r="P11" s="7" t="inlineStr">
-        <is>
-          <t>Instagram + LinkedIn</t>
-        </is>
-      </c>
-      <c r="Q11" s="7" t="inlineStr">
-        <is>
-          <t>FairJob; fairdata</t>
-        </is>
-      </c>
-      <c r="R11" s="7" t="inlineStr">
-        <is>
-          <t>O RH acompanha o cuidado por indicadores do grupo, anonimizados e integrados à fairdata. O que cada pessoa conta fica no atendimento.</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>Posicionamento Fair Health v3.2 (fairdata).</t>
-        </is>
-      </c>
-      <c r="T11" s="7" t="inlineStr">
-        <is>
-          <t>Time confirma quais indicadores entram no relatório. Painel com dados fictícios e aviso "dados ilustrativos". Não prometer conformidade com a NR-1.</t>
-        </is>
-      </c>
-      <c r="U11" s="7" t="inlineStr">
-        <is>
-          <t>Pauta proposta</t>
-        </is>
-      </c>
-      <c r="V11" s="7" t="n"/>
-      <c r="W11" s="7" t="inlineStr">
-        <is>
-          <t>Reel de 25 a 30 s, gravação de tela.
-0–3 s: "O que o RH vê no Escritório do Cuidado?"
-3–15 s: rolagem pelo painel (adesão, retorno, temas mais procurados), dados ilustrativos.
-15–22 s: "O que o RH não vê: o que cada pessoa contou."
-22–30 s: "Indicadores do grupo para cuidar antes." + logo.</t>
-        </is>
-      </c>
-      <c r="X11" s="7" t="inlineStr">
-        <is>
-          <t>Modelo M9. Painel montado com dados fictícios, moldura de navegador ou de notebook.</t>
-        </is>
-      </c>
-      <c r="Y11" s="7" t="n"/>
-      <c r="Z11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>M1-08</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Mês 1</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="17">
-        <f>$D$2+(C12-1)*7+4</f>
-        <v/>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>Apresentação</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>Virada</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Plano Individualizado de Cuidado</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>Como funciona o cuidado (2/3): o plano</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>O plano é seu: como nasce o Plano Individualizado de Cuidado</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>Colaboradores</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>Vou receber uma lista de regras impossíveis de seguir?</t>
-        </is>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
-        <is>
-          <t>Explicar como o plano é montado com a pessoa (decisão compartilhada)</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr">
-        <is>
-          <t>Carrossel</t>
-        </is>
-      </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>Carrossel com card de interface (M3), já testado no carrossel de acolhimento, contado pela história de uma personagem fictícia: história prende mais que explicação e mostra o plano como algo possível.</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>Instagram + LinkedIn</t>
-        </is>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
-        <is>
-          <t>FairJob</t>
-        </is>
-      </c>
-      <c r="R12" s="7" t="inlineStr">
-        <is>
-          <t>O plano parte do que é importante para você e da sua rotina real, com ações nos pilares da MEV, e muda quando a vida muda.</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>Cartilha do Escritório do Cuidado. Personagem fictícia.</t>
-        </is>
-      </c>
-      <c r="T12" s="7" t="inlineStr">
-        <is>
-          <t>Responsável médica valida etapas e prazos. Nome único do plano: "Plano Individualizado de Cuidado" ou "Plano de Cuidado Personalizado"? Indicar no slide e na legenda que é uma história ilustrativa (personagem fictícia), para não parecer depoimento.</t>
-        </is>
-      </c>
-      <c r="U12" s="7" t="inlineStr">
-        <is>
-          <t>Pauta proposta</t>
-        </is>
-      </c>
-      <c r="V12" s="7" t="n"/>
-      <c r="W12" s="7" t="inlineStr">
-        <is>
-          <t>7 slides, com a Clara (personagem fictícia, 41 anos, supervisora de turno).
-1 Capa: "O plano é seu."
-2 A Clara chegou dizendo: "Quero voltar a ter energia para brincar com meu filho." Isso é o que importa para ela.
-3 Card do plano da Clara: 3 ações pequenas (dormir 30 min mais cedo, caminhada de 10 min no almoço, conversa quinzenal com a psicóloga).
-4 Cabe na rotina real: no turno dela, não numa rotina ideal.
-5 Muda quando a vida muda.
-6 Alguém acompanha, sem julgamento.
-7 "E para você, o que é importante?" Rodapé: "História ilustrativa. Personagem fictícia."</t>
-        </is>
-      </c>
-      <c r="X12" s="7" t="inlineStr">
-        <is>
-          <t>Modelo M3 (card de interface do plano). Sem foto de pessoa: a personagem aparece só no texto e no card.</t>
-        </is>
-      </c>
-      <c r="Y12" s="7" t="n"/>
-      <c r="Z12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>M1-09</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Mês 1</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" s="17">
-        <f>$D$2+(C13-1)*7+1</f>
-        <v/>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>Projetos, eventos e entregas</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>Liderança Bem-Estar</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>Prova</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>Adesão (número liberado)</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>Quando o cuidado está perto, as pessoas voltam</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>RH; Diretoria financeira</t>
-        </is>
-      </c>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>Programa de saúde que ninguém usa é custo. As pessoas usam isso de verdade?</t>
-        </is>
-      </c>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>Provar adesão com número liberado, contado como cuidado e não como resultado</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>Vídeo</t>
-        </is>
-      </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>Número contado como história: primeiro a cena de cuidado, depois o número, em tom calmo. É a prova que o RH leva para a diretoria, sem cara de anúncio.</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>Instagram + LinkedIn</t>
-        </is>
-      </c>
-      <c r="Q13" s="7" t="inlineStr">
-        <is>
-          <t>FairJob</t>
-        </is>
-      </c>
-      <c r="R13" s="7" t="inlineStr">
-        <is>
-          <t>Quando o cuidado está perto e começa por uma conversa, as pessoas voltam: numa indústria atendida, 8 em cada 10 pessoas voltaram para mais de um atendimento.</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>Dados internos de um cliente do setor industrial, 1º semestre de 2026 (liberados; ver aba Fontes). Sempre agregado e sem o nome da empresa.</t>
-        </is>
-      </c>
-      <c r="T13" s="7" t="inlineStr">
-        <is>
-          <t>Nenhum nome real de pessoa ou empresa no post (decisão de 09/10). Usar "uma indústria". Número suave: cuidado primeiro, número como contexto, fonte visível e discreta (aba Ciência).</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr">
-        <is>
-          <t>Pauta proposta</t>
-        </is>
-      </c>
-      <c r="V13" s="7" t="n"/>
-      <c r="W13" s="7" t="inlineStr">
-        <is>
-          <t>Reel de 18 a 22 s, tipografia e números suaves.
-0–4 s: "Ninguém volta a um lugar onde não se sentiu cuidado."
-4–9 s: "Numa indústria que atendemos, no primeiro semestre de 2026..."
-9–14 s: "8 em cada 10 pessoas voltaram para mais de um atendimento." (número em destaque, sem exagero)
-14–18 s: em texto menor: "A adesão chegou a 98%."
-18–22 s: "Cuidado que as pessoas procuram." + fonte discreta + logo.</t>
-        </is>
-      </c>
-      <c r="X13" s="7" t="inlineStr">
-        <is>
-          <t>Modelo M6 (dado com fonte) animado, em ritmo lento. Número em verde-escuro, nunca em vermelho; sem setas para cima nem efeito de "conquista".</t>
-        </is>
-      </c>
-      <c r="Y13" s="7" t="n"/>
-      <c r="Z13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>M1-10</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Mês 1</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" s="17">
-        <f>$D$2+(C14-1)*7+2</f>
-        <v/>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Apresentação</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>Prova</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>Tecnologia: wearables</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>Como funciona o cuidado (3/3): o acompanhamento</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>O cuidado não para quando a consulta acaba</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>Colaboradores; RH</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="inlineStr">
-        <is>
-          <t>Para que serve a pulseira? Vão me vigiar?</t>
-        </is>
-      </c>
-      <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>Explicar o acompanhamento com tecnologia e a regra de privacidade</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="inlineStr">
-        <is>
-          <t>Carrossel</t>
-        </is>
-      </c>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>Carrossel explicativo com a objeção no título ("vão me vigiar?"): responde a dúvida mais comum antes que ela vire resistência.</t>
-        </is>
-      </c>
-      <c r="P14" s="7" t="inlineStr">
-        <is>
-          <t>Instagram + LinkedIn</t>
-        </is>
-      </c>
-      <c r="Q14" s="7" t="inlineStr">
-        <is>
-          <t>FairJob</t>
-        </is>
-      </c>
-      <c r="R14" s="7" t="inlineStr">
-        <is>
-          <t>A smartband e a bioimpedância ajudam a olhar, junto com a pessoa, como foram as últimas semanas. Os dados ficam no atendimento; o RH vê só o grupo.</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>Cartilha do Escritório do Cuidado.</t>
-        </is>
-      </c>
-      <c r="T14" s="7" t="inlineStr">
-        <is>
-          <t>[PENDENTE] Quais dados a smartband registra e se todos os atendidos usam a pulseira (instagram/posts/wearables/README.md).</t>
-        </is>
-      </c>
-      <c r="U14" s="7" t="inlineStr">
-        <is>
-          <t>Em revisão</t>
-        </is>
-      </c>
-      <c r="V14" s="7" t="n"/>
-      <c r="W14" s="7" t="n"/>
-      <c r="X14" s="7" t="inlineStr">
-        <is>
-          <t>Arte pronta em instagram/posts/wearables (8 slides). Capa: foto de pulso sem rosto (modelo com autorização, fora das empresas-clientes) ou capa só tipográfica.</t>
-        </is>
-      </c>
-      <c r="Y14" s="7" t="n"/>
-      <c r="Z14" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>M1-11</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Mês 1</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" s="17">
-        <f>$D$2+(C15-1)*7+3</f>
-        <v/>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>Institucional</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Apresentação</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Prova</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>Origem</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>Tudo começou num hospital</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>RH; Medicina do Trabalho</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="inlineStr">
-        <is>
-          <t>De onde vem esse modelo? É só mais um programa de bem-estar?</t>
-        </is>
-      </c>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>Dar lastro à marca com a história do modelo</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="inlineStr">
-        <is>
-          <t>Vídeo</t>
-        </is>
-      </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>Linha do tempo animada (ano grande + uma frase): história de origem gera confiança e não precisa mostrar pessoas.</t>
-        </is>
-      </c>
-      <c r="P15" s="7" t="inlineStr">
-        <is>
-          <t>Instagram + LinkedIn</t>
-        </is>
-      </c>
-      <c r="Q15" s="7" t="inlineStr">
-        <is>
-          <t>FairJob</t>
-        </is>
-      </c>
-      <c r="R15" s="7" t="inlineStr">
-        <is>
-          <t>O modelo nasceu em 2009, num hospital, para colocar o paciente no centro do cuidado. Hoje, coloca quem trabalha no centro, dentro da empresa.</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>Histórico do Escritório do Paciente (2009); caso do hospital onde o modelo começou (liberado; ver aba Fontes).</t>
-        </is>
-      </c>
-      <c r="T15" s="7" t="inlineStr">
-        <is>
-          <t>Sem nomes de pessoas nem do hospital. Não usar "validado no SUS" até confirmar a fonte. Conferir datas.</t>
-        </is>
-      </c>
-      <c r="U15" s="7" t="inlineStr">
-        <is>
-          <t>Pauta proposta</t>
-        </is>
-      </c>
-      <c r="V15" s="7" t="n"/>
-      <c r="W15" s="7" t="inlineStr">
-        <is>
-          <t>Reel de 25 a 30 s, linha do tempo em tipografia.
-0–3 s: "Tudo começou num hospital."
-3–10 s: 2009: Escritório do Paciente, o paciente no centro.
-10–18 s: o que o hospital aprendeu: ouvir antes de propor.
-18–25 s: hoje: o Escritório do Cuidado, dentro da empresa.
-25–30 s: "Mesma pergunta: o que é importante para você?" + logo.
-Alternativa: carrossel no modelo M2.</t>
-        </is>
-      </c>
-      <c r="X15" s="7" t="inlineStr">
-        <is>
-          <t>Modelo M9 com marcos da linha do tempo (modelo M2 animado). Sem fotos de pessoas.</t>
-        </is>
-      </c>
-      <c r="Y15" s="7" t="n"/>
-      <c r="Z15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>M1-12</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Mês 1</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" s="17">
-        <f>$D$2+(C16-1)*7+4</f>
-        <v/>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Projetos, eventos e entregas</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>NR-1</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>Prova</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>Na imprensa: artigo sobre riscos psicossociais</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>Saúde mental é de todos (2/2)</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>A pergunta maior</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>RH; Lideranças</t>
-        </is>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>Como olhar para a saúde mental do time sem simplificar?</t>
-        </is>
-      </c>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>Reaproveitar o artigo com uma frase forte e reforçar a autoridade</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="inlineStr">
-        <is>
-          <t>Foto única</t>
-        </is>
-      </c>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>Card de citação: uma frase forte, fácil de compartilhar nos stories e no LinkedIn. Reaproveita o artigo sem repetir o carrossel.</t>
-        </is>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>Instagram + LinkedIn</t>
-        </is>
-      </c>
-      <c r="Q16" s="7" t="inlineStr">
-        <is>
-          <t>FairJob</t>
-        </is>
-      </c>
-      <c r="R16" s="7" t="inlineStr">
-        <is>
-          <t>"Antes de perguntar apenas o que o trabalho está fazendo com a saúde mental das pessoas, deveríamos fazer uma pergunta maior: o que a nossa forma de viver em sociedade está fazendo com a saúde mental das pessoas?"</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>Artigo "Riscos psicossociais no ambiente de trabalho e saúde", RH Pra Você, 25/09/2026. https://rhpravoce.com.br/colab/riscos-psicossociais-no-ambiente-de-trabalho-2</t>
-        </is>
-      </c>
-      <c r="T16" s="7" t="inlineStr">
-        <is>
-          <t>Citação literal conferida com o artigo. Crédito só ao artigo e ao veículo, sem nome do autor. Nenhum nome real de pessoa ou empresa no post (decisão de 09/10).</t>
-        </is>
-      </c>
-      <c r="U16" s="7" t="inlineStr">
-        <is>
-          <t>Pauta proposta</t>
-        </is>
-      </c>
-      <c r="V16" s="7" t="n"/>
-      <c r="W16" s="7" t="inlineStr">
+      <c r="W23" s="7" t="n"/>
+      <c r="X23" s="7" t="inlineStr">
         <is>
           <t>Imagem única: a pergunta em destaque, assinatura "Do artigo 'Riscos psicossociais no ambiente de trabalho e saúde', RH Pra Você". Legenda curta que liga a pergunta à da marca ("o que é importante para você?") e convida a ler o artigo.</t>
         </is>
       </c>
-      <c r="X16" s="7" t="inlineStr">
+      <c r="Y23" s="7" t="inlineStr">
         <is>
           <t>Modelo M8 (citação), sem foto.</t>
         </is>
       </c>
-      <c r="Y16" s="7" t="n"/>
-      <c r="Z16" s="7" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>M1-13</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Mês 1</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" s="17">
-        <f>$D$2+(C17-1)*7+0</f>
-        <v/>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>Liderança Bem-Estar</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>Convite</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Pilar: sono</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>Pilares da MEV (1: sono)</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>Dormir não é tempo perdido</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>Colaboradores</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>Por que eu acordo cansado? O que dá para mudar na rotina?</t>
-        </is>
-      </c>
-      <c r="M17" s="7" t="inlineStr">
-        <is>
-          <t>Educar sobre o pilar sono e convidar o colaborador a procurar o Escritório</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>Vídeo</t>
-        </is>
-      </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>Reel de "3 hábitos" com texto na tela sobre imagens de banco: dica prática e salvável, sem rosto e sem gravar nas empresas.</t>
-        </is>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="Q17" s="7" t="inlineStr">
-        <is>
-          <t>FairJob</t>
-        </is>
-      </c>
-      <c r="R17" s="7" t="inlineStr">
-        <is>
-          <t>Dormir não é tempo perdido. A faixa saudável para adultos fica entre 7 e 9 horas por noite. No Escritório do Cuidado, o sono entra no plano a partir da sua rotina real.</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>Guia "Saúde mental: o cuidado no dia a dia" (higiene do sono; OMS, APA, IPq-USP). Hafner M. et al. Why sleep matters: the economic costs of insufficient sleep. RAND Europe, 2016 (RR-1791). https://www.rand.org/news/press/2016/11/30.html</t>
-        </is>
-      </c>
-      <c r="T17" s="7" t="inlineStr">
-        <is>
-          <t>Responsável médica valida as orientações. Sem promessa clínica. Número suave: cuidado primeiro, número como contexto, fonte visível e discreta (aba Ciência).</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="inlineStr">
-        <is>
-          <t>Pauta proposta</t>
-        </is>
-      </c>
-      <c r="V17" s="7" t="n"/>
-      <c r="W17" s="7" t="inlineStr">
-        <is>
-          <t>Reel de 22 a 27 s.
-0–3 s: "Acorda cansado mesmo dormindo?"
-3–6 s: em texto calmo: "Para adultos, o sono saudável fica entre 7 e 9 horas." (fonte discreta: RAND Europe, 2016)
-6–19 s: 3 hábitos, um por cena (tela antes de dormir, horário regular, cafeína à tarde).
-19–27 s: "Se o cansaço não passa, conversa com a gente no Escritório do Cuidado." + logo.
-Legenda (opcional, para o RH no LinkedIn): um estudo da RAND Europe estimou que a falta de sono custa mais de 1 milhão de dias de trabalho por ano só nos Estados Unidos.</t>
-        </is>
-      </c>
-      <c r="X17" s="7" t="inlineStr">
-        <is>
-          <t>Modelo M9 com etiqueta "PILARES · SONO". Imagens de banco (quarto, celular à noite), sem rosto identificável.</t>
-        </is>
-      </c>
-      <c r="Y17" s="7" t="n"/>
-      <c r="Z17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>M1-14</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Mês 1</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D18" s="17">
-        <f>$D$2+(C18-1)*7+1</f>
-        <v/>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>Institucional</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Liderança Bem-Estar</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>Convite</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>A pergunta (com a recomendação da OMS)</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>Ciência no cuidado</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
-        <is>
-          <t>Uma pergunta que todo líder pode fazer</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>Lideranças; RH</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>Como a liderança pode cuidar do time no dia a dia, sem ser médica nem psicóloga?</t>
-        </is>
-      </c>
-      <c r="M18" s="7" t="inlineStr">
-        <is>
-          <t>Levar a pergunta da marca para a liderança, com o respaldo da recomendação da OMS, e gerar conversa</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="inlineStr">
-        <is>
-          <t>Carrossel</t>
-        </is>
-      </c>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>Carrossel de ciência aplicada: a recomendação de uma fonte respeitada (OMS) vira um gesto simples que o líder pode repetir. Fecha com pergunta aberta, que gera comentários.</t>
-        </is>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
-        <is>
-          <t>Instagram + LinkedIn</t>
-        </is>
-      </c>
-      <c r="Q18" s="7" t="inlineStr">
-        <is>
-          <t>FairJob</t>
-        </is>
-      </c>
-      <c r="R18" s="7" t="inlineStr">
-        <is>
-          <t>A OMS recomenda preparar as lideranças para prevenir ambientes de estresse e acolher quem está em sofrimento. Um bom começo cabe numa pergunta: o que é importante para você?</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>OMS. Guidelines on mental health at work, 28/09/2022 (com a OIT: policy brief "Mental health at work"). https://www.who.int/news/item/28-09-2022-who-and-ilo-call-for-new-measures-to-tackle-mental-health-issues-at-work</t>
-        </is>
-      </c>
-      <c r="T18" s="7" t="inlineStr">
-        <is>
-          <t>Conferir a redação da recomendação nas diretrizes da OMS. O líder não substitui o cuidado clínico: deixar claro onde pedir ajuda.</t>
-        </is>
-      </c>
-      <c r="U18" s="7" t="inlineStr">
-        <is>
-          <t>Pauta proposta</t>
-        </is>
-      </c>
-      <c r="V18" s="7" t="n"/>
-      <c r="W18" s="7" t="inlineStr">
-        <is>
-          <t>6 slides.
-1 Capa: "Uma pergunta que todo líder pode fazer."
-2 Em 2022, a OMS publicou suas primeiras diretrizes sobre saúde mental no trabalho. Uma das recomendações: preparar as lideranças.
-3 Para quê? Para prevenir ambientes de estresse e acolher quem está em sofrimento.
-4 Não é virar terapeuta. É perguntar, ouvir e saber para onde encaminhar.
-5 Um bom começo: "O que é importante para você?"
-6 Líder, quando foi a última vez que você fez essa pergunta? Conta nos comentários. Fonte: OMS, 2022.
-Stories no mesmo dia com caixa de perguntas.</t>
-        </is>
-      </c>
-      <c r="X18" s="7" t="inlineStr">
-        <is>
-          <t>Modelo M1 na capa e M2 nos demais; fonte no rodapé (M6).</t>
-        </is>
-      </c>
-      <c r="Y18" s="7" t="n"/>
-      <c r="Z18" s="7" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>M1-15</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Mês 1</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D19" s="17">
-        <f>$D$2+(C19-1)*7+3</f>
-        <v/>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Projetos, eventos e entregas</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Apresentação</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>Convite</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>Como começa numa empresa</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>Como chega a uma empresa</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>Como o Escritório do Cuidado chega à sua empresa</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>RH; Diretoria financeira</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>Quero isso na minha empresa. Por onde começa?</t>
-        </is>
-      </c>
-      <c r="M19" s="7" t="inlineStr">
-        <is>
-          <t>Deixar clara a oferta e o primeiro passo comercial</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="inlineStr">
-        <is>
-          <t>Vídeo</t>
-        </is>
-      </c>
-      <c r="O19" s="7" t="inlineStr">
-        <is>
-          <t>Passo a passo animado com chamada para ação por palavra-chave ("comente CUIDADO"): fecha o mês com um caminho claro para o RH.</t>
-        </is>
-      </c>
-      <c r="P19" s="7" t="inlineStr">
-        <is>
-          <t>Instagram + LinkedIn</t>
-        </is>
-      </c>
-      <c r="Q19" s="7" t="inlineStr">
-        <is>
-          <t>FairJob</t>
-        </is>
-      </c>
-      <c r="R19" s="7" t="inlineStr">
-        <is>
-          <t>Começa com um diagnóstico gratuito, segue com uma proposta personalizada e chega à implantação. Comente CUIDADO.</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>Executive Summary (etapas comerciais).</t>
-        </is>
-      </c>
-      <c r="T19" s="7" t="inlineStr">
-        <is>
-          <t>Não citar prazos de cada etapa sem confirmação. Confirmar o destino do link (www.fairhealth.com.br) e quem responde os comentários e DMs.</t>
-        </is>
-      </c>
-      <c r="U19" s="7" t="inlineStr">
-        <is>
-          <t>Pauta proposta</t>
-        </is>
-      </c>
-      <c r="V19" s="7" t="n"/>
-      <c r="W19" s="7" t="inlineStr">
-        <is>
-          <t>Reel de 20 a 25 s, motion em 3 passos.
-0–3 s: "Como levar o Escritório do Cuidado para a sua empresa?"
-3–9 s: PASSO 1 · Diagnóstico gratuito
-9–15 s: PASSO 2 · Proposta personalizada
-15–20 s: PASSO 3 · Implantação e primeiros atendimentos
-20–25 s: "Comente CUIDADO." + logo.</t>
-        </is>
-      </c>
-      <c r="X19" s="7" t="inlineStr">
-        <is>
-          <t>Modelo M2 (passos) animado e M1 no fim.</t>
-        </is>
-      </c>
-      <c r="Y19" s="7" t="n"/>
-      <c r="Z19" s="7" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>M1-16</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Mês 1</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D20" s="17">
-        <f>$D$2+(C20-1)*7+4</f>
-        <v/>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Liderança Bem-Estar</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>Convite</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>Ciência: estilo de vida e diabetes (Dia Mundial do Diabetes, 14/11)</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>Ciência no cuidado</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>Estilo de vida também é tratamento sério</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>Colaboradores; RH; Medicina do Trabalho</t>
-        </is>
-      </c>
-      <c r="L20" s="7" t="inlineStr">
-        <is>
-          <t>Mudar hábitos faz diferença de verdade ou é só conselho?</t>
-        </is>
-      </c>
-      <c r="M20" s="7" t="inlineStr">
-        <is>
-          <t>Mostrar a base científica da MEV com um estudo clássico, na véspera do Dia Mundial do Diabetes</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="inlineStr">
-        <is>
-          <t>Carrossel</t>
-        </is>
-      </c>
-      <c r="O20" s="7" t="inlineStr">
-        <is>
-          <t>Carrossel "o que a ciência diz": um estudo, uma ideia, a fonte completa. Conecta uma data do calendário ao nosso trabalho com evidência, sem oportunismo.</t>
-        </is>
-      </c>
-      <c r="P20" s="7" t="inlineStr">
-        <is>
-          <t>Instagram + LinkedIn</t>
-        </is>
-      </c>
-      <c r="Q20" s="7" t="inlineStr">
-        <is>
-          <t>FairJob</t>
-        </is>
-      </c>
-      <c r="R20" s="7" t="inlineStr">
-        <is>
-          <t>Num estudo clássico, publicado no New England Journal of Medicine, mudanças de estilo de vida reduziram em 58% os novos casos de diabetes tipo 2 em pessoas com risco, em comparação com o placebo. É por isso que o nosso cuidado começa pela rotina.</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>Diabetes Prevention Program Research Group. Reduction in the incidence of type 2 diabetes with lifestyle intervention or metformin. N Engl J Med. 2002;346(6):393-403. doi:10.1056/NEJMoa012512</t>
-        </is>
-      </c>
-      <c r="T20" s="7" t="inlineStr">
-        <is>
-          <t>Responsável médica valida a leitura do estudo. Deixar claro que o estudo foi com adultos com pré-diabetes (risco aumentado) e que não é promessa individual. Número suave: cuidado primeiro, número como contexto, fonte visível e discreta (aba Ciência).</t>
-        </is>
-      </c>
-      <c r="U20" s="7" t="inlineStr">
-        <is>
-          <t>Pauta proposta</t>
-        </is>
-      </c>
-      <c r="V20" s="7" t="n"/>
-      <c r="W20" s="7" t="inlineStr">
-        <is>
-          <t>7 slides.
-1 Capa: "Estilo de vida também é tratamento sério."
-2 Amanhã é o Dia Mundial do Diabetes. Vale lembrar de um estudo que mudou a forma de cuidar.
-3 Mais de 3 mil adultos com risco aumentado de diabetes tipo 2 foram acompanhados por quase 3 anos.
-4 Quem mudou a rotina (alimentação e 150 minutos de atividade física por semana) teve 58% menos casos novos do que o grupo placebo.
-5 Em texto menor: mais do que o grupo que recebeu medicamento (31%).
-6 Não é promessa: é a ciência dizendo que a rotina importa. Por isso o nosso cuidado começa nela, com um plano feito para cada pessoa.
-7 "O que é importante para você?" Fonte completa: Diabetes Prevention Program, N Engl J Med, 2002.</t>
-        </is>
-      </c>
-      <c r="X20" s="7" t="inlineStr">
-        <is>
-          <t>Modelo M6 (dado com fonte) suave nos slides 4 e 5, M2 nos demais. Números em verde-escuro, sem destaque alarmista.</t>
-        </is>
-      </c>
-      <c r="Y20" s="7" t="n"/>
-      <c r="Z20" s="7" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>M2-01</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Mês 2</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D21" s="17">
-        <f>$D$2+(C21-1)*7+0</f>
-        <v/>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>Projetos, eventos e entregas</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>Stop Loss</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>Prova</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>Ciência: prevenção como investimento</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>Ciência no cuidado</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>Prevenção também é investimento</t>
-        </is>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>RH; Diretoria financeira</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>Prevenção dá retorno para a empresa ou é só mais um custo?</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>Mostrar, com estudos externos e a fonte visível, que prevenção também é investimento</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr">
-        <is>
-          <t>Foto única</t>
-        </is>
-      </c>
-      <c r="O21" s="7" t="inlineStr">
-        <is>
-          <t>A arte já está pronta: é o slide de números que saiu do carrossel "O que é a fairhealth" para ele caber em 10 fotos. Um post só dele dá espaço para explicar cada estudo com calma.</t>
-        </is>
-      </c>
-      <c r="P21" s="7" t="inlineStr">
-        <is>
-          <t>Instagram + LinkedIn</t>
-        </is>
-      </c>
-      <c r="Q21" s="7" t="inlineStr">
-        <is>
-          <t>FairJob</t>
-        </is>
-      </c>
-      <c r="R21" s="7" t="inlineStr">
-        <is>
-          <t>O que os estudos apontam: −28% de absenteísmo (Harvard Business Review, 2022) e −22% de custos com saúde (SHRM, 2023).</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>Harvard Business Review (2022); SHRM (2023). Números oficiais desde 25/09 (instagram/voice.md).</t>
-        </is>
-      </c>
-      <c r="T21" s="7" t="inlineStr">
-        <is>
-          <t>Confirmar o que cada estudo mediu (tipo de programa e população) antes de publicar. São estudos externos, nunca resultado da Fair Health. Número suave: cuidado primeiro, número como contexto, fonte visível e discreta (aba Ciência).</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
-          <t>Em revisão</t>
-        </is>
-      </c>
-      <c r="V21" s="7" t="inlineStr">
-        <is>
-          <t>Prevenção também é investimento.
-Cuidar antes faz bem para as pessoas. E os estudos mostram que também faz diferença para a empresa:
-−28% de absenteísmo (Harvard Business Review, 2022)
-−22% de custos com saúde (SHRM, 2023)
-São números de estudos externos, não uma promessa de resultado.
-É esse o trabalho da fairhealth: medicina preventiva, dentro da empresa, com um plano de cuidado para cada pessoa.
-Quer conversar sobre isso na sua empresa? Fale com a gente pelo direct.
-#fairhealth #saudecorporativa #medicinapreventiva #absenteismo #gestaodepessoas</t>
-        </is>
-      </c>
-      <c r="W21" s="7" t="inlineStr">
-        <is>
-          <t>Foto única 1080x1350, já pronta. Se quisermos explicar melhor cada estudo, vira um carrossel curto: capa, um número por slide com a fonte, fechamento.</t>
-        </is>
-      </c>
-      <c r="X21" s="7" t="inlineStr">
-        <is>
-          <t>Canva: design "O que é a fairhealth · carrossel v7", página guardada depois do carrossel (luz tiffany, números em tiffany, sem brilho). Repositório: instagram/posts/o-que-e-a-fairhealth/png-v10/d10.png.</t>
-        </is>
-      </c>
-      <c r="Y21" s="7" t="n"/>
-      <c r="Z21" s="7" t="inlineStr">
-        <is>
-          <t>Decisão da Nina (12/10): o slide de números saiu do carrossel "O que é a fairhealth" (limite de 10 fotos do Instagram) e vira um post separado.</t>
+      <c r="Z23" s="7" t="n"/>
+      <c r="AA23" s="7" t="inlineStr">
+        <is>
+          <t>Antes: M1-12 (ordem de 12/10). Saiu do Mês 1 em 13/10, junto com o M2-02. Data e posição a revisar quando o Mês 2 for montado.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Z81"/>
+  <autoFilter ref="A4:AA83"/>
   <mergeCells count="1">
     <mergeCell ref="A2:C2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E81">
+  <conditionalFormatting sqref="E5:E83">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E5="Institucional"</formula>
     </cfRule>
@@ -4193,12 +4662,12 @@
       <formula>$E5="Projetos, eventos e entregas"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N5:N81">
+  <conditionalFormatting sqref="O5:O83">
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>$N5="Vídeo"</formula>
+      <formula>$O5="Vídeo"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G81">
+  <conditionalFormatting sqref="G5:G83">
     <cfRule type="expression" priority="5" dxfId="4">
       <formula>$G5="Abertura"</formula>
     </cfRule>
@@ -4216,25 +4685,25 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
-    <dataValidation sqref="E5:E81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista (aba Listas). Para criar um valor novo, inclua-o na aba Listas." type="list" errorStyle="warning">
+    <dataValidation sqref="E5:E83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista (aba Listas). Para criar um valor novo, inclua-o na aba Listas." type="list" errorStyle="warning">
       <formula1>=Listas!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation sqref="N5:N81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista (aba Listas). Para criar um valor novo, inclua-o na aba Listas." type="list" errorStyle="warning">
+    <dataValidation sqref="O5:O83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista (aba Listas). Para criar um valor novo, inclua-o na aba Listas." type="list" errorStyle="warning">
       <formula1>=Listas!$B$2:$B$5</formula1>
     </dataValidation>
-    <dataValidation sqref="P5:P81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista (aba Listas). Para criar um valor novo, inclua-o na aba Listas." type="list" errorStyle="warning">
+    <dataValidation sqref="Q5:Q83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista (aba Listas). Para criar um valor novo, inclua-o na aba Listas." type="list" errorStyle="warning">
       <formula1>=Listas!$C$2:$C$5</formula1>
     </dataValidation>
-    <dataValidation sqref="U5:U81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista (aba Listas). Para criar um valor novo, inclua-o na aba Listas." type="list" errorStyle="warning">
+    <dataValidation sqref="V5:V83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista (aba Listas). Para criar um valor novo, inclua-o na aba Listas." type="list" errorStyle="warning">
       <formula1>=Listas!$D$2:$D$15</formula1>
     </dataValidation>
-    <dataValidation sqref="B5:B81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista (aba Listas). Para criar um valor novo, inclua-o na aba Listas." type="list" errorStyle="warning">
+    <dataValidation sqref="B5:B83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista (aba Listas). Para criar um valor novo, inclua-o na aba Listas." type="list" errorStyle="warning">
       <formula1>=Listas!$E$2:$E$13</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista (aba Listas). Para criar um valor novo, inclua-o na aba Listas." type="list" errorStyle="warning">
+    <dataValidation sqref="F5:F83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista (aba Listas). Para criar um valor novo, inclua-o na aba Listas." type="list" errorStyle="warning">
       <formula1>=Listas!$F$2:$F$7</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista (aba Listas). Para criar um valor novo, inclua-o na aba Listas." type="list" errorStyle="warning">
+    <dataValidation sqref="G5:G83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista (aba Listas). Para criar um valor novo, inclua-o na aba Listas." type="list" errorStyle="warning">
       <formula1>=Listas!$G$2:$G$6</formula1>
     </dataValidation>
   </dataValidations>
@@ -4327,7 +4796,7 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>M1-03, M1-11</t>
+          <t>M1-03, M1-02</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4828,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>M1-05, M1-15</t>
+          <t>M1-06, M1-16</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4860,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>M1-07</t>
+          <t>M1-09</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4892,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>M1-09</t>
+          <t>M1-11</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4924,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>M1-14, M1-16</t>
+          <t>M1-14, M1-15</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4988,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>M1-02, M1-10</t>
+          <t>M1-05, M1-08</t>
         </is>
       </c>
     </row>
@@ -4551,7 +5020,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>M1-08</t>
+          <t>M1-07</t>
         </is>
       </c>
     </row>
@@ -4583,7 +5052,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>M1-04</t>
+          <t>M2-02</t>
         </is>
       </c>
     </row>
@@ -4615,7 +5084,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>M1-06</t>
+          <t>M1-10</t>
         </is>
       </c>
     </row>
@@ -4647,7 +5116,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>M1-12</t>
+          <t>M2-03</t>
         </is>
       </c>
     </row>
@@ -4751,7 +5220,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>M1-09: 8 em cada 10 em destaque; 98% em texto menor.</t>
+          <t>M1-11: 8 em cada 10 em destaque; 98% em texto menor.</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -4958,7 +5427,7 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>M1-16</t>
+          <t>M1-15</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5575,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>M1-04</t>
+          <t>M2-02</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5768,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>M1-04, M1-12</t>
+          <t>M2-02, M2-03</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5795,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>M1-09</t>
+          <t>M1-11</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5861,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Definição de Medicina do Estilo de Vida e seus 6 pilares: alimentação, atividade física, sono, manejo do estresse, relacionamentos e evitar substâncias de risco.</t>
+          <t>Definição de Medicina do Estilo de Vida e seus pilares. O conteúdo usa 7: os seis do one-pager (alimentação saudável, movimento, gerenciamento de estresse, sono de qualidade, manejo de vícios e relacionamentos) mais espiritualidade e propósito.</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -5402,12 +5871,12 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Responsável médica confere. Espiritualidade fora (a confirmar).</t>
+          <t>Responsável médica confere a definição. 7 pilares por decisão da Nina (12/10).</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>M1-05</t>
+          <t>M1-06</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5658,39 +6127,39 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Checklist "Antes de preencher a planilha: 5 perguntas sobre riscos psicossociais"</t>
+          <t>Artigo da RH Pra Você sobre riscos psicossociais (carrossel e card de citação)</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Mês 1 (versão de 09/10)</t>
+          <t>Mês 1 (ordem de 12/10: M1-04 e M1-12)</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Ideia</t>
+          <t>Pauta proposta</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Saiu do Mês 1 para dar lugar ao post de ciência do Dia Mundial do Diabetes. Abre bem o mês da NR-1.</t>
+          <t>Saiu do Mês 1 em 13/10, porque o Mês 1 conta a história da marca. Abre o capítulo da NR-1.</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Mês 2, semana 1</t>
+          <t>Mês 2, semana 1 (M2-02 e M2-03)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Série NR-1 (contexto, diagnóstico, cuidado individualizado, acompanhamento, versão para colaboradores)</t>
+          <t>Checklist "Antes de preencher a planilha: 5 perguntas sobre riscos psicossociais"</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Plano mensal (Mês 2)</t>
+          <t>Mês 1 (versão de 09/10)</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -5700,24 +6169,24 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Próximo capítulo. O artigo da RH Pra Você já abre o tema. Estudo de Goh, Pfeffer e Zenios (aba Ciência) para o RH.</t>
+          <t>Saiu do Mês 1 para dar lugar ao post de ciência do Dia Mundial do Diabetes. Abre bem o mês da NR-1.</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Mês 2</t>
+          <t>Mês 2, semana 1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Série "Ciência no cuidado": um estudo por mês ligado ao pilar ou ao argumento do mês</t>
+          <t>Série NR-1 (contexto, diagnóstico, cuidado individualizado, acompanhamento, versão para colaboradores)</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Decisão de 09/10</t>
+          <t>Plano mensal (Mês 2)</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -5727,24 +6196,24 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Estudos na aba Ciência: atividade física e saúde mental (Singh, 2023), relações sociais (Holt-Lunstad, 2010), estressores do trabalho (Goh, 2016), OMS (12 bilhões de dias).</t>
+          <t>Próximo capítulo. O artigo da RH Pra Você já abre o tema. Estudo de Goh, Pfeffer e Zenios (aba Ciência) para o RH.</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Todo mês</t>
+          <t>Mês 2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>"O que nos diferencia": plano de saúde, plataformas de bem-estar e QVT (3 posts)</t>
+          <t>Série "Ciência no cuidado": um estudo por mês ligado ao pilar ou ao argumento do mês</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Posicionamento v3.2</t>
+          <t>Decisão de 09/10</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -5754,24 +6223,24 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Falar da categoria, sem citar marcas.</t>
+          <t>Estudos na aba Ciência: atividade física e saúde mental (Singh, 2023), relações sociais (Holt-Lunstad, 2010), estressores do trabalho (Goh, 2016), OMS (12 bilhões de dias).</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Mês 2 ou 3</t>
+          <t>Todo mês</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>"Quem cuida também precisa de cuidado" (edição especial para a saúde)</t>
+          <t>"O que nos diferencia": plano de saúde, plataformas de bem-estar e QVT (3 posts)</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Posicionamento v3.2 (arenas)</t>
+          <t>Posicionamento v3.2</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -5781,24 +6250,24 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Liga a origem hospitalar ao cuidado de quem cuida.</t>
+          <t>Falar da categoria, sem citar marcas.</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Mês 3</t>
+          <t>Mês 2 ou 3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Pilares da MEV, um por vez (alimentação, atividade física, manejo do estresse, relacionamentos, evitar substâncias de risco)</t>
+          <t>"Quem cuida também precisa de cuidado" (edição especial para a saúde)</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Calendário de 90 dias</t>
+          <t>Posicionamento v3.2 (arenas)</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -5808,24 +6277,24 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>6 pilares, sem espiritualidade (a confirmar). Sono já entra no Mês 1.</t>
+          <t>Liga a origem hospitalar ao cuidado de quem cuida.</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Um pilar por mês</t>
+          <t>Mês 3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Histórias com personagens fictícias (um dia na rotina de quem é cuidado)</t>
+          <t>Pilares da MEV, um por vez (alimentação saudável, movimento, gerenciamento de estresse, manejo de vícios, relacionamentos, espiritualidade e propósito)</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Decisão de 09/10</t>
+          <t>Calendário de 90 dias</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -5835,24 +6304,24 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Sempre sinalizadas como ilustrativas.</t>
+          <t>7 pilares (decisão da Nina, 12/10). Sono abre a série no Mês 1 (M1-13), retomando a Clara do M1-07.</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Todo mês, 1 peça</t>
+          <t>Um pilar por mês</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Case do hospital onde o modelo começou (sem o nome)</t>
+          <t>Etiqueta de capítulo na capa ("Capítulo 1 · Por que existimos" e assim por diante)</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>voice.md (liberado)</t>
+          <t>Reorganização de 13/10</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -5862,37 +6331,91 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Prova da origem do modelo.</t>
+          <t>[SUGESTÃO] Ajuda quem chega pelo perfil a ler os posts como uma sequência. Fica pequena, no lugar da etiqueta de tema.</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Mês de Stop Loss ou de prova</t>
+          <t>Mês 1, se aprovada</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
+          <t>Histórias com personagens fictícias (um dia na rotina de quem é cuidado)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Decisão de 09/10</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Ideia</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Sempre sinalizadas como ilustrativas.</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Todo mês, 1 peça</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Case do hospital onde o modelo começou (sem o nome)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>voice.md (liberado)</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Ideia</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Prova da origem do modelo.</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Mês de Stop Loss ou de prova</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
           <t>Indicadores para o RH (HBR 2022, SHRM 2023)</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>voice.md (liberado)</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Pauta proposta</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>Virou o post M2-01 "Prevenção também é investimento" (arte pronta, saiu do carrossel "O que é a fairhealth" em 12/10).</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>Mês 2, semana 1 (M2-01)</t>
         </is>
@@ -6268,7 +6791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6403,7 +6926,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Todas as pautas com "responsável médica"; M1-13, M1-14, M1-16</t>
+          <t>Todas as pautas com "responsável médica"; M1-13, M1-14, M1-15</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -6428,12 +6951,12 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>M1-05 e série Pilares</t>
+          <t>M1-06 e série Pilares</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Aberta</t>
+          <t>Resolvida em 12/10: 7 pilares, com espiritualidade e propósito (decisão da Nina).</t>
         </is>
       </c>
     </row>
@@ -6478,7 +7001,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>M1-08</t>
+          <t>M1-07</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -6503,7 +7026,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>M1-02, M1-08, M1-10</t>
+          <t>M1-05, M1-07, M1-08</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -6528,7 +7051,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>M1-11</t>
+          <t>M1-02</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -6553,7 +7076,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>M1-07</t>
+          <t>M1-09</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -6628,7 +7151,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>M1-06, M1-15</t>
+          <t>M1-10, M1-16</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -6643,17 +7166,17 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Texto, prazos e obrigações da NR-1 com fonte oficial; aprovação da posição [SUGESTÃO] 1 do voice.md.</t>
+          <t>Origem e licença das fotos dos pilares (enviadas em 12/10).</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Responsável médica + sócios</t>
+          <t>Comunicação</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Banco de ideias (checklist NR-1)</t>
+          <t>M1-04</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -6668,7 +7191,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Fontes dos números do posicionamento (23%, R$ 2.400, burnout).</t>
+          <t>Aprovar as cinco crenças do manifesto "Fazemos o certo pelos motivos certos".</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -6678,7 +7201,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Fontes</t>
+          <t>M1-12</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -6693,22 +7216,22 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Crédito do autor do artigo da RH Pra Você.</t>
+          <t>Etiqueta de capítulo na capa dos posts do Mês 1 [SUGESTÃO].</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Comunicação</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>M1-04, M1-12</t>
+          <t>Mês 1</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Resolvida em 09/10: citar só o artigo e o veículo, sem nome.</t>
+          <t>Aberta</t>
         </is>
       </c>
     </row>
@@ -6718,20 +7241,95 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
+          <t>Texto, prazos e obrigações da NR-1 com fonte oficial; aprovação da posição [SUGESTÃO] 1 do voice.md.</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Responsável médica + sócios</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Banco de ideias (checklist NR-1)</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Aberta</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Fontes dos números do posicionamento (23%, R$ 2.400, burnout).</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Sócios</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Fontes</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Aberta</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Crédito do autor do artigo da RH Pra Você.</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Comunicação</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>M2-02, M2-03</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Resolvida em 09/10: citar só o artigo e o veículo, sem nome.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
           <t>Números no Mês 1 e nome do cliente industrial.</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Sócios</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>M1-09</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>M1-11</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>Resolvida em 09/10: números sim, com suavidade; nunca o nome do cliente.</t>
         </is>
